--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -2829,14 +2829,22 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/health -&gt; 200 application/json {status:'ok', runtime:{enabled,runtime_status,started_at,last_error,llm_failure_count,llm_last_failure_at,updated_at}}; all 7 runtime keys present.</t>
+        </is>
+      </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr"/>
-      <c r="M50" s="2" t="inlineStr"/>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -2876,14 +2884,22 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/sentinel/toggle with Origin: http://evil.example -&gt; 403, Flask default HTML body containing 'cross-site request rejected'.</t>
+        </is>
+      </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr"/>
-      <c r="M51" s="2" t="inlineStr"/>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2923,14 +2939,22 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>POST with Origin: null -&gt; 403.</t>
+        </is>
+      </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr"/>
-      <c r="M52" s="2" t="inlineStr"/>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -2970,14 +2994,22 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>POST toggle with Origin: http://127.0.0.1:5001 -&gt; 200 {state:{enabled:false,...}} (guard passed, handler ran).</t>
+        </is>
+      </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr"/>
-      <c r="M53" s="2" t="inlineStr"/>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3017,14 +3049,22 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>No Origin + Referer http://evil.example/page -&gt; 403; Referer http://127.0.0.1:5001/page -&gt; 200.</t>
+        </is>
+      </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr"/>
-      <c r="M54" s="2" t="inlineStr"/>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3064,14 +3104,22 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Origin https://public.example + X-Forwarded-Host public.example -&gt; 200 {state:...}.</t>
+        </is>
+      </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr"/>
-      <c r="M55" s="2" t="inlineStr"/>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -3111,14 +3159,22 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/settings with Origin: http://evil.example -&gt; 200.</t>
+        </is>
+      </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3158,14 +3214,22 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Second instance on :5002 with BASIC_AUTH_USER=u/PASSWORD=p: GET /api/settings no creds -&gt; 401 body 'authentication required' + WWW-Authenticate: Basic realm="DockSentinel"; -u u:p -&gt; 200; -u u:wrong -&gt; 401; GET / and POST toggle -&gt; 401. Main :5001 (not enabled) -&gt; 200 without creds.</t>
+        </is>
+      </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr"/>
-      <c r="M57" s="2" t="inlineStr"/>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3205,14 +3269,22 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>On :5002 with basic auth enabled, GET /api/health without Authorization -&gt; 200 {status:'ok',runtime:{...}}.</t>
+        </is>
+      </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr"/>
-      <c r="M58" s="2" t="inlineStr"/>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -3252,14 +3324,22 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/settings {nightly_hour:99} -&gt; 400 {"error":"Input should be less than or equal to 23"}; value not echoed.</t>
+        </is>
+      </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -3299,14 +3379,22 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/settings -&gt; 200 with 32 fields incl. llm_base_url,llm_model,nightly_hour,...,updated_at; llm_api_key '********' when set, '' after cleared; telegram_token null when unset.</t>
+        </is>
+      </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr"/>
-      <c r="M60" s="2" t="inlineStr"/>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -3346,14 +3434,22 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>PUT {nightly_hour:7,nightly_minute:30} -&gt; 200 full masked schema with nightly_hour 7, nightly_minute 30; other fields unchanged; updated_at bumped.</t>
+        </is>
+      </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -3393,14 +3489,22 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Set llm_api_key sk-test then PUT '********', '', '   ' -&gt; each 200 and llm_api_key still '********' (secret retained).</t>
+        </is>
+      </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr"/>
-      <c r="M62" s="2" t="inlineStr"/>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -3440,14 +3544,22 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>PUT {telegram_token:'123:abc'} -&gt; 200, response telegram_token '********'.</t>
+        </is>
+      </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr"/>
-      <c r="M63" s="2" t="inlineStr"/>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -3487,14 +3599,22 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>PUT {llm_api_key:null} -&gt; 200 llm_api_key ''; subsequent GET also '' (cleared, not masked).</t>
+        </is>
+      </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr"/>
-      <c r="M64" s="2" t="inlineStr"/>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -3534,14 +3654,22 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>PUT {bogus:1} -&gt; 400 {"error":"Extra inputs are not permitted"}.</t>
+        </is>
+      </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr"/>
-      <c r="M65" s="2" t="inlineStr"/>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -3581,14 +3709,22 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>PUT {id:5} -&gt; 400 Extra inputs not permitted; PUT {updated_at:...} -&gt; 400 same.</t>
+        </is>
+      </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr"/>
-      <c r="M66" s="2" t="inlineStr"/>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -3628,14 +3764,22 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>nightly_minute 60 -&gt; 400 'Input should be less than or equal to 59'; nightly_hour -1 -&gt; 400 'greater than or equal to 0'; 99 -&gt; 400.</t>
+        </is>
+      </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -3675,14 +3819,22 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>All 10 ge=1 fields set to 0 -&gt; 400 {"error":"Input should be greater than or equal to 1"} each.</t>
+        </is>
+      </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr"/>
-      <c r="M68" s="2" t="inlineStr"/>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -3722,14 +3874,22 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>All 8 ge=0 fields: -1 -&gt; 400 'greater than or equal to 0'; 0 -&gt; 200 each.</t>
+        </is>
+      </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr"/>
-      <c r="M69" s="2" t="inlineStr"/>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -3769,14 +3929,22 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>alert_min_classification 'severe' -&gt; 400 {"error":"Input should be 'noise', 'warning' or 'critical'"}; 'warning' -&gt; 200.</t>
+        </is>
+      </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr"/>
-      <c r="M70" s="2" t="inlineStr"/>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -3816,14 +3984,22 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>nightly_hour 'abc' -&gt; 400 'Input should be a valid integer...'; non-JSON body with JSON content-type -&gt; 400 (Flask HTML); empty body with JSON content-type -&gt; 400. Note: no body AND no Content-Type -&gt; 415 (Flask default), not 400.</t>
+        </is>
+      </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr"/>
-      <c r="M71" s="2" t="inlineStr"/>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -3863,14 +4039,22 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>No reachable LLM. POST /api/settings/test-llm -&gt; 400 {"ok":false,"error":"[Errno 8] nodename nor servname provided, or not known"} (fallback passes). Success path unverified.</t>
+        </is>
+      </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr"/>
-      <c r="M72" s="2" t="inlineStr"/>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -3910,14 +4094,22 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/exclusions -&gt; 200 {items:[{id,container_pattern,enabled,created_at,updated_at}...]} (4 seeded rules).</t>
+        </is>
+      </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr"/>
-      <c r="M73" s="2" t="inlineStr"/>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -3957,14 +4149,22 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>POST {container_pattern:'  test-*  '} -&gt; 201 {container_pattern:'test-*',enabled:true,id,created_at,updated_at}.</t>
+        </is>
+      </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr"/>
-      <c r="M74" s="2" t="inlineStr"/>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4004,14 +4204,22 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>POST 'dup-x' twice: first 201 id 6, second 200 same id 6; list shows exactly one dup-x row.</t>
+        </is>
+      </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr"/>
-      <c r="M75" s="2" t="inlineStr"/>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4051,14 +4259,22 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>'   ' -&gt; 400 'String should have at least 1 character'; {} -&gt; 400 'Field required'; enabled:'maybe' -&gt; 400 'Input should be a valid boolean...'.</t>
+        </is>
+      </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr"/>
-      <c r="M76" s="2" t="inlineStr"/>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -4098,14 +4314,22 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>DELETE /api/exclusions/999999 -&gt; 404 {"error":"rule not found"}; /abc -&gt; 404; deleting real ids 5,6 -&gt; 200 {"deleted":true}.</t>
+        </is>
+      </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr"/>
-      <c r="M77" s="2" t="inlineStr"/>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -4145,14 +4369,22 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/prompts -&gt; 200 items keys [JSON_OUTPUT_GUARD,NIGHTLY_REPORT,NIGHTLY_SYSTEM,SENTINEL_ANALYSIS,SENTINEL_SYSTEM]; each item has key,content,default_content,version,is_default,created_at,updated_at.</t>
+        </is>
+      </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr"/>
-      <c r="M78" s="2" t="inlineStr"/>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -4192,14 +4424,22 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/prompts/JSON_OUTPUT_GUARD {content:'  custom prompt  '} -&gt; 200 content 'custom prompt' (stripped), version 1-&gt;2, is_default false.</t>
+        </is>
+      </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr"/>
-      <c r="M79" s="2" t="inlineStr"/>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -4239,14 +4479,22 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>{content:'  '} on unknown key -&gt; 400 'String should have at least 1 character' (validation before lookup); {} -&gt; 400 'Field required'; '' -&gt; 400.</t>
+        </is>
+      </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr"/>
-      <c r="M80" s="2" t="inlineStr"/>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -4286,14 +4534,22 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/prompts/nope {content:'x'} -&gt; 404 {"error":"prompt not found"}.</t>
+        </is>
+      </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr"/>
-      <c r="M81" s="2" t="inlineStr"/>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -4333,14 +4589,22 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/prompts/JSON_OUTPUT_GUARD/reset -&gt; 200 content==default_content, is_default true, version 2-&gt;3; /nope/reset -&gt; 404 {"error":"prompt not found"}.</t>
+        </is>
+      </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr"/>
-      <c r="M82" s="2" t="inlineStr"/>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -4380,14 +4644,22 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/sentinel/status -&gt; 200 {state:{enabled,runtime_status,started_at,last_error,llm_failure_count,llm_last_failure_at,updated_at}, active_containers:[]}.</t>
+        </is>
+      </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr"/>
-      <c r="M83" s="2" t="inlineStr"/>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -4427,14 +4699,22 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>toggle {enabled:true} -&gt; 200 state.enabled true (runtime_status running); {enabled:false} -&gt; 200 state.enabled false.</t>
+        </is>
+      </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr"/>
-      <c r="M84" s="2" t="inlineStr"/>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -4474,14 +4754,22 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>status enabled false; POST {} -&gt; enabled true; POST {enabled:null} -&gt; enabled false (flipped each time).</t>
+        </is>
+      </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr"/>
-      <c r="M85" s="2" t="inlineStr"/>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -4521,14 +4809,22 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>{enabled:'maybe'} -&gt; 400 {"error":"Input should be a valid boolean, unable to interpret input"}.</t>
+        </is>
+      </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr"/>
-      <c r="M86" s="2" t="inlineStr"/>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -4568,14 +4864,22 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>No docker. {container:'  '} -&gt; 400 'String should have at least 1 character'; {} -&gt; 400 'Field required'; nonexistent and excluded ('portainer') containers -&gt; 500 {error:docker connection error}. Exclusion 400 path needs docker (name resolved via docker first).</t>
+        </is>
+      </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr"/>
-      <c r="M87" s="2" t="inlineStr"/>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -4615,14 +4919,22 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/insights -&gt; 200 {items:[],offset:0,limit:100} (no events in DB).</t>
+        </is>
+      </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="2" t="inlineStr"/>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
@@ -4662,14 +4974,22 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>limit=501 -&gt; 400 'less than or equal to 500'; limit=0 -&gt; 400; offset=-1 -&gt; 400; limit=abc -&gt; 400 valid integer; offset=5&amp;limit=10 -&gt; echoed 5/10.</t>
+        </is>
+      </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="2" t="inlineStr"/>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
@@ -4709,14 +5029,22 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>container=web&amp;classification=critical&amp;start=..&amp;end=.. -&gt; 200 {items:[],offset:0,limit:100}; start=notadate -&gt; 400 'Input should be a valid datetime or date...'; end=notadate -&gt; 400.</t>
+        </is>
+      </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr"/>
-      <c r="M90" s="2" t="inlineStr"/>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
@@ -4756,14 +5084,22 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>sort=id -&gt; 400 {"error":"Input should be 'created_at' or '-created_at'"}; sort=created_at -&gt; 200; sort=-created_at -&gt; 200.</t>
+        </is>
+      </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr"/>
-      <c r="M91" s="2" t="inlineStr"/>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -4803,14 +5139,22 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/reports?limit=5 -&gt; 200 {items,offset:0,limit:5}; item keys id,created_at,period_start,period_end,status,markdown_content,model,prompt_version,error; limit=0 -&gt; 400; limit=501 -&gt; 400.</t>
+        </is>
+      </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr"/>
-      <c r="M92" s="2" t="inlineStr"/>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
@@ -4850,14 +5194,22 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/reports/999999 -&gt; 404 {"error":"report not found"}; GET /api/reports/1 (generated) -&gt; 200 with same fields as ReportItem.</t>
+        </is>
+      </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr"/>
-      <c r="M93" s="2" t="inlineStr"/>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -4897,14 +5249,22 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>No LLM. POST /api/reports/generate -&gt; 201 report object with status 'llm_error', error '[Errno 8] nodename nor servname...', markdown_content fallback template, model llama3, prompt_version 1. Failure path OK; LLM content path unverified.</t>
+        </is>
+      </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr"/>
-      <c r="M94" s="2" t="inlineStr"/>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -4944,14 +5304,22 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>No Telegram creds. POST /api/telegram/test -&gt; 400 {"ok":false,"error":"telegram credentials are not configured"} (fallback passes).</t>
+        </is>
+      </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr"/>
-      <c r="M95" s="2" t="inlineStr"/>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4991,14 +5359,22 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>No Ollama. ?base_url=http://127.0.0.1:9 -&gt; 502 {"ok":false,"error":"could not reach an Ollama server at that base_url"}; no param (stored URL) -&gt; 502 same generic error. Success shape unverified.</t>
+        </is>
+      </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr"/>
-      <c r="M96" s="2" t="inlineStr"/>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5038,14 +5414,22 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>base_url=ftp://x -&gt; 400 {ok:false,error:'base_url must be an http(s) URL'}; file:///etc -&gt; 400 same; with stored llm_base_url cleared to '' -&gt; 400 {ok:false,error:'base_url not configured'} (restored after).</t>
+        </is>
+      </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr"/>
-      <c r="M97" s="2" t="inlineStr"/>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5085,14 +5469,22 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/issues?limit=5 -&gt; 200 JSON list; with seeded row item has all 14 keys (id,event_id,container_name,title,body,status,action,confidence,discussion,telegram_chat_id,telegram_message_id,llm_model,created_at,updated_at); limit=abc -&gt; 500 as documented.</t>
+        </is>
+      </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr"/>
-      <c r="M98" s="2" t="inlineStr"/>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5132,14 +5524,22 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>status=bogus -&gt; 400 {"error":"invalid status"}; open/discussing/rejected/closed -&gt; 200 each.</t>
+        </is>
+      </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr"/>
-      <c r="M99" s="2" t="inlineStr"/>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5179,14 +5579,22 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/issues/999999 -&gt; 404 {"error":"not found"}; GET /api/issues/1 (seeded fixture) -&gt; 200 issue dict.</t>
+        </is>
+      </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr"/>
-      <c r="M100" s="2" t="inlineStr"/>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -5226,14 +5634,22 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>PATCH 999999 -&gt; 404 {"error":"not found"}; on seeded issue: status 'bogus' -&gt; 200 unchanged 'open'; {} -&gt; 200 'open'; 'closed' -&gt; 200 'closed' and appears in ?status=closed.</t>
+        </is>
+      </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr"/>
-      <c r="M101" s="2" t="inlineStr"/>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -5273,14 +5689,22 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>No LLM. try-llm on 999999 -&gt; 404 {"error":"not found"}; on seeded issue with base_url http://127.0.0.1:9/v1 -&gt; 400 {"ok":false,"error":"[Errno 61] Connection refused"}. Success 200 shape unverified.</t>
+        </is>
+      </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr"/>
-      <c r="M102" s="2" t="inlineStr"/>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -5320,14 +5744,22 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>On seeded issue: {prompt:'  '} -&gt; 400 {"error":"prompt is required"}; {} -&gt; 400 same; non-JSON body -&gt; 400 same.</t>
+        </is>
+      </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr"/>
-      <c r="M103" s="2" t="inlineStr"/>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -5367,14 +5799,22 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>On seeded issue: {prompt:'x',base_url:'ftp://evil'} -&gt; 400 {"error":"base_url must be an http(s) URL"}. api_key-stripping on foreign base_url confirmed by code read (issues.py:120-122) only.</t>
+        </is>
+      </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr"/>
-      <c r="M104" s="2" t="inlineStr"/>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -5414,14 +5854,22 @@
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/nope -&gt; 404; DELETE /api/settings -&gt; 405.</t>
+        </is>
+      </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr"/>
-      <c r="M105" s="2" t="inlineStr"/>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -5461,14 +5909,26 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
-      <c r="J106" s="2" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>GET/PUT /api/settings include updated_at and PUT bumps it (20:17:53 -&gt; 20:18:05 after later PUT). But value is RFC 1123 HTTP-date 'Sat, 15 Aug 2026 20:18:05 GMT', not ISO 8601.</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr">
+        <is>
+          <t>Expected ISO datetime string; observed 'Sat, 15 Aug 2026 20:18:05 GMT'. Cause: SettingsSchema.model_dump() (app/schemas/settings.py:74) yields datetime, and Flask default JSON provider (no custom provider in app/__init__.py) serializes datetimes as HTTP-date. Same format on all other endpoints. Minor severity.</t>
+        </is>
+      </c>
       <c r="K106" s="2" t="inlineStr"/>
       <c r="L106" s="2" t="inlineStr"/>
-      <c r="M106" s="2" t="inlineStr"/>
+      <c r="M106" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -5508,14 +5968,26 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr"/>
-      <c r="J107" s="2" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>create_app() config: SESSION_COOKIE_SAMESITE=None, SESSION_COOKIE_HTTPONLY=True, BASIC_AUTH_ENABLED=True with env vars set / False without.</t>
+        </is>
+      </c>
+      <c r="J107" s="2" t="inlineStr">
+        <is>
+          <t>Expected SESSION_COOKIE_SAMESITE='Lax'; observed None. app/security.py:86 uses app.config.setdefault('SESSION_COOKIE_SAMESITE','Lax') but Flask's default config already defines that key as None, so setdefault is a no-op. HTTPONLY and BASIC_AUTH_ENABLED are correct.</t>
+        </is>
+      </c>
       <c r="K107" s="2" t="inlineStr"/>
       <c r="L107" s="2" t="inlineStr"/>
-      <c r="M107" s="2" t="inlineStr"/>
+      <c r="M107" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -7059,14 +7531,30 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I140" s="2" t="inlineStr"/>
-      <c r="J140" s="2" t="inlineStr"/>
-      <c r="K140" s="2" t="inlineStr"/>
+          <t>Fixed - retest</t>
+        </is>
+      </c>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>Live call to Qwen server → HTTP 400 'System message must be at the beginning' because sentinel sends 2 system messages (system + JSON guard). Same in telegram_bot._ask_llm.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr">
+        <is>
+          <t>sentinel.py process_chunk messages had two role=system entries; chat-template servers (mlx/llama.cpp/vLLM) reject.</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>commit: guard appended to the single system message; bot merged too</t>
+        </is>
+      </c>
       <c r="L140" s="2" t="inlineStr"/>
-      <c r="M140" s="2" t="inlineStr"/>
+      <c r="M140" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
@@ -7999,14 +8487,30 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I160" s="2" t="inlineStr"/>
-      <c r="J160" s="2" t="inlineStr"/>
-      <c r="K160" s="2" t="inlineStr"/>
+          <t>Fixed - retest</t>
+        </is>
+      </c>
+      <c r="I160" s="2" t="inlineStr">
+        <is>
+          <t>Live call to keyless OpenAI-compatible server (Qwen @10.0.0.79) failed before any HTTP: httpx 'Illegal header value b"Bearer "'.</t>
+        </is>
+      </c>
+      <c r="J160" s="2" t="inlineStr">
+        <is>
+          <t>llm_client.chat_completion always sent Authorization: Bearer &lt;key&gt;; blank key → illegal header → every call errors. Also 4xx errors surfaced as bare '400 Bad Request' hiding server message.</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>commit: omit Authorization when key blank; include server error detail</t>
+        </is>
+      </c>
       <c r="L160" s="2" t="inlineStr"/>
-      <c r="M160" s="2" t="inlineStr"/>
+      <c r="M160" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
@@ -11430,14 +11934,26 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I233" s="2" t="inlineStr"/>
-      <c r="J233" s="2" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Followed README local-dev steps on a fresh clone: `flask --app app run` crashed with 'no such table: schema_version' — create_all only runs under TESTING; alembic must be run first but the README only mentions it 'after dependency changes'.</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>README.md:244-250 order/wording; app/__init__.py:70-72 (create_all gated on TESTING). Expected: first-run works or README says run `alembic upgrade head` BEFORE first `flask run`.</t>
+        </is>
+      </c>
       <c r="K233" s="2" t="inlineStr"/>
       <c r="L233" s="2" t="inlineStr"/>
-      <c r="M233" s="2" t="inlineStr"/>
+      <c r="M233" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="inlineStr">

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -5909,7 +5909,7 @@
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5922,7 +5922,11 @@
           <t>Expected ISO datetime string; observed 'Sat, 15 Aug 2026 20:18:05 GMT'. Cause: SettingsSchema.model_dump() (app/schemas/settings.py:74) yields datetime, and Flask default JSON provider (no custom provider in app/__init__.py) serializes datetimes as HTTP-date. Same format on all other endpoints. Minor severity.</t>
         </is>
       </c>
-      <c r="K106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>__init__.py: ISOJSONProvider — datetimes serialised ISO-8601</t>
+        </is>
+      </c>
       <c r="L106" s="2" t="inlineStr"/>
       <c r="M106" s="2" t="inlineStr">
         <is>
@@ -5968,7 +5972,7 @@
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5981,7 +5985,11 @@
           <t>Expected SESSION_COOKIE_SAMESITE='Lax'; observed None. app/security.py:86 uses app.config.setdefault('SESSION_COOKIE_SAMESITE','Lax') but Flask's default config already defines that key as None, so setdefault is a no-op. HTTPONLY and BASIC_AUTH_ENABLED are correct.</t>
         </is>
       </c>
-      <c r="K107" s="2" t="inlineStr"/>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>security.py: explicit set (Flask predefines key as None so setdefault was a no-op)</t>
+        </is>
+      </c>
       <c r="L107" s="2" t="inlineStr"/>
       <c r="M107" s="2" t="inlineStr">
         <is>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -6035,14 +6035,22 @@
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>start() twice: stop() invoked once on restart, fresh Events, from_env twice, daemon threads named docker-events/docker-reconcile, reconcile ran once synchronously</t>
+        </is>
+      </c>
       <c r="J108" s="2" t="inlineStr"/>
       <c r="K108" s="2" t="inlineStr"/>
       <c r="L108" s="2" t="inlineStr"/>
-      <c r="M108" s="2" t="inlineStr"/>
+      <c r="M108" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6082,14 +6090,22 @@
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>stop(): stop_event+reconcile_now set, workers popped+joined, client closed (error swallowed) &amp; nulled, threads joined &amp; nulled, active_container_ids()==[]</t>
+        </is>
+      </c>
       <c r="J109" s="2" t="inlineStr"/>
       <c r="K109" s="2" t="inlineStr"/>
       <c r="L109" s="2" t="inlineStr"/>
-      <c r="M109" s="2" t="inlineStr"/>
+      <c r="M109" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6129,14 +6145,22 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>start/restart-&gt;attach, die/destroy/stop-&gt;detach, non-container &amp; id-less ignored, stream exception swallowed</t>
+        </is>
+      </c>
       <c r="J110" s="2" t="inlineStr"/>
       <c r="K110" s="2" t="inlineStr"/>
       <c r="L110" s="2" t="inlineStr"/>
-      <c r="M110" s="2" t="inlineStr"/>
+      <c r="M110" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6176,14 +6200,22 @@
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>existing tests pass; extra: name fallback id[:12], exitCode int coercion + raw fallback, attrs copied, non-listed status ignored</t>
+        </is>
+      </c>
       <c r="J111" s="2" t="inlineStr"/>
       <c r="K111" s="2" t="inlineStr"/>
       <c r="L111" s="2" t="inlineStr"/>
-      <c r="M111" s="2" t="inlineStr"/>
+      <c r="M111" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6223,14 +6255,22 @@
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>force_reconcile wakes loop, event cleared, periodic ticks (5 in ~0.3s @0.05s), exits on stop_event</t>
+        </is>
+      </c>
       <c r="J112" s="2" t="inlineStr"/>
       <c r="K112" s="2" t="inlineStr"/>
       <c r="L112" s="2" t="inlineStr"/>
-      <c r="M112" s="2" t="inlineStr"/>
+      <c r="M112" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6270,14 +6310,22 @@
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>excluded names filtered, desired-active attached, active-desired detached (name None), no-op when client None</t>
+        </is>
+      </c>
       <c r="J113" s="2" t="inlineStr"/>
       <c r="K113" s="2" t="inlineStr"/>
       <c r="L113" s="2" t="inlineStr"/>
-      <c r="M113" s="2" t="inlineStr"/>
+      <c r="M113" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6317,14 +6365,22 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>double attach -&gt; one worker; excluded name -&gt; none; containers.get error -&gt; none; thread named log-tail-&lt;name&gt;, daemon</t>
+        </is>
+      </c>
       <c r="J114" s="2" t="inlineStr"/>
       <c r="K114" s="2" t="inlineStr"/>
       <c r="L114" s="2" t="inlineStr"/>
-      <c r="M114" s="2" t="inlineStr"/>
+      <c r="M114" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6364,14 +6420,22 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>detach pops worker, sets stop_flag, joins, callback(id, name-or-stored, '', True); unknown id no-op</t>
+        </is>
+      </c>
       <c r="J115" s="2" t="inlineStr"/>
       <c r="K115" s="2" t="inlineStr"/>
       <c r="L115" s="2" t="inlineStr"/>
-      <c r="M115" s="2" t="inlineStr"/>
+      <c r="M115" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6411,14 +6475,22 @@
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>backoff 1,2,4,8,16,30,30; logs(stream,follow,stdout,stderr,since); empty lines skipped; clean end breaks; not-running exits</t>
+        </is>
+      </c>
       <c r="J116" s="2" t="inlineStr"/>
       <c r="K116" s="2" t="inlineStr"/>
       <c r="L116" s="2" t="inlineStr"/>
-      <c r="M116" s="2" t="inlineStr"/>
+      <c r="M116" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6458,14 +6530,22 @@
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_docker_watcher.py::test_line_callback_exception_does_not_kill_stream passes: callback raising on 'boom' is logged, 'one','two' still delivered, single logs() call (no reconnect).</t>
+        </is>
+      </c>
       <c r="J117" s="2" t="inlineStr"/>
       <c r="K117" s="2" t="inlineStr"/>
       <c r="L117" s="2" t="inlineStr"/>
-      <c r="M117" s="2" t="inlineStr"/>
+      <c r="M117" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6505,14 +6585,22 @@
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>existing tests pass; extra: worker kept when stop_flag differs; final-flush callback error swallowed; errored -&gt; reconcile_now</t>
+        </is>
+      </c>
       <c r="J118" s="2" t="inlineStr"/>
       <c r="K118" s="2" t="inlineStr"/>
       <c r="L118" s="2" t="inlineStr"/>
-      <c r="M118" s="2" t="inlineStr"/>
+      <c r="M118" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6552,14 +6640,22 @@
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I119" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I119" s="2" t="inlineStr">
+        <is>
+          <t>test passes; patterns confirmed incl. edge cases</t>
+        </is>
+      </c>
       <c r="J119" s="2" t="inlineStr"/>
       <c r="K119" s="2" t="inlineStr"/>
       <c r="L119" s="2" t="inlineStr"/>
-      <c r="M119" s="2" t="inlineStr"/>
+      <c r="M119" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
@@ -6599,14 +6695,22 @@
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I120" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I120" s="2" t="inlineStr">
+        <is>
+          <t>default 15s; SentinelService uses default; elapsed&gt;=15 flushes old buffer as own chunk, new state starts; 14.9s does not</t>
+        </is>
+      </c>
       <c r="J120" s="2" t="inlineStr"/>
       <c r="K120" s="2" t="inlineStr"/>
       <c r="L120" s="2" t="inlineStr"/>
-      <c r="M120" s="2" t="inlineStr"/>
+      <c r="M120" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -6646,14 +6750,22 @@
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I121" s="2" t="inlineStr">
+        <is>
+          <t>existing tests pass; keyword_hit re-primes and resets lines_since_keyword; flush at delay lines</t>
+        </is>
+      </c>
       <c r="J121" s="2" t="inlineStr"/>
       <c r="K121" s="2" t="inlineStr"/>
       <c r="L121" s="2" t="inlineStr"/>
-      <c r="M121" s="2" t="inlineStr"/>
+      <c r="M121" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -6693,14 +6805,22 @@
       </c>
       <c r="H122" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>3 named tests pass: python traceback &amp; java trace (at/Caused by/... lines) never count toward delay, flush only on next normal line; delay 0 flushes on keyword line.</t>
+        </is>
+      </c>
       <c r="J122" s="2" t="inlineStr"/>
       <c r="K122" s="2" t="inlineStr"/>
       <c r="L122" s="2" t="inlineStr"/>
-      <c r="M122" s="2" t="inlineStr"/>
+      <c r="M122" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6740,14 +6860,22 @@
       </c>
       <c r="H123" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>existing tests pass; chars&gt;=max flushes even on continuation line while primed</t>
+        </is>
+      </c>
       <c r="J123" s="2" t="inlineStr"/>
       <c r="K123" s="2" t="inlineStr"/>
       <c r="L123" s="2" t="inlineStr"/>
-      <c r="M123" s="2" t="inlineStr"/>
+      <c r="M123" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6787,14 +6915,22 @@
       </c>
       <c r="H124" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>chars=ceil(len/4) min1; tiktoken unknown model/empty model -&gt; char fallback; gpt-4o uses tiktoken, cached, incremental running estimate</t>
+        </is>
+      </c>
       <c r="J124" s="2" t="inlineStr"/>
       <c r="K124" s="2" t="inlineStr"/>
       <c r="L124" s="2" t="inlineStr"/>
-      <c r="M124" s="2" t="inlineStr"/>
+      <c r="M124" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -6834,14 +6970,22 @@
       </c>
       <c r="H125" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I125" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I125" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_log_buffer.py::test_flush_pops_state_and_drop_container_discards passes: flush returns chunk &amp; pops state, second flush None, drop_container discards without chunk. BufferChunk fields verified in PIPE-17/29.</t>
+        </is>
+      </c>
       <c r="J125" s="2" t="inlineStr"/>
       <c r="K125" s="2" t="inlineStr"/>
       <c r="L125" s="2" t="inlineStr"/>
-      <c r="M125" s="2" t="inlineStr"/>
+      <c r="M125" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -6881,14 +7025,22 @@
       </c>
       <c r="H126" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I126" s="2" t="inlineStr">
+        <is>
+          <t>primed flushes at &gt;=15s, others at &gt;=30s, empty states dropped</t>
+        </is>
+      </c>
       <c r="J126" s="2" t="inlineStr"/>
       <c r="K126" s="2" t="inlineStr"/>
       <c r="L126" s="2" t="inlineStr"/>
-      <c r="M126" s="2" t="inlineStr"/>
+      <c r="M126" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -6928,14 +7080,22 @@
       </c>
       <c r="H127" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I127" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; _sync_buffer_limits applies all 6 Settings values on handle_log_line</t>
+        </is>
+      </c>
       <c r="J127" s="2" t="inlineStr"/>
       <c r="K127" s="2" t="inlineStr"/>
       <c r="L127" s="2" t="inlineStr"/>
-      <c r="M127" s="2" t="inlineStr"/>
+      <c r="M127" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
@@ -6975,14 +7135,22 @@
       </c>
       <c r="H128" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I128" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I128" s="2" t="inlineStr">
+        <is>
+          <t>keywords lowercased/stripped, empties dropped, configured order preserved, \b boundaries</t>
+        </is>
+      </c>
       <c r="J128" s="2" t="inlineStr"/>
       <c r="K128" s="2" t="inlineStr"/>
       <c r="L128" s="2" t="inlineStr"/>
-      <c r="M128" s="2" t="inlineStr"/>
+      <c r="M128" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
@@ -7022,14 +7190,22 @@
       </c>
       <c r="H129" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I129" s="2" t="inlineStr">
+        <is>
+          <t>phrase pattern joins with \s+; whitespace variants match, single words don't</t>
+        </is>
+      </c>
       <c r="J129" s="2" t="inlineStr"/>
       <c r="K129" s="2" t="inlineStr"/>
       <c r="L129" s="2" t="inlineStr"/>
-      <c r="M129" s="2" t="inlineStr"/>
+      <c r="M129" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
@@ -7069,14 +7245,22 @@
       </c>
       <c r="H130" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I130" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I130" s="2" t="inlineStr">
+        <is>
+          <t>benign JSON (0/false/null, case-insens, spaces) suppresses; mixed still hits</t>
+        </is>
+      </c>
       <c r="J130" s="2" t="inlineStr"/>
       <c r="K130" s="2" t="inlineStr"/>
       <c r="L130" s="2" t="inlineStr"/>
-      <c r="M130" s="2" t="inlineStr"/>
+      <c r="M130" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
@@ -7116,14 +7300,22 @@
       </c>
       <c r="H131" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I131" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I131" s="2" t="inlineStr">
+        <is>
+          <t>DEFAULT_KEYWORD_LIST exact match; sentinel splits Settings.keyword_list on commas per call (source read)</t>
+        </is>
+      </c>
       <c r="J131" s="2" t="inlineStr"/>
       <c r="K131" s="2" t="inlineStr"/>
       <c r="L131" s="2" t="inlineStr"/>
-      <c r="M131" s="2" t="inlineStr"/>
+      <c r="M131" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -7163,14 +7355,22 @@
       </c>
       <c r="H132" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I132" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I132" s="2" t="inlineStr">
+        <is>
+          <t>window&lt;=0 no-op; timer reset per chunk (fired once ~1s after last, batch ['x','y'] in app_context); cb exception swallowed; flush_all cancels timers &amp; flushes sync; pending_count sums</t>
+        </is>
+      </c>
       <c r="J132" s="2" t="inlineStr"/>
       <c r="K132" s="2" t="inlineStr"/>
       <c r="L132" s="2" t="inlineStr"/>
-      <c r="M132" s="2" t="inlineStr"/>
+      <c r="M132" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
@@ -7210,14 +7410,22 @@
       </c>
       <c r="H133" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I133" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I133" s="2" t="inlineStr">
+        <is>
+          <t>disabled -&gt; no-op; case-insens substring exclusion (enabled only) -&gt; one 'excluded' event per container per 5 min, then return</t>
+        </is>
+      </c>
       <c r="J133" s="2" t="inlineStr"/>
       <c r="K133" s="2" t="inlineStr"/>
       <c r="L133" s="2" t="inlineStr"/>
-      <c r="M133" s="2" t="inlineStr"/>
+      <c r="M133" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
@@ -7257,14 +7465,22 @@
       </c>
       <c r="H134" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I134" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I134" s="2" t="inlineStr">
+        <is>
+          <t>flush_only flushes buffered text -&gt; process_chunk ('skipped' for no keywords); line arg ignored; empty buffer no-op</t>
+        </is>
+      </c>
       <c r="J134" s="2" t="inlineStr"/>
       <c r="K134" s="2" t="inlineStr"/>
       <c r="L134" s="2" t="inlineStr"/>
-      <c r="M134" s="2" t="inlineStr"/>
+      <c r="M134" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
@@ -7304,14 +7520,22 @@
       </c>
       <c r="H135" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I135" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I135" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; handle_log_line: prefilter -&gt; add_line(keyword_hit) -&gt; chunk -&gt; process_chunk analyzed</t>
+        </is>
+      </c>
       <c r="J135" s="2" t="inlineStr"/>
       <c r="K135" s="2" t="inlineStr"/>
       <c r="L135" s="2" t="inlineStr"/>
-      <c r="M135" s="2" t="inlineStr"/>
+      <c r="M135" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
@@ -7351,14 +7575,22 @@
       </c>
       <c r="H136" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I136" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I136" s="2" t="inlineStr">
+        <is>
+          <t>no keyword -&gt; skipped/noise persisted with sha256 hash, 1200-char excerpt, input_chars, tokens; no LLM call</t>
+        </is>
+      </c>
       <c r="J136" s="2" t="inlineStr"/>
       <c r="K136" s="2" t="inlineStr"/>
       <c r="L136" s="2" t="inlineStr"/>
-      <c r="M136" s="2" t="inlineStr"/>
+      <c r="M136" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
@@ -7398,14 +7630,22 @@
       </c>
       <c r="H137" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I137" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>test passes; default 300; dedup crosses containers by hash; outside window not deduped</t>
+        </is>
+      </c>
       <c r="J137" s="2" t="inlineStr"/>
       <c r="K137" s="2" t="inlineStr"/>
       <c r="L137" s="2" t="inlineStr"/>
-      <c r="M137" s="2" t="inlineStr"/>
+      <c r="M137" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
@@ -7445,14 +7685,22 @@
       </c>
       <c r="H138" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>test passes; defaults 10/3600; counts analyzed+parse_error+llm_error only; per container; window respected</t>
+        </is>
+      </c>
       <c r="J138" s="2" t="inlineStr"/>
       <c r="K138" s="2" t="inlineStr"/>
       <c r="L138" s="2" t="inlineStr"/>
-      <c r="M138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
@@ -7492,14 +7740,22 @@
       </c>
       <c r="H139" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I139" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>default 0=off; window&gt;0 -&gt; enqueue + 'queued'/noise; coalesce=False bypasses; flush_coalesced joins with separator, trims to last max_input_chars, prefixes header, coalesce=False</t>
+        </is>
+      </c>
       <c r="J139" s="2" t="inlineStr"/>
       <c r="K139" s="2" t="inlineStr"/>
       <c r="L139" s="2" t="inlineStr"/>
-      <c r="M139" s="2" t="inlineStr"/>
+      <c r="M139" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
@@ -7524,7 +7780,7 @@
       </c>
       <c r="E140" s="2" t="inlineStr">
         <is>
-          <t>messages = [system SENTINEL_SYSTEM, system JSON_OUTPUT_GUARD, user: SENTINEL_ANALYSIS + '=== CONTAINER ===' + name + '=== LOGS ===' warning text + '&lt;logs&gt;...&lt;/logs&gt;']. Missing prompt template raises RuntimeError. max_tokens=reserved_output_tokens (default 600).</t>
+          <t>messages = [system: SENTINEL_SYSTEM + '\n\n' + JSON_OUTPUT_GUARD (ONE system message — chat-template servers reject a second), user: SENTINEL_ANALYSIS + '=== CONTAINER ===' + name + '=== LOGS ===' warning + '&lt;logs&gt;...&lt;/logs&gt;']. Missing template raises RuntimeError. max_tokens=reserved_output_tokens (default 600).</t>
         </is>
       </c>
       <c r="F140" s="2" t="inlineStr">
@@ -7539,25 +7795,25 @@
       </c>
       <c r="H140" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I140" s="2" t="inlineStr">
         <is>
-          <t>Live call to Qwen server → HTTP 400 'System message must be at the beginning' because sentinel sends 2 system messages (system + JSON guard). Same in telegram_bot._ask_llm.</t>
-        </is>
-      </c>
-      <c r="J140" s="2" t="inlineStr">
-        <is>
-          <t>sentinel.py process_chunk messages had two role=system entries; chat-template servers (mlx/llama.cpp/vLLM) reject.</t>
-        </is>
-      </c>
+          <t>Now [system(SENTINEL_SYSTEM+guard), user]; verified live against Qwen server. Story expectation updated to single system message.</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
       <c r="K140" s="2" t="inlineStr">
         <is>
           <t>commit: guard appended to the single system message; bot merged too</t>
         </is>
       </c>
-      <c r="L140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="M140" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -7602,14 +7858,22 @@
       </c>
       <c r="H141" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I141" s="2" t="inlineStr">
+        <is>
+          <t>llm exception -&gt; llm_error event committed; failure_count+1, last_failure_at, last_error, runtime degraded</t>
+        </is>
+      </c>
       <c r="J141" s="2" t="inlineStr"/>
       <c r="K141" s="2" t="inlineStr"/>
       <c r="L141" s="2" t="inlineStr"/>
-      <c r="M141" s="2" t="inlineStr"/>
+      <c r="M141" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
@@ -7649,14 +7913,22 @@
       </c>
       <c r="H142" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I142" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>test passes; parse_error stores model/latency/prompt_version; degraded with 'unparseable LLM reply: ' + &lt;=300 chars</t>
+        </is>
+      </c>
       <c r="J142" s="2" t="inlineStr"/>
       <c r="K142" s="2" t="inlineStr"/>
       <c r="L142" s="2" t="inlineStr"/>
-      <c r="M142" s="2" t="inlineStr"/>
+      <c r="M142" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -7696,14 +7968,22 @@
       </c>
       <c r="H143" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I143" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; ranks noise0/warning1/critical2, default 'critical'; keyboard has event id; alert gating by threshold; runtime running</t>
+        </is>
+      </c>
       <c r="J143" s="2" t="inlineStr"/>
       <c r="K143" s="2" t="inlineStr"/>
       <c r="L143" s="2" t="inlineStr"/>
-      <c r="M143" s="2" t="inlineStr"/>
+      <c r="M143" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -7743,14 +8023,22 @@
       </c>
       <c r="H144" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I144" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I144" s="2" t="inlineStr">
+        <is>
+          <t>successful analysis clears degraded -&gt; running/last_error None; no-op when disabled</t>
+        </is>
+      </c>
       <c r="J144" s="2" t="inlineStr"/>
       <c r="K144" s="2" t="inlineStr"/>
       <c r="L144" s="2" t="inlineStr"/>
-      <c r="M144" s="2" t="inlineStr"/>
+      <c r="M144" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
@@ -7790,14 +8078,22 @@
       </c>
       <c r="H145" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I145" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I145" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; full classification matrix incl. 143/139/None/kill w/o signal verified</t>
+        </is>
+      </c>
       <c r="J145" s="2" t="inlineStr"/>
       <c r="K145" s="2" t="inlineStr"/>
       <c r="L145" s="2" t="inlineStr"/>
-      <c r="M145" s="2" t="inlineStr"/>
+      <c r="M145" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
@@ -7837,14 +8133,22 @@
       </c>
       <c r="H146" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I146" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I146" s="2" t="inlineStr">
+        <is>
+          <t>tests pass (threshold, cooldown suppression msg, window, global rate limit); defaults 3/10min/10min confirmed</t>
+        </is>
+      </c>
       <c r="J146" s="2" t="inlineStr"/>
       <c r="K146" s="2" t="inlineStr"/>
       <c r="L146" s="2" t="inlineStr"/>
-      <c r="M146" s="2" t="inlineStr"/>
+      <c r="M146" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
@@ -7884,14 +8188,22 @@
       </c>
       <c r="H147" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I147" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; logs(tail=200,stdout,stderr); empty -&gt; placeholder text; trimmed to last max_input_chars; client closed; coalesce bypassed</t>
+        </is>
+      </c>
       <c r="J147" s="2" t="inlineStr"/>
       <c r="K147" s="2" t="inlineStr"/>
       <c r="L147" s="2" t="inlineStr"/>
-      <c r="M147" s="2" t="inlineStr"/>
+      <c r="M147" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
@@ -7931,14 +8243,22 @@
       </c>
       <c r="H148" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I148" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; excluded (by buffered name) skipped; name falls back to id; returns processed count</t>
+        </is>
+      </c>
       <c r="J148" s="2" t="inlineStr"/>
       <c r="K148" s="2" t="inlineStr"/>
       <c r="L148" s="2" t="inlineStr"/>
-      <c r="M148" s="2" t="inlineStr"/>
+      <c r="M148" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
@@ -7978,14 +8298,22 @@
       </c>
       <c r="H149" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I149" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I149" s="2" t="inlineStr">
+        <is>
+          <t>defaults enabled False/stopped/0; set_enabled True-&gt;running+started_at; False-&gt;stopped+None; degraded sets last_error</t>
+        </is>
+      </c>
       <c r="J149" s="2" t="inlineStr"/>
       <c r="K149" s="2" t="inlineStr"/>
       <c r="L149" s="2" t="inlineStr"/>
-      <c r="M149" s="2" t="inlineStr"/>
+      <c r="M149" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
@@ -8025,14 +8353,22 @@
       </c>
       <c r="H150" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I150" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>4 tests pass (same container+classification suppressed w/ exact message; cross-container/expired not; unsent ignored); default 10</t>
+        </is>
+      </c>
       <c r="J150" s="2" t="inlineStr"/>
       <c r="K150" s="2" t="inlineStr"/>
       <c r="L150" s="2" t="inlineStr"/>
-      <c r="M150" s="2" t="inlineStr"/>
+      <c r="M150" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
@@ -8072,14 +8408,22 @@
       </c>
       <c r="H151" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I151" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I151" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; constant 24h; message 'suppressed: recently rejected'</t>
+        </is>
+      </c>
       <c r="J151" s="2" t="inlineStr"/>
       <c r="K151" s="2" t="inlineStr"/>
       <c r="L151" s="2" t="inlineStr"/>
-      <c r="M151" s="2" t="inlineStr"/>
+      <c r="M151" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
@@ -8119,14 +8463,22 @@
       </c>
       <c r="H152" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I152" s="2" t="inlineStr">
+        <is>
+          <t>tests pass (maybe_send + send_plain paths); defaults 20/300s</t>
+        </is>
+      </c>
       <c r="J152" s="2" t="inlineStr"/>
       <c r="K152" s="2" t="inlineStr"/>
       <c r="L152" s="2" t="inlineStr"/>
-      <c r="M152" s="2" t="inlineStr"/>
+      <c r="M152" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
@@ -8166,14 +8518,22 @@
       </c>
       <c r="H153" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I153" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>layout matches: header/sep/summary/ROOT CAUSE/SUGGESTED FIX/LOG EXCERPT last5 trunc160(157+...)/Confidence/Event ID/Dashboard urlencoded; default CRITICAL</t>
+        </is>
+      </c>
       <c r="J153" s="2" t="inlineStr"/>
       <c r="K153" s="2" t="inlineStr"/>
       <c r="L153" s="2" t="inlineStr"/>
-      <c r="M153" s="2" t="inlineStr"/>
+      <c r="M153" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -8213,14 +8573,22 @@
       </c>
       <c r="H154" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I154" s="2" t="inlineStr">
+        <is>
+          <t>keyboard exact; None for None id; passed as reply_markup to strategy.send</t>
+        </is>
+      </c>
       <c r="J154" s="2" t="inlineStr"/>
       <c r="K154" s="2" t="inlineStr"/>
       <c r="L154" s="2" t="inlineStr"/>
-      <c r="M154" s="2" t="inlineStr"/>
+      <c r="M154" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
@@ -8260,14 +8628,22 @@
       </c>
       <c r="H155" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I155" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I155" s="2" t="inlineStr">
+        <is>
+          <t>send_plain: rate-limit only, reply_markup None; strategy delegates token/chat from config; empty creds -&gt; credentials error tuple</t>
+        </is>
+      </c>
       <c r="J155" s="2" t="inlineStr"/>
       <c r="K155" s="2" t="inlineStr"/>
       <c r="L155" s="2" t="inlineStr"/>
-      <c r="M155" s="2" t="inlineStr"/>
+      <c r="M155" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
@@ -8307,14 +8683,22 @@
       </c>
       <c r="H156" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I156" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I156" s="2" t="inlineStr">
+        <is>
+          <t>schema enforces classification set (lowercased), required fields, confidence [0,1]; safe_parse returns (None, msg) for JSON/Validation/Type errors; dict payload ok</t>
+        </is>
+      </c>
       <c r="J156" s="2" t="inlineStr"/>
       <c r="K156" s="2" t="inlineStr"/>
       <c r="L156" s="2" t="inlineStr"/>
-      <c r="M156" s="2" t="inlineStr"/>
+      <c r="M156" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
@@ -8354,14 +8738,22 @@
       </c>
       <c r="H157" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I157" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I157" s="2" t="inlineStr">
+        <is>
+          <t>test passes; fence strip, outermost balanced object string/escape aware, passthrough w/o '{'</t>
+        </is>
+      </c>
       <c r="J157" s="2" t="inlineStr"/>
       <c r="K157" s="2" t="inlineStr"/>
       <c r="L157" s="2" t="inlineStr"/>
-      <c r="M157" s="2" t="inlineStr"/>
+      <c r="M157" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
@@ -8401,14 +8793,22 @@
       </c>
       <c r="H158" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I158" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I158" s="2" t="inlineStr">
+        <is>
+          <t>cli-&gt;cli_* (defaults 120/1), else llm_* (20/2); temperature only when given; complete() preferred, chat_completion fallback drops transport/cli_backend; LLMClient.complete dispatches cli</t>
+        </is>
+      </c>
       <c r="J158" s="2" t="inlineStr"/>
       <c r="K158" s="2" t="inlineStr"/>
       <c r="L158" s="2" t="inlineStr"/>
-      <c r="M158" s="2" t="inlineStr"/>
+      <c r="M158" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
@@ -8448,14 +8848,22 @@
       </c>
       <c r="H159" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I159" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I159" s="2" t="inlineStr">
+        <is>
+          <t>3 named tests pass: response_format json_object sent for host.docker.internal:11434 + 'JSON' prompt, dropped after 400 mentioning response_format and not resent; markdown prompt -&gt; no json mode; heuristic host/model prefixes.</t>
+        </is>
+      </c>
       <c r="J159" s="2" t="inlineStr"/>
       <c r="K159" s="2" t="inlineStr"/>
       <c r="L159" s="2" t="inlineStr"/>
-      <c r="M159" s="2" t="inlineStr"/>
+      <c r="M159" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
@@ -8495,12 +8903,12 @@
       </c>
       <c r="H160" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Live call to keyless OpenAI-compatible server (Qwen @10.0.0.79) failed before any HTTP: httpx 'Illegal header value b"Bearer "'.</t>
+          <t>test_llm_client_retries passes + snippet: 500/429/malformed-JSON retried with sleeps 0.5,1,2; POST &lt;base&gt;/chat/completions, temperature 0.1, max_tokens; RuntimeError after retries; LLMResult fields. Note (13:20 edit): Bearer header only sent when api_key non-empty; 4xx now RuntimeError w/ detail.</t>
         </is>
       </c>
       <c r="J160" s="2" t="inlineStr">
@@ -8558,14 +8966,22 @@
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I161" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I161" s="2" t="inlineStr">
+        <is>
+          <t>header lines + ROLE:\ncontent sections joined by blank lines; RuntimeError without cli_runner; model label cli:&lt;backend&gt;, usage {} (checked in PIPE-51)</t>
+        </is>
+      </c>
       <c r="J161" s="2" t="inlineStr"/>
       <c r="K161" s="2" t="inlineStr"/>
       <c r="L161" s="2" t="inlineStr"/>
-      <c r="M161" s="2" t="inlineStr"/>
+      <c r="M161" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -8605,14 +9021,22 @@
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I162" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>name regex, missing/non-exec RuntimeErrors; nonzero exit -&gt; stderr/stdout/generic msg; empty output msg; retries+1 attempts; DOCKSENTINEL_BACKEND env; content stripped</t>
+        </is>
+      </c>
       <c r="J162" s="2" t="inlineStr"/>
       <c r="K162" s="2" t="inlineStr"/>
       <c r="L162" s="2" t="inlineStr"/>
-      <c r="M162" s="2" t="inlineStr"/>
+      <c r="M162" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -8652,14 +9076,22 @@
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I163" s="2" t="inlineStr">
+        <is>
+          <t>test passes + snippet: BoundedSemaphore(max(1,n)); busy lock -&gt; RuntimeError 'cli backend call queue timeout (single-call lock busy)', each attempt waits timeout+5s (2 attempts=12.0s); composition.py uses max_concurrent_calls=1.</t>
+        </is>
+      </c>
       <c r="J163" s="2" t="inlineStr"/>
       <c r="K163" s="2" t="inlineStr"/>
       <c r="L163" s="2" t="inlineStr"/>
-      <c r="M163" s="2" t="inlineStr"/>
+      <c r="M163" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
@@ -8699,14 +9131,22 @@
       </c>
       <c r="H164" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I164" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; PATH default /usr/local/bin:/usr/bin:/bin; prefixes &amp; exact names pass; secrets dropped</t>
+        </is>
+      </c>
       <c r="J164" s="2" t="inlineStr"/>
       <c r="K164" s="2" t="inlineStr"/>
       <c r="L164" s="2" t="inlineStr"/>
-      <c r="M164" s="2" t="inlineStr"/>
+      <c r="M164" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -8746,14 +9186,22 @@
       </c>
       <c r="H165" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I165" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I165" s="2" t="inlineStr">
+        <is>
+          <t>test passes; timeout msg exact, timeout 0 -&gt; 1s, retried per max_retries (2.0s), killpg/start_new_session/wait(5) in source</t>
+        </is>
+      </c>
       <c r="J165" s="2" t="inlineStr"/>
       <c r="K165" s="2" t="inlineStr"/>
       <c r="L165" s="2" t="inlineStr"/>
-      <c r="M165" s="2" t="inlineStr"/>
+      <c r="M165" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
@@ -8793,14 +9241,22 @@
       </c>
       <c r="H166" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; 24h window; 300 crit/warn + fill to 500 noise; 50 open/discussing issues; max_tokens 1200 temp 0.2; status generated, model from response, prompt_version</t>
+        </is>
+      </c>
       <c r="J166" s="2" t="inlineStr"/>
       <c r="K166" s="2" t="inlineStr"/>
       <c r="L166" s="2" t="inlineStr"/>
-      <c r="M166" s="2" t="inlineStr"/>
+      <c r="M166" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -8840,14 +9296,22 @@
       </c>
       <c r="H167" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; fallback has counts, restart lines '- name: N exit(s) (last: ...)', top 5 containers</t>
+        </is>
+      </c>
       <c r="J167" s="2" t="inlineStr"/>
       <c r="K167" s="2" t="inlineStr"/>
       <c r="L167" s="2" t="inlineStr"/>
-      <c r="M167" s="2" t="inlineStr"/>
+      <c r="M167" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -8887,14 +9351,22 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>tests pass; cron hour/minute from settings (defaults 0/5), replace_existing, max_instances 1, coalesce; header + 3900 trunc with …; empty text skipped; failures logged</t>
+        </is>
+      </c>
       <c r="J168" s="2" t="inlineStr"/>
       <c r="K168" s="2" t="inlineStr"/>
       <c r="L168" s="2" t="inlineStr"/>
-      <c r="M168" s="2" t="inlineStr"/>
+      <c r="M168" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -8934,14 +9406,22 @@
       </c>
       <c r="H169" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>2 named tests pass + snippet: default 14; job prune-events 03:15; only 5 low-value statuses deleted; no-op when event_repo None. Nuance: retention 0 is treated as 14 (`or 14` before max(1,..)); API rejects 0 so unreachable.</t>
+        </is>
+      </c>
       <c r="J169" s="2" t="inlineStr"/>
       <c r="K169" s="2" t="inlineStr"/>
       <c r="L169" s="2" t="inlineStr"/>
-      <c r="M169" s="2" t="inlineStr"/>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -8981,14 +9461,22 @@
       </c>
       <c r="H170" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I170" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>test passes; start() False under TESTING / debug reloader parent / lock held; True if already started; pid written; release nulls fd</t>
+        </is>
+      </c>
       <c r="J170" s="2" t="inlineStr"/>
       <c r="K170" s="2" t="inlineStr"/>
       <c r="L170" s="2" t="inlineStr"/>
-      <c r="M170" s="2" t="inlineStr"/>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -9028,14 +9516,22 @@
       </c>
       <c r="H171" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>Snippet with docker.from_env patched: start() -&gt; running+started_at (enabled) / stopped (disabled), last_error None, watcher(60s) threads alive, scheduler w/ both jobs, 'coordinator-health-check' thread, bot.start(); from_env raising -&gt; degraded + 'docker watcher failed to start: no docker'; committ</t>
+        </is>
+      </c>
       <c r="J171" s="2" t="inlineStr"/>
       <c r="K171" s="2" t="inlineStr"/>
       <c r="L171" s="2" t="inlineStr"/>
-      <c r="M171" s="2" t="inlineStr"/>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
@@ -9075,14 +9571,22 @@
       </c>
       <c r="H172" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I172" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>test passes; default 30s; reconcile-thread death restarts; restart failure -&gt; False; healthy -&gt; False; loop ticks</t>
+        </is>
+      </c>
       <c r="J172" s="2" t="inlineStr"/>
       <c r="K172" s="2" t="inlineStr"/>
       <c r="L172" s="2" t="inlineStr"/>
-      <c r="M172" s="2" t="inlineStr"/>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -9122,14 +9626,22 @@
       </c>
       <c r="H173" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>test passes; loop calls check then flush each tick</t>
+        </is>
+      </c>
       <c r="J173" s="2" t="inlineStr"/>
       <c r="K173" s="2" t="inlineStr"/>
       <c r="L173" s="2" t="inlineStr"/>
-      <c r="M173" s="2" t="inlineStr"/>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
@@ -9169,14 +9681,22 @@
       </c>
       <c r="H174" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I174" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>stop(): health thread joined, watcher.stop+cleared, scheduler.shutdown(wait=False), bot.stop, lock released, _started False; proxies ok</t>
+        </is>
+      </c>
       <c r="J174" s="2" t="inlineStr"/>
       <c r="K174" s="2" t="inlineStr"/>
       <c r="L174" s="2" t="inlineStr"/>
-      <c r="M174" s="2" t="inlineStr"/>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="inlineStr">

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$234</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$238</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M234"/>
+  <dimension ref="A1:M238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -12530,10 +12530,246 @@
       <c r="L234" s="2" t="inlineStr"/>
       <c r="M234" s="2" t="inlineStr"/>
     </row>
+    <row r="235">
+      <c r="A235" s="2" t="inlineStr">
+        <is>
+          <t>UX-01</t>
+        </is>
+      </c>
+      <c r="B235" s="2" t="inlineStr">
+        <is>
+          <t>UI: Cross-cutting</t>
+        </is>
+      </c>
+      <c r="C235" s="2" t="inlineStr">
+        <is>
+          <t>Timestamp formatting</t>
+        </is>
+      </c>
+      <c r="D235" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want timestamps shown as readable local-ish datetimes so I can scan lists.</t>
+        </is>
+      </c>
+      <c r="E235" s="2" t="inlineStr">
+        <is>
+          <t>All rendered datetimes (events, issues, reports, dashboard) show 'YYYY-MM-DD HH:MM:SS' (or relative) — never Python's default repr with microseconds.</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>app/templates/insights.html, issues.html, reports.html, dashboard.html</t>
+        </is>
+      </c>
+      <c r="G235" s="2" t="inlineStr">
+        <is>
+          <t>Open /insights, /issues?id=N, /reports with seeded rows; inspect time columns.</t>
+        </is>
+      </c>
+      <c r="H235" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I235" s="2" t="inlineStr">
+        <is>
+          <t>Events/Issues/Reports/Dashboard show e.g. '2026-08-15 20:30:46.327049'</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>Templates print datetime objects directly (str()) → microseconds. Add a Jinja filter `dt` → strftime('%Y-%m-%d %H:%M:%S') and apply everywhere.</t>
+        </is>
+      </c>
+      <c r="K235" s="2" t="inlineStr"/>
+      <c r="L235" s="2" t="inlineStr"/>
+      <c r="M235" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="2" t="inlineStr">
+        <is>
+          <t>UX-02</t>
+        </is>
+      </c>
+      <c r="B236" s="2" t="inlineStr">
+        <is>
+          <t>UI: Events</t>
+        </is>
+      </c>
+      <c r="C236" s="2" t="inlineStr">
+        <is>
+          <t>Severity badge for non-analysed rows</t>
+        </is>
+      </c>
+      <c r="D236" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I don't want a misleading 'noise' badge on rows that never got a classification (llm_error, parse_error, container_event with none).</t>
+        </is>
+      </c>
+      <c r="E236" s="2" t="inlineStr">
+        <is>
+          <t>Rows whose classification is None show '—' (neutral) instead of defaulting to 'noise'; llm_error/parse_error rows show an error-styled status badge.</t>
+        </is>
+      </c>
+      <c r="F236" s="2" t="inlineStr">
+        <is>
+          <t>app/templates/insights.html</t>
+        </is>
+      </c>
+      <c r="G236" s="2" t="inlineStr">
+        <is>
+          <t>Seed an llm_error event; open /insights; check the severity cell.</t>
+        </is>
+      </c>
+      <c r="H236" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I236" s="2" t="inlineStr">
+        <is>
+          <t>llm_error row shows 'noise' severity badge; skipped rows show 'noise' + 'skipped' badge (redundant).</t>
+        </is>
+      </c>
+      <c r="J236" s="2" t="inlineStr">
+        <is>
+          <t>insights.html severity badge falls back to 'noise' when classification is None.</t>
+        </is>
+      </c>
+      <c r="K236" s="2" t="inlineStr"/>
+      <c r="L236" s="2" t="inlineStr"/>
+      <c r="M236" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="2" t="inlineStr">
+        <is>
+          <t>UX-03</t>
+        </is>
+      </c>
+      <c r="B237" s="2" t="inlineStr">
+        <is>
+          <t>UI: Issues</t>
+        </is>
+      </c>
+      <c r="C237" s="2" t="inlineStr">
+        <is>
+          <t>Issue body rendering</t>
+        </is>
+      </c>
+      <c r="D237" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want the issue body (markdown built by the bot) rendered like reports, not raw '# heading' text.</t>
+        </is>
+      </c>
+      <c r="E237" s="2" t="inlineStr">
+        <is>
+          <t>Issue detail renders body via markdown_lite (headings, lists, code) inside .prose; discussion transcript keeps monospace.</t>
+        </is>
+      </c>
+      <c r="F237" s="2" t="inlineStr">
+        <is>
+          <t>app/templates/issues.html, app/web/routes.py issues_page, app/web/markdown_lite.py</t>
+        </is>
+      </c>
+      <c r="G237" s="2" t="inlineStr">
+        <is>
+          <t>Open /issues?id=1 with a seeded markdown body; headings render as &lt;h1&gt;/&lt;h2&gt;.</t>
+        </is>
+      </c>
+      <c r="H237" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I237" s="2" t="inlineStr">
+        <is>
+          <t>Issue body shows raw markdown ('# app OOM killed') in a &lt;pre&gt;.</t>
+        </is>
+      </c>
+      <c r="J237" s="2" t="inlineStr">
+        <is>
+          <t>issues.html renders issue.body in &lt;pre&gt;; route doesn't call render_markdown.</t>
+        </is>
+      </c>
+      <c r="K237" s="2" t="inlineStr"/>
+      <c r="L237" s="2" t="inlineStr"/>
+      <c r="M237" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="2" t="inlineStr">
+        <is>
+          <t>UX-04</t>
+        </is>
+      </c>
+      <c r="B238" s="2" t="inlineStr">
+        <is>
+          <t>UI: Dashboard</t>
+        </is>
+      </c>
+      <c r="C238" s="2" t="inlineStr">
+        <is>
+          <t>First-run checklist LLM criterion</t>
+        </is>
+      </c>
+      <c r="D238" s="2" t="inlineStr">
+        <is>
+          <t>As a new user I want 'Configure the LLM' ticked only when the LLM has actually been verified.</t>
+        </is>
+      </c>
+      <c r="E238" s="2" t="inlineStr">
+        <is>
+          <t>Checklist item is done when base_url+model are set AND (api transport: a Test LLM has succeeded or api_key set for non-local hosts) — at minimum not ticked on the pristine defaults; simplest: track last successful test-llm timestamp in SentinelState/settings and use that.</t>
+        </is>
+      </c>
+      <c r="F238" s="2" t="inlineStr">
+        <is>
+          <t>app/templates/dashboard.html checklist, app/web/routes.py dashboard</t>
+        </is>
+      </c>
+      <c r="G238" s="2" t="inlineStr">
+        <is>
+          <t>Fresh DB → /dashboard: LLM item should be unticked; after POST /api/settings/test-llm succeeds it ticks.</t>
+        </is>
+      </c>
+      <c r="H238" s="2" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I238" s="2" t="inlineStr">
+        <is>
+          <t>Pristine DB (api key '', model llama3, default base_url) shows 'Configure the LLM' as done.</t>
+        </is>
+      </c>
+      <c r="J238" s="2" t="inlineStr">
+        <is>
+          <t>dashboard checklist criterion too weak.</t>
+        </is>
+      </c>
+      <c r="K238" s="2" t="inlineStr"/>
+      <c r="L238" s="2" t="inlineStr"/>
+      <c r="M238" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M234"/>
+  <autoFilter ref="A1:M238"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H234" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H238" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not tested,Pass,Fail,Fixed - retest,Pass (after fix),Blocked (needs docker/LLM/Telegram),Won't fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12547,7 +12783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D48"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -12577,7 +12813,7 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$234,A2)</f>
+        <f>COUNTIF(Stories!$H$2:$H$238,A2)</f>
         <v/>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -12590,7 +12826,7 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$234,A3)</f>
+        <f>COUNTIF(Stories!$H$2:$H$238,A3)</f>
         <v/>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -12603,7 +12839,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$234,A4)</f>
+        <f>COUNTIF(Stories!$H$2:$H$238,A4)</f>
         <v/>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -12616,7 +12852,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$234,A5)</f>
+        <f>COUNTIF(Stories!$H$2:$H$238,A5)</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -12629,7 +12865,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$234,A6)</f>
+        <f>COUNTIF(Stories!$H$2:$H$238,A6)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -12642,7 +12878,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$234,A7)</f>
+        <f>COUNTIF(Stories!$H$2:$H$238,A7)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -12655,7 +12891,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$234,A8)</f>
+        <f>COUNTIF(Stories!$H$2:$H$238,A8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -12668,7 +12904,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTA(Stories!$A$2:$A$234)</f>
+        <f>COUNTA(Stories!$A$2:$A$238)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -12732,15 +12968,15 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A14)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A14)</f>
         <v/>
       </c>
       <c r="C14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A14,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A14,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A14,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A14,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A14,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A14,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12751,15 +12987,15 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A15)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A15)</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A15,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A15,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A15,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A15,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A15,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A15,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12770,15 +13006,15 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A16)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A16)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A16,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A16,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A16,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A16,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A16,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A16,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12789,15 +13025,15 @@
         </is>
       </c>
       <c r="B17" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A17)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A17)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A17,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A17,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A17,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A17,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A17,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A17,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12808,15 +13044,15 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A18)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A18)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A18,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A18,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A18,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A18,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A18,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A18,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12827,15 +13063,15 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A19)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A19)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A19,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A19,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A19,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A19,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A19,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A19,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12846,15 +13082,15 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A20)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A20)</f>
         <v/>
       </c>
       <c r="C20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A20,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A20,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A20,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A20,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A20,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A20,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12865,15 +13101,15 @@
         </is>
       </c>
       <c r="B21" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A21)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A21)</f>
         <v/>
       </c>
       <c r="C21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A21,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A21,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A21,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A21,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A21,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A21,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12884,15 +13120,15 @@
         </is>
       </c>
       <c r="B22" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A22)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A22)</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A22,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A22,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A22,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A22,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A22,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A22,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12903,15 +13139,15 @@
         </is>
       </c>
       <c r="B23" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A23)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A23)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A23,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A23,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A23,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A23,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A23,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A23,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12922,15 +13158,15 @@
         </is>
       </c>
       <c r="B24" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A24)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A24)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A24,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A24,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A24,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A24,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A24,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A24,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12941,15 +13177,15 @@
         </is>
       </c>
       <c r="B25" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A25)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A25)</f>
         <v/>
       </c>
       <c r="C25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A25,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A25,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A25,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A25,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A25,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A25,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12960,15 +13196,15 @@
         </is>
       </c>
       <c r="B26" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A26)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A26)</f>
         <v/>
       </c>
       <c r="C26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A26,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A26,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A26,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A26,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A26,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A26,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12979,15 +13215,15 @@
         </is>
       </c>
       <c r="B27" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A27)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A27)</f>
         <v/>
       </c>
       <c r="C27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A27,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A27,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A27,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A27,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A27,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A27,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -12998,15 +13234,15 @@
         </is>
       </c>
       <c r="B28" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A28)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A28)</f>
         <v/>
       </c>
       <c r="C28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A28,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A28,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A28,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A28,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A28,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A28,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13017,15 +13253,15 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A29)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A29)</f>
         <v/>
       </c>
       <c r="C29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A29,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A29,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A29,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A29,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A29,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A29,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13036,15 +13272,15 @@
         </is>
       </c>
       <c r="B30" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A30)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A30)</f>
         <v/>
       </c>
       <c r="C30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A30,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A30,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A30,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A30,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A30,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A30,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13055,15 +13291,15 @@
         </is>
       </c>
       <c r="B31" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A31)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A31)</f>
         <v/>
       </c>
       <c r="C31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A31,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A31,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A31,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A31,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A31,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A31,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13074,15 +13310,15 @@
         </is>
       </c>
       <c r="B32" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A32)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A32)</f>
         <v/>
       </c>
       <c r="C32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A32,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A32,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A32,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A32,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A32,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A32,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13093,15 +13329,15 @@
         </is>
       </c>
       <c r="B33" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A33)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A33)</f>
         <v/>
       </c>
       <c r="C33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A33,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A33,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A33,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A33,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A33,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A33,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13112,15 +13348,15 @@
         </is>
       </c>
       <c r="B34" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A34)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A34)</f>
         <v/>
       </c>
       <c r="C34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A34,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A34,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A34,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A34,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A34,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A34,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13131,15 +13367,15 @@
         </is>
       </c>
       <c r="B35" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A35)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A35)</f>
         <v/>
       </c>
       <c r="C35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A35,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A35,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A35,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A35,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A35,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A35,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13150,15 +13386,15 @@
         </is>
       </c>
       <c r="B36" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A36)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A36)</f>
         <v/>
       </c>
       <c r="C36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A36,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A36,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A36,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A36,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A36,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A36,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13169,15 +13405,15 @@
         </is>
       </c>
       <c r="B37" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A37)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A37)</f>
         <v/>
       </c>
       <c r="C37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A37,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A37,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A37,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A37,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A37,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A37,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13188,15 +13424,15 @@
         </is>
       </c>
       <c r="B38" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A38)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A38)</f>
         <v/>
       </c>
       <c r="C38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A38,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A38,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A38,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A38,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A38,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A38,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13207,15 +13443,15 @@
         </is>
       </c>
       <c r="B39" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A39)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A39)</f>
         <v/>
       </c>
       <c r="C39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A39,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A39,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A39,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A39,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A39,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A39,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13226,15 +13462,15 @@
         </is>
       </c>
       <c r="B40" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A40)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A40)</f>
         <v/>
       </c>
       <c r="C40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A40,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A40,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A40,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A40,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A40,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A40,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -13245,148 +13481,167 @@
         </is>
       </c>
       <c r="B41" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A41)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A41)</f>
         <v/>
       </c>
       <c r="C41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A41,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A41,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A41,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A41,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A41,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A41,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>UI: Dashboard</t>
+          <t>UI: Cross-cutting</t>
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A42)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A42)</f>
         <v/>
       </c>
       <c r="C42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A42,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A42,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A42,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A42,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A42,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A42,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>UI: Events</t>
+          <t>UI: Dashboard</t>
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A43)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A43)</f>
         <v/>
       </c>
       <c r="C43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A43,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A43,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A43,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A43,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A43,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A43,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>UI: Exclusions</t>
+          <t>UI: Events</t>
         </is>
       </c>
       <c r="B44" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A44)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A44)</f>
         <v/>
       </c>
       <c r="C44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A44,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A44,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A44,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A44,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A44,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A44,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>UI: Issues</t>
+          <t>UI: Exclusions</t>
         </is>
       </c>
       <c r="B45" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A45)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A45)</f>
         <v/>
       </c>
       <c r="C45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A45,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A45,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A45,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A45,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A45,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A45,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>UI: Prompts</t>
+          <t>UI: Issues</t>
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A46)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A46)</f>
         <v/>
       </c>
       <c r="C46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A46,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A46,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A46,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A46,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A46,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A46,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>UI: Reports</t>
+          <t>UI: Prompts</t>
         </is>
       </c>
       <c r="B47" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A47)</f>
+        <f>COUNTIF(Stories!$B$2:$B$238,A47)</f>
         <v/>
       </c>
       <c r="C47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A47,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A47,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A47,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A47,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A47,Stories!$H$2:$H$234,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$238,A47,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
+          <t>UI: Reports</t>
+        </is>
+      </c>
+      <c r="B48" s="4">
+        <f>COUNTIF(Stories!$B$2:$B$238,A48)</f>
+        <v/>
+      </c>
+      <c r="C48" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$238,A48,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A48,Stories!$H$2:$H$238,"Pass (after fix)")</f>
+        <v/>
+      </c>
+      <c r="D48" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$238,A48,Stories!$H$2:$H$238,"Fail")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
           <t>UI: Settings</t>
         </is>
       </c>
-      <c r="B48" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$234,A48)</f>
+      <c r="B49" s="4">
+        <f>COUNTIF(Stories!$B$2:$B$238,A49)</f>
         <v/>
       </c>
-      <c r="C48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A48,Stories!$H$2:$H$234,"Pass")+COUNTIFS(Stories!$B$2:$B$234,A48,Stories!$H$2:$H$234,"Pass (after fix)")</f>
+      <c r="C49" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$238,A49,Stories!$H$2:$H$238,"Pass")+COUNTIFS(Stories!$B$2:$B$238,A49,Stories!$H$2:$H$238,"Pass (after fix)")</f>
         <v/>
       </c>
-      <c r="D48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$234,A48,Stories!$H$2:$H$234,"Fail")</f>
+      <c r="D49" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$238,A49,Stories!$H$2:$H$238,"Fail")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -9736,14 +9736,22 @@
       </c>
       <c r="H175" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>int_checks/test_bot.py::test_int01_*: start() twice -&gt; single daemon thread named 'telegram-bot'; stop() sets event and joins (thread dead). Coordinator.start/stop source contains telegram_bot.start()/stop(). tests/test_runtime_lock.py passes.</t>
+        </is>
+      </c>
       <c r="J175" s="2" t="inlineStr"/>
       <c r="K175" s="2" t="inlineStr"/>
       <c r="L175" s="2" t="inlineStr"/>
-      <c r="M175" s="2" t="inlineStr"/>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
@@ -9783,14 +9791,22 @@
       </c>
       <c r="H176" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>test_int02_idle_without_token: token='' -&gt; loop ran 0.5s with zero get_updates calls (waits on stop event; source waits 10s).</t>
+        </is>
+      </c>
       <c r="J176" s="2" t="inlineStr"/>
       <c r="K176" s="2" t="inlineStr"/>
       <c r="L176" s="2" t="inlineStr"/>
-      <c r="M176" s="2" t="inlineStr"/>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
@@ -9830,14 +9846,22 @@
       </c>
       <c r="H177" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I177" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>test_int03: fake get_updates returned ids 5,6 then raised; _offset==7, get_updates called with (0,25) then offset 7; dispatch exceptions swallowed and both updates dispatched; stop.wait(5) backoff observed and loop continued.</t>
+        </is>
+      </c>
       <c r="J177" s="2" t="inlineStr"/>
       <c r="K177" s="2" t="inlineStr"/>
       <c r="L177" s="2" t="inlineStr"/>
-      <c r="M177" s="2" t="inlineStr"/>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
@@ -9877,14 +9901,22 @@
       </c>
       <c r="H178" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I178" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_review_batch2.py::test_bot_ignores_updates_from_other_chats and ::test_bot_ignores_everything_when_no_chat_configured pass and assert no send/answer for wrong/empty chat.</t>
+        </is>
+      </c>
       <c r="J178" s="2" t="inlineStr"/>
       <c r="K178" s="2" t="inlineStr"/>
       <c r="L178" s="2" t="inlineStr"/>
-      <c r="M178" s="2" t="inlineStr"/>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
@@ -9924,14 +9956,22 @@
       </c>
       <c r="H179" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>test_int05: 'nope'-&gt;Invalid action, 'approve:x'-&gt;Invalid event id, 'approve:9999'-&gt;Event not found, 'zap:&lt;id&gt;'-&gt;Unknown action; LocalIssue count 0; nothing sent.</t>
+        </is>
+      </c>
       <c r="J179" s="2" t="inlineStr"/>
       <c r="K179" s="2" t="inlineStr"/>
       <c r="L179" s="2" t="inlineStr"/>
-      <c r="M179" s="2" t="inlineStr"/>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
@@ -9971,14 +10011,22 @@
       </c>
       <c r="H180" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I180" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>test_int06: reject:&lt;id&gt; -&gt; LocalIssue status=rejected action=reject; edit_message_reply_markup with {'inline_keyboard':[]}; answer 'Rejected'; sent '✕ REJECTED · Issue #N recorded.' reply_to alert msg. test_track_a rejected-suppression tests pass.</t>
+        </is>
+      </c>
       <c r="J180" s="2" t="inlineStr"/>
       <c r="K180" s="2" t="inlineStr"/>
       <c r="L180" s="2" t="inlineStr"/>
-      <c r="M180" s="2" t="inlineStr"/>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
@@ -10018,14 +10066,22 @@
       </c>
       <c r="H181" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>test_int07: approve:&lt;id&gt; -&gt; status open/action approve; keyboard stripped; answer 'Issue #N created'; text '✓ APPROVED · Issue #N open locally.\nQuery it at /issues.' with reply_to_message_id == alert message_id.</t>
+        </is>
+      </c>
       <c r="J181" s="2" t="inlineStr"/>
       <c r="K181" s="2" t="inlineStr"/>
       <c r="L181" s="2" t="inlineStr"/>
-      <c r="M181" s="2" t="inlineStr"/>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
@@ -10065,14 +10121,22 @@
       </c>
       <c r="H182" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I182" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>test_int08: discuss:&lt;id&gt; -&gt; status discussing/action discuss; keyboard stripped; prompt text starts '💬 DISCUSSING · Issue #N\nReply to THIS message'; issue.telegram_message_id updated to 555; answer 'Ask a follow-up'.</t>
+        </is>
+      </c>
       <c r="J182" s="2" t="inlineStr"/>
       <c r="K182" s="2" t="inlineStr"/>
       <c r="L182" s="2" t="inlineStr"/>
-      <c r="M182" s="2" t="inlineStr"/>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
@@ -10112,14 +10176,22 @@
       </c>
       <c r="H183" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I183" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>test_int09: 600-char summary -&gt; title len 500; body has Container/Classification/Status/Analyzed by/Root cause/Suggested fix; 3000-char excerpt fenced, capped at 2000; defaults critical/analyzed/unknown and '&lt;container&gt;: critical alert'; event_id/confidence/chat/msg id/llm_model stored.</t>
+        </is>
+      </c>
       <c r="J183" s="2" t="inlineStr"/>
       <c r="K183" s="2" t="inlineStr"/>
       <c r="L183" s="2" t="inlineStr"/>
-      <c r="M183" s="2" t="inlineStr"/>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
@@ -10159,14 +10231,22 @@
       </c>
       <c r="H184" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I184" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I184" s="2" t="inlineStr">
+        <is>
+          <t>Existing batch2 tests pass + test_int10: blank text ignored; reply_to a non-discussing issue -&gt; silent; no reply_to &amp; no discussing -&gt; silent; falls back to latest discussing issue for chat.</t>
+        </is>
+      </c>
       <c r="J184" s="2" t="inlineStr"/>
       <c r="K184" s="2" t="inlineStr"/>
       <c r="L184" s="2" t="inlineStr"/>
-      <c r="M184" s="2" t="inlineStr"/>
+      <c r="M184" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
@@ -10206,14 +10286,22 @@
       </c>
       <c r="H185" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I185" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I185" s="2" t="inlineStr">
+        <is>
+          <t>test_int11: after owner reply, discussion contains '[YYYY-MM-DD HH:MM:SS] USER:\nwhy?' and 'ASSISTANT:\nthe answer'; answer sent as reply to user msg; telegram_message_id updated to 777.</t>
+        </is>
+      </c>
       <c r="J185" s="2" t="inlineStr"/>
       <c r="K185" s="2" t="inlineStr"/>
       <c r="L185" s="2" t="inlineStr"/>
-      <c r="M185" s="2" t="inlineStr"/>
+      <c r="M185" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -10253,14 +10341,26 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I186" s="2" t="inlineStr"/>
-      <c r="J186" s="2" t="inlineStr"/>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="I186" s="2" t="inlineStr">
+        <is>
+          <t>test_int12: message structure, LLMConfig.from_settings, max_tokens=reserved_output_tokens, '(empty response)' and '[LLM error: ...]' all OK. But system prompt is ALWAYS the fallback SRE text: prompt_repo.get() does not exist (PromptRepository only has get_by_key), AttributeError is swallowed.</t>
+        </is>
+      </c>
+      <c r="J186" s="2" t="inlineStr">
+        <is>
+          <t>Expected messages[0].content == SENTINEL_SYSTEM prompt; observed 'You are an SRE assistant helping triage Docker container issues.' every call. app/services/telegram_bot.py:264 calls self.prompt_repo.get(PromptKey.SENTINEL_SYSTEM) but app/repositories/prompts.py:7 only defines get_by_key -&gt; AttributeError caught at :265.</t>
+        </is>
+      </c>
       <c r="K186" s="2" t="inlineStr"/>
       <c r="L186" s="2" t="inlineStr"/>
-      <c r="M186" s="2" t="inlineStr"/>
+      <c r="M186" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -10300,14 +10400,22 @@
       </c>
       <c r="H187" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I187" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I187" s="2" t="inlineStr">
+        <is>
+          <t>test_int13 (httpx.Client faked): no token/chat -&gt; (False,'telegram credentials are not configured',None), no HTTP; POST .../bot&lt;T&gt;/sendMessage payload chat_id,text,+reply_markup,+reply_to_message_id&amp;allow_sending_without_reply,+parse_mode; timeout 10; (True,None,7); ConnectError -&gt; (False,str,None).</t>
+        </is>
+      </c>
       <c r="J187" s="2" t="inlineStr"/>
       <c r="K187" s="2" t="inlineStr"/>
       <c r="L187" s="2" t="inlineStr"/>
-      <c r="M187" s="2" t="inlineStr"/>
+      <c r="M187" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -10347,14 +10455,22 @@
       </c>
       <c r="H188" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I188" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_api.py::test_core_api_endpoints (400 unconfigured) + test_int14: 400 body ok=false with error; with token/chat set and notifier.send_message patched -&gt; 200 ok=true, sent ('tok','1000','DockSentinel test message').</t>
+        </is>
+      </c>
       <c r="J188" s="2" t="inlineStr"/>
       <c r="K188" s="2" t="inlineStr"/>
       <c r="L188" s="2" t="inlineStr"/>
-      <c r="M188" s="2" t="inlineStr"/>
+      <c r="M188" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
@@ -10394,14 +10510,22 @@
       </c>
       <c r="H189" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I189" s="2" t="inlineStr">
+        <is>
+          <t>test_int15: empty token -&gt; no HTTP for all three helpers; URLs editMessageReplyMarkup/editMessageText/answerCallbackQuery; answer payload includes 'text' only when non-empty; timeout 10; httpx.ConnectError swallowed.</t>
+        </is>
+      </c>
       <c r="J189" s="2" t="inlineStr"/>
       <c r="K189" s="2" t="inlineStr"/>
       <c r="L189" s="2" t="inlineStr"/>
-      <c r="M189" s="2" t="inlineStr"/>
+      <c r="M189" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -10441,14 +10565,22 @@
       </c>
       <c r="H190" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I190" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I190" s="2" t="inlineStr">
+        <is>
+          <t>test_int16: get_updates('',0)==[] without HTTP; GET getUpdates params offset/timeout/allowed_updates='["message","callback_query"]', client timeout=timeout+10 (35); HTTPError -&gt; RuntimeError('telegram getUpdates failed: ...').</t>
+        </is>
+      </c>
       <c r="J190" s="2" t="inlineStr"/>
       <c r="K190" s="2" t="inlineStr"/>
       <c r="L190" s="2" t="inlineStr"/>
-      <c r="M190" s="2" t="inlineStr"/>
+      <c r="M190" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
@@ -10488,14 +10620,22 @@
       </c>
       <c r="H191" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I191" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>test_int17: _build_keyboard(5) -&gt; [('✕ Reject','reject:5'),('✓ Approve','approve:5'),('💬 Discuss','discuss:5')]; None-&gt;None; TelegramAlertStrategy passes markup+config chat/token to send_message; maybe_send end-to-end carries keyboard.</t>
+        </is>
+      </c>
       <c r="J191" s="2" t="inlineStr"/>
       <c r="K191" s="2" t="inlineStr"/>
       <c r="L191" s="2" t="inlineStr"/>
-      <c r="M191" s="2" t="inlineStr"/>
+      <c r="M191" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -10535,14 +10675,22 @@
       </c>
       <c r="H192" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I192" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I192" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_track_a.py::test_nightly_job_pushes_briefing_to_telegram (len&lt;=3900, header, token/chat) and ::test_nightly_job_skips_telegram_when_unconfigured_or_failed pass.</t>
+        </is>
+      </c>
       <c r="J192" s="2" t="inlineStr"/>
       <c r="K192" s="2" t="inlineStr"/>
       <c r="L192" s="2" t="inlineStr"/>
-      <c r="M192" s="2" t="inlineStr"/>
+      <c r="M192" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
@@ -10582,14 +10730,22 @@
       </c>
       <c r="H193" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I193" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_cli_backends.py::test_cli_backend_runner_executes_backend passes + test_int19: '../x' -&gt; 'invalid backend name'; missing -&gt; 'backend script not found'; chmod -x -&gt; 'not executable'; stdin prompt echoed to stdout; non-zero exit -&gt; RuntimeError.</t>
+        </is>
+      </c>
       <c r="J193" s="2" t="inlineStr"/>
       <c r="K193" s="2" t="inlineStr"/>
       <c r="L193" s="2" t="inlineStr"/>
-      <c r="M193" s="2" t="inlineStr"/>
+      <c r="M193" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -10629,14 +10785,22 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I194" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>batch2 env tests pass + test_int20: PASSTHROUGH='FOO, BAR' passes FOO/BAR not BAZ; secrets dropped; exact names and all prefixes pass; PATH default '/usr/local/bin:/usr/bin:/bin'; DOCKSENTINEL_BACKEND=&lt;name&gt; visible to script.</t>
+        </is>
+      </c>
       <c r="J194" s="2" t="inlineStr"/>
       <c r="K194" s="2" t="inlineStr"/>
       <c r="L194" s="2" t="inlineStr"/>
-      <c r="M194" s="2" t="inlineStr"/>
+      <c r="M194" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
@@ -10676,14 +10840,22 @@
       </c>
       <c r="H195" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I195" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_review_batch2.py::test_cli_backend_timeout_kills_child_process_group passes (child gone) + test_int21: error 'backend 'slow' timed out after 1s'. start_new_session=True/killpg confirmed in source.</t>
+        </is>
+      </c>
       <c r="J195" s="2" t="inlineStr"/>
       <c r="K195" s="2" t="inlineStr"/>
       <c r="L195" s="2" t="inlineStr"/>
-      <c r="M195" s="2" t="inlineStr"/>
+      <c r="M195" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
@@ -10723,14 +10895,22 @@
       </c>
       <c r="H196" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I196" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I196" s="2" t="inlineStr">
+        <is>
+          <t>test_cli_backends lock/exec tests pass + test_int22: exit 3 with max_retries=1 -&gt; 2 attempts and 'exit code 3'; blank stdout -&gt; 'returned empty output'; stderr surfaced; content stripped; max_concurrent_calls=0 -&gt; 1; held semaphore -&gt; 'single-call lock busy' after timeout+5s.</t>
+        </is>
+      </c>
       <c r="J196" s="2" t="inlineStr"/>
       <c r="K196" s="2" t="inlineStr"/>
       <c r="L196" s="2" t="inlineStr"/>
-      <c r="M196" s="2" t="inlineStr"/>
+      <c r="M196" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
@@ -10770,14 +10950,22 @@
       </c>
       <c r="H197" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I197" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I197" s="2" t="inlineStr">
+        <is>
+          <t>llm-backends/claude.sh via runner: no claude on PATH -&gt; 'claude CLI is not installed or not in PATH'; stub whose --help mentions --tools receives '-p --tools  PROMPT'. Note: no-'--tools' branch fails under macOS bash 3.2 ('extra[@]: unbound variable', needs bash&gt;=4.4); Docker image bash 5.2 is fine.</t>
+        </is>
+      </c>
       <c r="J197" s="2" t="inlineStr"/>
       <c r="K197" s="2" t="inlineStr"/>
       <c r="L197" s="2" t="inlineStr"/>
-      <c r="M197" s="2" t="inlineStr"/>
+      <c r="M197" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
@@ -10817,14 +11005,22 @@
       </c>
       <c r="H198" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I198" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I198" s="2" t="inlineStr">
+        <is>
+          <t>codex.sh via runner with stub codex: missing -&gt; 'codex CLI is not installed'; args 'exec --skip-git-repo-check --ephemeral --sandbox read-only --output-last-message &lt;tmp&gt; PROMPT'; stub stdout discarded; content=='ok' from tmp file; tmp file removed after exit.</t>
+        </is>
+      </c>
       <c r="J198" s="2" t="inlineStr"/>
       <c r="K198" s="2" t="inlineStr"/>
       <c r="L198" s="2" t="inlineStr"/>
-      <c r="M198" s="2" t="inlineStr"/>
+      <c r="M198" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
@@ -10864,14 +11060,22 @@
       </c>
       <c r="H199" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I199" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I199" s="2" t="inlineStr">
+        <is>
+          <t>gemini.sh/ollama.sh via runner: missing binaries -&gt; 'not installed or not in PATH' errors; gemini stub gets '-p PROMPT'; ollama stub gets 'run foo PROMPT' with OLLAMA_MODEL=foo (prefix passthrough) and 'run llama3 PROMPT' when unset.</t>
+        </is>
+      </c>
       <c r="J199" s="2" t="inlineStr"/>
       <c r="K199" s="2" t="inlineStr"/>
       <c r="L199" s="2" t="inlineStr"/>
-      <c r="M199" s="2" t="inlineStr"/>
+      <c r="M199" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
@@ -10911,14 +11115,22 @@
       </c>
       <c r="H200" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I200" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I200" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">test_llm_client passes + test_int26: LLMClient(cli_runner=None).complete(transport='cli')/chat_completion_cli raise 'cli backend runner is not configured'; CLI_BACKENDS_DIR=tmp -&gt; cli_runner.backends_dir==tmp, max_concurrent 1; model 'cli:codex'; default dir &lt;repo&gt;/llm-backends. </t>
+        </is>
+      </c>
       <c r="J200" s="2" t="inlineStr"/>
       <c r="K200" s="2" t="inlineStr"/>
       <c r="L200" s="2" t="inlineStr"/>
-      <c r="M200" s="2" t="inlineStr"/>
+      <c r="M200" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
@@ -10958,14 +11170,22 @@
       </c>
       <c r="H201" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I201" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I201" s="2" t="inlineStr">
+        <is>
+          <t>test_int27_30_config: SECRET_KEY unset, FLASK_ENV unset -&gt; 'dev-secret-key'; FLASK_ENV=production+TESTING=true -&gt; 'dev-secret-key'.</t>
+        </is>
+      </c>
       <c r="J201" s="2" t="inlineStr"/>
       <c r="K201" s="2" t="inlineStr"/>
       <c r="L201" s="2" t="inlineStr"/>
-      <c r="M201" s="2" t="inlineStr"/>
+      <c r="M201" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -11005,14 +11225,22 @@
       </c>
       <c r="H202" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I202" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>FLASK_ENV=production, TESTING=false: unset -&gt; 'SECRET_KEY must be set'; 'change-me'/'Dev-Secret-Key'/'CHANGE-ME' -&gt; placeholder error; 'short' -&gt; 'at least 16 characters'; 32-char OK.</t>
+        </is>
+      </c>
       <c r="J202" s="2" t="inlineStr"/>
       <c r="K202" s="2" t="inlineStr"/>
       <c r="L202" s="2" t="inlineStr"/>
-      <c r="M202" s="2" t="inlineStr"/>
+      <c r="M202" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
@@ -11052,14 +11280,22 @@
       </c>
       <c r="H203" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I203" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I203" s="2" t="inlineStr">
+        <is>
+          <t>_as_bool: None-&gt;default; '1','true','yes','on',' YES ','On','TRUE' -&gt; True; 'Off','0','no','' -&gt; False; START_COORDINATOR Off-&gt;False, YES-&gt;True, unset-&gt;True; TESTING unset-&gt;False.</t>
+        </is>
+      </c>
       <c r="J203" s="2" t="inlineStr"/>
       <c r="K203" s="2" t="inlineStr"/>
       <c r="L203" s="2" t="inlineStr"/>
-      <c r="M203" s="2" t="inlineStr"/>
+      <c r="M203" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
@@ -11099,14 +11335,22 @@
       </c>
       <c r="H204" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I204" s="2" t="inlineStr">
+        <is>
+          <t>dev: sqlite:///./data/docksentinel.db &amp; ./data/runtime.lock; production: sqlite:////data/docksentinel.db &amp; /data/runtime.lock; DATABASE_URL/RUNTIME_LOCK_PATH override honoured.</t>
+        </is>
+      </c>
       <c r="J204" s="2" t="inlineStr"/>
       <c r="K204" s="2" t="inlineStr"/>
       <c r="L204" s="2" t="inlineStr"/>
-      <c r="M204" s="2" t="inlineStr"/>
+      <c r="M204" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
@@ -11146,14 +11390,22 @@
       </c>
       <c r="H205" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I205" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>test_int31: DATABASE_URL=sqlite:///&lt;tmp&gt;/nested/deep/x.db -&gt; create_app creates nested dir; relative path resolved under instance_path; ':memory:', '' and postgresql URIs skipped.</t>
+        </is>
+      </c>
       <c r="J205" s="2" t="inlineStr"/>
       <c r="K205" s="2" t="inlineStr"/>
       <c r="L205" s="2" t="inlineStr"/>
-      <c r="M205" s="2" t="inlineStr"/>
+      <c r="M205" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -11193,14 +11445,22 @@
       </c>
       <c r="H206" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I206" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I206" s="2" t="inlineStr">
+        <is>
+          <t>test_int32: TESTING app has local_issues table (create_all), config START_COORDINATOR False, RUNTIME_LOCK_PATH, FLASK_PYDANTIC_VALIDATION_ERROR_RAISE True, coordinator._started False; START_COORDINATOR=true + TESTING still not started.</t>
+        </is>
+      </c>
       <c r="J206" s="2" t="inlineStr"/>
       <c r="K206" s="2" t="inlineStr"/>
       <c r="L206" s="2" t="inlineStr"/>
-      <c r="M206" s="2" t="inlineStr"/>
+      <c r="M206" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
@@ -11240,14 +11500,22 @@
       </c>
       <c r="H207" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I207" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I207" s="2" t="inlineStr">
+        <is>
+          <t>test_int33 (fake MDNSPublisher): TESTING -&gt; not created; TESTING=false FLASK_ENV=development MDNS_ENABLED=TRUE -&gt; MDNSPublisher('docksentinel',80).start(); MDNS_HOSTNAME/PORT honoured ('myhost',8080); MDNS_ENABLED=false -&gt; nothing.</t>
+        </is>
+      </c>
       <c r="J207" s="2" t="inlineStr"/>
       <c r="K207" s="2" t="inlineStr"/>
       <c r="L207" s="2" t="inlineStr"/>
-      <c r="M207" s="2" t="inlineStr"/>
+      <c r="M207" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
@@ -11287,14 +11555,22 @@
       </c>
       <c r="H208" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I208" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I208" s="2" t="inlineStr">
+        <is>
+          <t>test_int34: _primary_ipv4 None -&gt; _zc stays None; fake Zeroconf: ServiceInfo _http._tcp.local., '&lt;host&gt;._http._tcp.local.', server '&lt;host&gt;.local.', port, path '/'; 2nd start no-op; stop unregisters+closes+resets; register error -&gt; reset; stop swallows errors; UDP connect 10.255.255.255.</t>
+        </is>
+      </c>
       <c r="J208" s="2" t="inlineStr"/>
       <c r="K208" s="2" t="inlineStr"/>
       <c r="L208" s="2" t="inlineStr"/>
-      <c r="M208" s="2" t="inlineStr"/>
+      <c r="M208" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
@@ -11334,14 +11610,22 @@
       </c>
       <c r="H209" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I209" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I209" s="2" t="inlineStr">
+        <is>
+          <t>test_int35: patched load_dotenv called exactly once and env it sets is seen by AppConfig (SECRET_KEY from fake dotenv); source order load_dotenv() before AppConfig.from_env() in create_app.</t>
+        </is>
+      </c>
       <c r="J209" s="2" t="inlineStr"/>
       <c r="K209" s="2" t="inlineStr"/>
       <c r="L209" s="2" t="inlineStr"/>
-      <c r="M209" s="2" t="inlineStr"/>
+      <c r="M209" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
@@ -11381,14 +11665,22 @@
       </c>
       <c r="H210" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I210" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I210" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_models.py::test_seed_data_created_once passes: Settings/SentinelState/SchemaVersion counts ==1 after two boots.</t>
+        </is>
+      </c>
       <c r="J210" s="2" t="inlineStr"/>
       <c r="K210" s="2" t="inlineStr"/>
       <c r="L210" s="2" t="inlineStr"/>
-      <c r="M210" s="2" t="inlineStr"/>
+      <c r="M210" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
@@ -11428,14 +11720,22 @@
       </c>
       <c r="H211" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I211" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_models.py::test_seed_data_created_once passes: ExclusionRule count 4 after two boots; bootstrap.py seeds docksentinel/ollama/portainer/open-webui enabled.</t>
+        </is>
+      </c>
       <c r="J211" s="2" t="inlineStr"/>
       <c r="K211" s="2" t="inlineStr"/>
       <c r="L211" s="2" t="inlineStr"/>
-      <c r="M211" s="2" t="inlineStr"/>
+      <c r="M211" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
@@ -11475,14 +11775,22 @@
       </c>
       <c r="H212" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I212" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I212" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_models.py::test_seed_data_created_once passes: PromptTemplate count 5; bootstrap creates content=default_content, version=1, is_default=True.</t>
+        </is>
+      </c>
       <c r="J212" s="2" t="inlineStr"/>
       <c r="K212" s="2" t="inlineStr"/>
       <c r="L212" s="2" t="inlineStr"/>
-      <c r="M212" s="2" t="inlineStr"/>
+      <c r="M212" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
@@ -11522,14 +11830,22 @@
       </c>
       <c r="H213" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I213" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_ui_routes.py::test_seed_defaults_refreshes_default_prompt passes: default row content refreshed, customised row keeps content but default_content updated.</t>
+        </is>
+      </c>
       <c r="J213" s="2" t="inlineStr"/>
       <c r="K213" s="2" t="inlineStr"/>
       <c r="L213" s="2" t="inlineStr"/>
-      <c r="M213" s="2" t="inlineStr"/>
+      <c r="M213" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
@@ -11569,14 +11885,22 @@
       </c>
       <c r="H214" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I214" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I214" s="2" t="inlineStr">
+        <is>
+          <t>Heredoc run: settings w/o keyword_flush_delay_lines -&gt; 5ca5251db402; with -&gt; 8b3f1a2c9d45; fresh/has alembic_version/relative URL -&gt; ''. Full script under /bin/sh with stubbed alembic: legacy -&gt; stamp &lt;rev&gt;, upgrade head, flask; fresh -&gt; upgrade head only. Docker path not run.</t>
+        </is>
+      </c>
       <c r="J214" s="2" t="inlineStr"/>
       <c r="K214" s="2" t="inlineStr"/>
       <c r="L214" s="2" t="inlineStr"/>
-      <c r="M214" s="2" t="inlineStr"/>
+      <c r="M214" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
@@ -11616,14 +11940,22 @@
       </c>
       <c r="H215" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I215" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I215" s="2" t="inlineStr">
+        <is>
+          <t>Stub run: entrypoint does 'alembic upgrade head' then exec 'python -m flask --app app run --host 0.0.0.0 --port ${APP_PORT:-5000}' (5000 default/8123 set); alembic failure aborts (exit 1). Real alembic upgrade head on temp sqlite -&gt; c3d4e5f6a7b8 (0008, head moved past b2c3d4e5f6a7). Docker not run.</t>
+        </is>
+      </c>
       <c r="J215" s="2" t="inlineStr"/>
       <c r="K215" s="2" t="inlineStr"/>
       <c r="L215" s="2" t="inlineStr"/>
-      <c r="M215" s="2" t="inlineStr"/>
+      <c r="M215" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
@@ -11663,14 +11995,22 @@
       </c>
       <c r="H216" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I216" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I216" s="2" t="inlineStr">
+        <is>
+          <t>Static Dockerfile check OK: python:3.12-slim; apt curl nodejs npm; npm -g @openai/codex @google/gemini-cli; groupadd/useradd uid/gid 1000 appuser; requirements copied+pip installed before app COPY; chmod +x entrypoint; /data chown appuser; USER appuser; EXPOSE 5000. Not built.</t>
+        </is>
+      </c>
       <c r="J216" s="2" t="inlineStr"/>
       <c r="K216" s="2" t="inlineStr"/>
       <c r="L216" s="2" t="inlineStr"/>
-      <c r="M216" s="2" t="inlineStr"/>
+      <c r="M216" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
@@ -11710,14 +12050,22 @@
       </c>
       <c r="H217" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I217" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I217" s="2" t="inlineStr">
+        <is>
+          <t>Static: Dockerfile &amp; docker-compose.yml HEALTHCHECK curl -fsS http://localhost:5000/api/health interval 30s timeout 5s start-period 15s retries 3; unraid uses localhost:80. /api/health returns 200 (app/api/health.py; tests/test_api.py, test_security.py pass). docker inspect not run.</t>
+        </is>
+      </c>
       <c r="J217" s="2" t="inlineStr"/>
       <c r="K217" s="2" t="inlineStr"/>
       <c r="L217" s="2" t="inlineStr"/>
-      <c r="M217" s="2" t="inlineStr"/>
+      <c r="M217" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
@@ -11757,14 +12105,22 @@
       </c>
       <c r="H218" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I218" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I218" s="2" t="inlineStr">
+        <is>
+          <t>Static compose matches: 5050:5000; FLASK_ENV=production; DATABASE_URL=sqlite:////data/docksentinel.db; RUNTIME_LOCK_PATH; START_COORDINATOR=true; DOCKER_HOST unix socket; CLI_BACKENDS_DIR=/app/llm-backends; SECRET_KEY=${SECRET_KEY:?...}; PYTHONUNBUFFERED=1; restart unless-stopped. Not run.</t>
+        </is>
+      </c>
       <c r="J218" s="2" t="inlineStr"/>
       <c r="K218" s="2" t="inlineStr"/>
       <c r="L218" s="2" t="inlineStr"/>
-      <c r="M218" s="2" t="inlineStr"/>
+      <c r="M218" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
@@ -11804,14 +12160,22 @@
       </c>
       <c r="H219" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I219" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I219" s="2" t="inlineStr">
+        <is>
+          <t>Static: both compose files mount /var/run/docker.sock:/var/run/docker.sock:ro and docksentinel_data:/data with named volume declared. docker inspect not run.</t>
+        </is>
+      </c>
       <c r="J219" s="2" t="inlineStr"/>
       <c r="K219" s="2" t="inlineStr"/>
       <c r="L219" s="2" t="inlineStr"/>
-      <c r="M219" s="2" t="inlineStr"/>
+      <c r="M219" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
@@ -11851,14 +12215,22 @@
       </c>
       <c r="H220" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I220" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>Static: both compose files declare extra_hosts 'host.docker.internal:host-gateway'. getent inside container not run.</t>
+        </is>
+      </c>
       <c r="J220" s="2" t="inlineStr"/>
       <c r="K220" s="2" t="inlineStr"/>
       <c r="L220" s="2" t="inlineStr"/>
-      <c r="M220" s="2" t="inlineStr"/>
+      <c r="M220" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
@@ -11898,14 +12270,22 @@
       </c>
       <c r="H221" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I221" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I221" s="2" t="inlineStr">
+        <is>
+          <t>Static unraid example: hostname docksentinel; group_add '281'; sysctl net.ipv4.ip_unprivileged_port_start=80; APP_PORT=80, MDNS_ENABLED=true, MDNS_HOSTNAME=docksentinel, MDNS_PORT=80; networks br0 external with ipv4_address placeholder 10.0.0.X; healthcheck port 80. Not deployed.</t>
+        </is>
+      </c>
       <c r="J221" s="2" t="inlineStr"/>
       <c r="K221" s="2" t="inlineStr"/>
       <c r="L221" s="2" t="inlineStr"/>
-      <c r="M221" s="2" t="inlineStr"/>
+      <c r="M221" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
@@ -11945,14 +12325,22 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I222" s="2" t="inlineStr">
+        <is>
+          <t>alembic history on temp sqlite: 5ca5251db402 -&gt; 8b3f1a2c9d45 -&gt; a71f0c2d3e10 -&gt; b82e1f4a5c66 -&gt; c9a0d7f2e411 -&gt; a1b2c3d4e5f6 -&gt; b2c3d4e5f6a7 -&gt; c3d4e5f6a7b8 (single head; story predates 0008 llm_extra_request_json). 0001 creates the 7 base tables. test_migration_0006_ids passes.</t>
+        </is>
+      </c>
       <c r="J222" s="2" t="inlineStr"/>
       <c r="K222" s="2" t="inlineStr"/>
       <c r="L222" s="2" t="inlineStr"/>
-      <c r="M222" s="2" t="inlineStr"/>
+      <c r="M222" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
@@ -11992,14 +12380,22 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I223" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>alembic upgrade 8b3f1a2c9d45: settings gains llm_transport 'api', cli_backend 'codex', cli_timeout_seconds 120, cli_max_retries 1, dedup_window_seconds 300, container_rate_limit_count 10, container_rate_limit_window_seconds 3600, keyword_flush_delay_lines 5 (NOT NULL); downgrade removes them.</t>
+        </is>
+      </c>
       <c r="J223" s="2" t="inlineStr"/>
       <c r="K223" s="2" t="inlineStr"/>
       <c r="L223" s="2" t="inlineStr"/>
-      <c r="M223" s="2" t="inlineStr"/>
+      <c r="M223" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
@@ -12039,14 +12435,22 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I224" s="2" t="inlineStr">
+        <is>
+          <t>alembic upgrade b82e1f4a5c66: settings.chunk_coalesce_window_seconds NOT NULL default '0'; local_issues created with status default 'open', discussion default ''; indexes ix_local_issues_event_id/_status/_telegram_message_id; downgrade to a71f0c2d3e10 drops table+indexes.</t>
+        </is>
+      </c>
       <c r="J224" s="2" t="inlineStr"/>
       <c r="K224" s="2" t="inlineStr"/>
       <c r="L224" s="2" t="inlineStr"/>
-      <c r="M224" s="2" t="inlineStr"/>
+      <c r="M224" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
@@ -12086,14 +12490,22 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I225" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I225" s="2" t="inlineStr">
+        <is>
+          <t>alembic upgrade head: local_issues.llm_model VARCHAR(255) nullable; settings alert_min_classification 'critical', event_retention_days 14, restart_alert_count 3, restart_alert_window_minutes 10; downgrade to b82e1f4a5c66 removes them all.</t>
+        </is>
+      </c>
       <c r="J225" s="2" t="inlineStr"/>
       <c r="K225" s="2" t="inlineStr"/>
       <c r="L225" s="2" t="inlineStr"/>
-      <c r="M225" s="2" t="inlineStr"/>
+      <c r="M225" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
@@ -12133,14 +12545,22 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I226" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I226" s="2" t="inlineStr">
+        <is>
+          <t>env.py: DATABASE_URL=sqlite:///&lt;tmp&gt;/e2.db creates file there; temp ini sqlalchemy.url wins over DATABASE_URL; alembic.ini has no url; upgrade --sql offline succeeds and offline downgrade reports batch-mode reflection limit (render_as_batch=True in both modes confirmed).</t>
+        </is>
+      </c>
       <c r="J226" s="2" t="inlineStr"/>
       <c r="K226" s="2" t="inlineStr"/>
       <c r="L226" s="2" t="inlineStr"/>
-      <c r="M226" s="2" t="inlineStr"/>
+      <c r="M226" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
@@ -12180,14 +12600,22 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I227" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>After upgrade head, alembic compare_metadata(db.metadata) -&gt; 0 diffs; PRAGMA table_info(local_issues) column set == LocalIssue.__table__.columns (14 cols); 3 ix_local_issues_* indexes present; enums open/discussing/rejected/closed &amp; approve/reject/discuss.</t>
+        </is>
+      </c>
       <c r="J227" s="2" t="inlineStr"/>
       <c r="K227" s="2" t="inlineStr"/>
       <c r="L227" s="2" t="inlineStr"/>
-      <c r="M227" s="2" t="inlineStr"/>
+      <c r="M227" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
@@ -12227,14 +12655,22 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I228" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>test_int54: GET /api/issues?status=bogus -&gt; 400 {'error':'invalid status'}; valid statuses 200; PATCH {'status':'closed'} -&gt; row closed; PATCH invalid status leaves it closed.</t>
+        </is>
+      </c>
       <c r="J228" s="2" t="inlineStr"/>
       <c r="K228" s="2" t="inlineStr"/>
       <c r="L228" s="2" t="inlineStr"/>
-      <c r="M228" s="2" t="inlineStr"/>
+      <c r="M228" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
@@ -12274,14 +12710,22 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I229" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I229" s="2" t="inlineStr">
+        <is>
+          <t>Static: README quick start (export SECRET_KEY=$(openssl rand -hex 32); docker compose up -d --build; http://localhost:5050) matches compose 5050:5000 and SECRET_KEY ${SECRET_KEY:?} requirement. Not run against docker.</t>
+        </is>
+      </c>
       <c r="J229" s="2" t="inlineStr"/>
       <c r="K229" s="2" t="inlineStr"/>
       <c r="L229" s="2" t="inlineStr"/>
-      <c r="M229" s="2" t="inlineStr"/>
+      <c r="M229" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
@@ -12321,14 +12765,22 @@
       </c>
       <c r="H230" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I230" s="2" t="inlineStr"/>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Static: README documents BotFather token/chat id, Test Telegram, enable Sentinel, Reject/Approve/Discuss, long-polling no webhook, group privacy-mode note; matches app/api/telegram.py and bot. Test endpoint failure path verified (400); live delivery needs Telegram.</t>
+        </is>
+      </c>
       <c r="J230" s="2" t="inlineStr"/>
       <c r="K230" s="2" t="inlineStr"/>
       <c r="L230" s="2" t="inlineStr"/>
-      <c r="M230" s="2" t="inlineStr"/>
+      <c r="M230" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
@@ -12368,14 +12820,22 @@
       </c>
       <c r="H231" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I231" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I231" s="2" t="inlineStr">
+        <is>
+          <t>test_int57: CLI_BACKENDS_DIR=tmp with codex.sh echoing JSON verdict; PUT /api/settings {llm_transport:'cli',cli_backend:'codex'} 200; POST /api/settings/test-llm 200 ok=true; llm-backends/{codex,claude,gemini,ollama}.sh exist and are executable. README steps match.</t>
+        </is>
+      </c>
       <c r="J231" s="2" t="inlineStr"/>
       <c r="K231" s="2" t="inlineStr"/>
       <c r="L231" s="2" t="inlineStr"/>
-      <c r="M231" s="2" t="inlineStr"/>
+      <c r="M231" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
@@ -12415,14 +12875,22 @@
       </c>
       <c r="H232" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I232" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I232" s="2" t="inlineStr">
+        <is>
+          <t>README env table vs code: SECRET_KEY rules, DATABASE_URL/RUNTIME_LOCK_PATH dev defaults, START_COORDINATOR true, CLI_BACKENDS_DIR, APP_PORT 5000 (entrypoint), MDNS_* (app/__init__.py), BASIC_AUTH_* (security.py, test ok), DOCKSENTINEL_CLI_ENV_PASSTHROUGH; DOCKER_HOST via docker.from_env().</t>
+        </is>
+      </c>
       <c r="J232" s="2" t="inlineStr"/>
       <c r="K232" s="2" t="inlineStr"/>
       <c r="L232" s="2" t="inlineStr"/>
-      <c r="M232" s="2" t="inlineStr"/>
+      <c r="M232" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
@@ -12462,12 +12930,12 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
         <is>
-          <t>Followed README local-dev steps on a fresh clone: `flask --app app run` crashed with 'no such table: schema_version' — create_all only runs under TESTING; alembic must be run first but the README only mentions it 'after dependency changes'.</t>
+          <t>Fresh copy of repo (with data/.gitkeep): `alembic upgrade head` without DATABASE_URL creates ./data/docksentinel.db at c3d4e5f6a7b8. `pytest -q` in repo: 137 passed, coverage 83.75% &gt;= 80% gate (pytest.ini). Minor: README says '46 tests'.</t>
         </is>
       </c>
       <c r="J233" s="2" t="inlineStr">
@@ -12521,14 +12989,22 @@
       </c>
       <c r="H234" s="2" t="inlineStr">
         <is>
-          <t>Not tested</t>
-        </is>
-      </c>
-      <c r="I234" s="2" t="inlineStr"/>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I234" s="2" t="inlineStr">
+        <is>
+          <t>Static .github/workflows/ci.yml: name CI; on push branches ['**'] and pull_request; ubuntu-latest; setup-python 3.12 cache pip; pip install -r requirements.txt; `python -m pytest -q` with TESTING=true START_COORDINATOR=false. Replicated locally: 137 passed.</t>
+        </is>
+      </c>
       <c r="J234" s="2" t="inlineStr"/>
       <c r="K234" s="2" t="inlineStr"/>
       <c r="L234" s="2" t="inlineStr"/>
-      <c r="M234" s="2" t="inlineStr"/>
+      <c r="M234" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="inlineStr">

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -10341,7 +10341,7 @@
       </c>
       <c r="H186" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
@@ -10354,7 +10354,11 @@
           <t>Expected messages[0].content == SENTINEL_SYSTEM prompt; observed 'You are an SRE assistant helping triage Docker container issues.' every call. app/services/telegram_bot.py:264 calls self.prompt_repo.get(PromptKey.SENTINEL_SYSTEM) but app/repositories/prompts.py:7 only defines get_by_key -&gt; AttributeError caught at :265.</t>
         </is>
       </c>
-      <c r="K186" s="2" t="inlineStr"/>
+      <c r="K186" s="2" t="inlineStr">
+        <is>
+          <t>telegram_bot._ask_llm: get_by_key + fallback only when missing; regression test added</t>
+        </is>
+      </c>
       <c r="L186" s="2" t="inlineStr"/>
       <c r="M186" s="2" t="inlineStr">
         <is>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -12934,7 +12934,7 @@
       </c>
       <c r="H233" s="2" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I233" s="2" t="inlineStr">
@@ -12947,7 +12947,11 @@
           <t>README.md:244-250 order/wording; app/__init__.py:70-72 (create_all gated on TESTING). Expected: first-run works or README says run `alembic upgrade head` BEFORE first `flask run`.</t>
         </is>
       </c>
-      <c r="K233" s="2" t="inlineStr"/>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>README local-dev: run alembic upgrade head before first flask run</t>
+        </is>
+      </c>
       <c r="L233" s="2" t="inlineStr"/>
       <c r="M233" s="2" t="inlineStr">
         <is>
@@ -13048,7 +13052,7 @@
       </c>
       <c r="H235" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I235" s="2" t="inlineStr">
@@ -13061,7 +13065,11 @@
           <t>Templates print datetime objects directly (str()) → microseconds. Add a Jinja filter `dt` → strftime('%Y-%m-%d %H:%M:%S') and apply everywhere.</t>
         </is>
       </c>
-      <c r="K235" s="2" t="inlineStr"/>
+      <c r="K235" s="2" t="inlineStr">
+        <is>
+          <t>__init__: |dt Jinja filter applied in dashboard/insights/issues/reports</t>
+        </is>
+      </c>
       <c r="L235" s="2" t="inlineStr"/>
       <c r="M235" s="2" t="inlineStr">
         <is>
@@ -13107,7 +13115,7 @@
       </c>
       <c r="H236" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
@@ -13120,7 +13128,11 @@
           <t>insights.html severity badge falls back to 'noise' when classification is None.</t>
         </is>
       </c>
-      <c r="K236" s="2" t="inlineStr"/>
+      <c r="K236" s="2" t="inlineStr">
+        <is>
+          <t>insights.html: '—' for unclassified, 'error' badge for llm/parse errors</t>
+        </is>
+      </c>
       <c r="L236" s="2" t="inlineStr"/>
       <c r="M236" s="2" t="inlineStr">
         <is>
@@ -13166,7 +13178,7 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
@@ -13179,7 +13191,11 @@
           <t>issues.html renders issue.body in &lt;pre&gt;; route doesn't call render_markdown.</t>
         </is>
       </c>
-      <c r="K237" s="2" t="inlineStr"/>
+      <c r="K237" s="2" t="inlineStr">
+        <is>
+          <t>routes.issues_page passes selected_body_html via render_markdown; template uses .prose</t>
+        </is>
+      </c>
       <c r="L237" s="2" t="inlineStr"/>
       <c r="M237" s="2" t="inlineStr">
         <is>
@@ -13225,7 +13241,7 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
@@ -13238,7 +13254,11 @@
           <t>dashboard checklist criterion too weak.</t>
         </is>
       </c>
-      <c r="K238" s="2" t="inlineStr"/>
+      <c r="K238" s="2" t="inlineStr">
+        <is>
+          <t>dashboard checklist llm_ready = state.llm_last_test_ok_at set (recorded on successful test-llm)</t>
+        </is>
+      </c>
       <c r="L238" s="2" t="inlineStr"/>
       <c r="M238" s="2" t="inlineStr">
         <is>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -3433,7 +3433,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Fixed - retest</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3446,7 +3446,11 @@
           <t>Expected every empty state to have a CTA link/button; observed none in app/templates/exclusions.html:53-59 (empty state has only text; add form is above) and app/templates/issues.html:47-54 when no status filter (no link/button). Also dashboard 'No events yet' has no CTA when sentinel is enabled (dashboard.html:170-179).</t>
         </is>
       </c>
-      <c r="K54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>empty states now carry a CTA (Add a pattern / Browse events / Open events)</t>
+        </is>
+      </c>
       <c r="L54" s="2" t="inlineStr"/>
       <c r="M54" s="2" t="inlineStr">
         <is>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -3433,7 +3433,7 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
@@ -3451,7 +3451,11 @@
           <t>empty states now carry a CTA (Add a pattern / Browse events / Open events)</t>
         </is>
       </c>
-      <c r="L54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>CTA present in every empty state (verified issues?status=closed 'Show all'; exclusions template has 'Add a pattern')</t>
+        </is>
+      </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -6741,7 +6745,7 @@
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -6759,7 +6763,11 @@
           <t>__init__.py: ISOJSONProvider — datetimes serialised ISO-8601</t>
         </is>
       </c>
-      <c r="L114" s="2" t="inlineStr"/>
+      <c r="L114" s="2" t="inlineStr">
+        <is>
+          <t>updated_at now ISO-8601 (2026-08-15T20:36:56)</t>
+        </is>
+      </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -6804,7 +6812,7 @@
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -6822,7 +6830,11 @@
           <t>security.py: explicit set (Flask predefines key as None so setdefault was a no-op)</t>
         </is>
       </c>
-      <c r="L115" s="2" t="inlineStr"/>
+      <c r="L115" s="2" t="inlineStr">
+        <is>
+          <t>SESSION_COOKIE_SAMESITE == 'Lax'</t>
+        </is>
+      </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -9735,7 +9747,7 @@
       </c>
       <c r="H168" s="2" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I168" s="2" t="inlineStr">
@@ -9753,7 +9765,11 @@
           <t>commit: omit Authorization when key blank; include server error detail</t>
         </is>
       </c>
-      <c r="L168" s="2" t="inlineStr"/>
+      <c r="L168" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_llm_client.py: no Authorization header for blank key; extra_body merged</t>
+        </is>
+      </c>
       <c r="M168" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -11173,7 +11189,7 @@
       </c>
       <c r="H194" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I194" s="2" t="inlineStr">
@@ -11191,7 +11207,11 @@
           <t>telegram_bot._ask_llm: get_by_key + fallback only when missing; regression test added</t>
         </is>
       </c>
-      <c r="L194" s="2" t="inlineStr"/>
+      <c r="L194" s="2" t="inlineStr">
+        <is>
+          <t>regression test passes: bot uses SENTINEL_SYSTEM content, single system message</t>
+        </is>
+      </c>
       <c r="M194" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -13766,7 +13786,7 @@
       </c>
       <c r="H241" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I241" s="2" t="inlineStr">
@@ -13784,7 +13804,11 @@
           <t>README local-dev: run alembic upgrade head before first flask run</t>
         </is>
       </c>
-      <c r="L241" s="2" t="inlineStr"/>
+      <c r="L241" s="2" t="inlineStr">
+        <is>
+          <t>README now says alembic upgrade head before first flask run</t>
+        </is>
+      </c>
       <c r="M241" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -13884,7 +13908,7 @@
       </c>
       <c r="H243" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
@@ -13902,7 +13926,11 @@
           <t>__init__: |dt Jinja filter applied in dashboard/insights/issues/reports</t>
         </is>
       </c>
-      <c r="L243" s="2" t="inlineStr"/>
+      <c r="L243" s="2" t="inlineStr">
+        <is>
+          <t>/insights times render 'YYYY-MM-DD HH:MM:SS'</t>
+        </is>
+      </c>
       <c r="M243" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -13947,7 +13975,7 @@
       </c>
       <c r="H244" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I244" s="2" t="inlineStr">
@@ -13965,7 +13993,11 @@
           <t>insights.html: '—' for unclassified, 'error' badge for llm/parse errors</t>
         </is>
       </c>
-      <c r="L244" s="2" t="inlineStr"/>
+      <c r="L244" s="2" t="inlineStr">
+        <is>
+          <t>llm_error row shows 'error' badge; unclassified '—'</t>
+        </is>
+      </c>
       <c r="M244" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -14010,7 +14042,7 @@
       </c>
       <c r="H245" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I245" s="2" t="inlineStr">
@@ -14028,7 +14060,11 @@
           <t>routes.issues_page passes selected_body_html via render_markdown; template uses .prose</t>
         </is>
       </c>
-      <c r="L245" s="2" t="inlineStr"/>
+      <c r="L245" s="2" t="inlineStr">
+        <is>
+          <t>/issues?id=2 renders &lt;h1&gt; from body markdown</t>
+        </is>
+      </c>
       <c r="M245" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -14073,7 +14109,7 @@
       </c>
       <c r="H246" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I246" s="2" t="inlineStr">
@@ -14091,7 +14127,11 @@
           <t>dashboard checklist llm_ready = state.llm_last_test_ok_at set (recorded on successful test-llm)</t>
         </is>
       </c>
-      <c r="L246" s="2" t="inlineStr"/>
+      <c r="L246" s="2" t="inlineStr">
+        <is>
+          <t>pristine state: 0 checklist items ticked; ticks after test-llm succeeds</t>
+        </is>
+      </c>
       <c r="M246" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$246</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$248</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M246"/>
+  <dimension ref="A1:M248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14138,10 +14138,128 @@
         </is>
       </c>
     </row>
+    <row r="247">
+      <c r="A247" s="2" t="inlineStr">
+        <is>
+          <t>OPS-01</t>
+        </is>
+      </c>
+      <c r="B247" s="2" t="inlineStr">
+        <is>
+          <t>Ops: Live deploy</t>
+        </is>
+      </c>
+      <c r="C247" s="2" t="inlineStr">
+        <is>
+          <t>Secrets never appear in container logs</t>
+        </is>
+      </c>
+      <c r="D247" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want bot tokens/API keys never written to docker logs.</t>
+        </is>
+      </c>
+      <c r="E247" s="2" t="inlineStr">
+        <is>
+          <t>Telegram HTTP errors are logged without the token URL; LLM errors don't include api keys.</t>
+        </is>
+      </c>
+      <c r="F247" s="2" t="inlineStr">
+        <is>
+          <t>app/services/telegram.py, telegram_bot.py</t>
+        </is>
+      </c>
+      <c r="G247" s="2" t="inlineStr">
+        <is>
+          <t>docker logs docksentinel | grep -c 'bot[0-9]*:' → 0 while a 409/401 is happening.</t>
+        </is>
+      </c>
+      <c r="H247" s="2" t="inlineStr">
+        <is>
+          <t>Fixed - retest</t>
+        </is>
+      </c>
+      <c r="I247" s="2" t="inlineStr">
+        <is>
+          <t>Live logs showed full bot token in getUpdates 409 traceback</t>
+        </is>
+      </c>
+      <c r="J247" s="2" t="inlineStr">
+        <is>
+          <t>telegram.get_updates raised RuntimeError(str(exc)) incl. URL with token; bot logged traceback every 5s</t>
+        </is>
+      </c>
+      <c r="K247" s="2" t="inlineStr">
+        <is>
+          <t>redact + one-line warning</t>
+        </is>
+      </c>
+      <c r="L247" s="2" t="inlineStr"/>
+      <c r="M247" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
+        <is>
+          <t>OPS-02</t>
+        </is>
+      </c>
+      <c r="B248" s="2" t="inlineStr">
+        <is>
+          <t>Ops: Live deploy</t>
+        </is>
+      </c>
+      <c r="C248" s="2" t="inlineStr">
+        <is>
+          <t>Legacy volume upgrade on Unraid</t>
+        </is>
+      </c>
+      <c r="D248" s="2" t="inlineStr">
+        <is>
+          <t>As an operator upgrading the old April deployment I want the container to come up healthy on the existing data volume.</t>
+        </is>
+      </c>
+      <c r="E248" s="2" t="inlineStr">
+        <is>
+          <t>Compose up on Tower with volume docksentinel_docksentinel_data → migrations 0006-0009 apply, health 200 at http://10.0.0.220/api/health.</t>
+        </is>
+      </c>
+      <c r="F248" s="2" t="inlineStr">
+        <is>
+          <t>docker-entrypoint.sh, docker-compose.unraid.example.yml</t>
+        </is>
+      </c>
+      <c r="G248" s="2" t="inlineStr">
+        <is>
+          <t>docker logs docksentinel | grep 'Running upgrade'; curl http://10.0.0.220/api/health</t>
+        </is>
+      </c>
+      <c r="H248" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I248" s="2" t="inlineStr">
+        <is>
+          <t>Legacy volume: stamp path not needed (alembic_version existed at c9a0d7f2e411); 0006→0009 applied; healthy</t>
+        </is>
+      </c>
+      <c r="J248" s="2" t="inlineStr"/>
+      <c r="K248" s="2" t="inlineStr"/>
+      <c r="L248" s="2" t="inlineStr"/>
+      <c r="M248" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M246"/>
+  <autoFilter ref="A1:M248"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H246" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not tested,Pass,Fail,Fixed - retest,Pass (after fix),Blocked (needs docker/LLM/Telegram),Won't fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14155,7 +14273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -14185,7 +14303,7 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$246,A2)</f>
+        <f>COUNTIF(Stories!$H$2:$H$248,A2)</f>
         <v/>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -14198,7 +14316,7 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$246,A3)</f>
+        <f>COUNTIF(Stories!$H$2:$H$248,A3)</f>
         <v/>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -14211,7 +14329,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$246,A4)</f>
+        <f>COUNTIF(Stories!$H$2:$H$248,A4)</f>
         <v/>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -14224,7 +14342,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$246,A5)</f>
+        <f>COUNTIF(Stories!$H$2:$H$248,A5)</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -14237,7 +14355,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$246,A6)</f>
+        <f>COUNTIF(Stories!$H$2:$H$248,A6)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -14250,7 +14368,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$246,A7)</f>
+        <f>COUNTIF(Stories!$H$2:$H$248,A7)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -14263,7 +14381,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$246,A8)</f>
+        <f>COUNTIF(Stories!$H$2:$H$248,A8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -14276,7 +14394,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTA(Stories!$A$2:$A$246)</f>
+        <f>COUNTA(Stories!$A$2:$A$248)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -14340,15 +14458,15 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A14)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A14)</f>
         <v/>
       </c>
       <c r="C14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A14,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A14,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A14,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A14,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A14,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A14,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14359,15 +14477,15 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A15)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A15)</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A15,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A15,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A15,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A15,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A15,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A15,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14378,15 +14496,15 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A16)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A16)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A16,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A16,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A16,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A16,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A16,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A16,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14397,15 +14515,15 @@
         </is>
       </c>
       <c r="B17" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A17)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A17)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A17,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A17,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A17,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A17,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A17,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A17,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14416,15 +14534,15 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A18)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A18)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A18,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A18,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A18,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A18,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A18,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A18,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14435,15 +14553,15 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A19)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A19)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A19,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A19,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A19,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A19,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A19,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A19,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14454,15 +14572,15 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A20)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A20)</f>
         <v/>
       </c>
       <c r="C20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A20,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A20,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A20,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A20,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A20,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A20,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14473,15 +14591,15 @@
         </is>
       </c>
       <c r="B21" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A21)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A21)</f>
         <v/>
       </c>
       <c r="C21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A21,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A21,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A21,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A21,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A21,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A21,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14492,15 +14610,15 @@
         </is>
       </c>
       <c r="B22" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A22)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A22)</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A22,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A22,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A22,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A22,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A22,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A22,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14511,15 +14629,15 @@
         </is>
       </c>
       <c r="B23" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A23)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A23)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A23,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A23,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A23,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A23,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A23,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A23,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14530,15 +14648,15 @@
         </is>
       </c>
       <c r="B24" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A24)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A24)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A24,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A24,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A24,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A24,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A24,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A24,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14549,15 +14667,15 @@
         </is>
       </c>
       <c r="B25" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A25)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A25)</f>
         <v/>
       </c>
       <c r="C25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A25,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A25,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A25,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A25,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A25,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A25,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14568,15 +14686,15 @@
         </is>
       </c>
       <c r="B26" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A26)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A26)</f>
         <v/>
       </c>
       <c r="C26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A26,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A26,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A26,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A26,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A26,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A26,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14587,15 +14705,15 @@
         </is>
       </c>
       <c r="B27" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A27)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A27)</f>
         <v/>
       </c>
       <c r="C27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A27,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A27,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A27,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A27,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A27,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A27,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14606,15 +14724,15 @@
         </is>
       </c>
       <c r="B28" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A28)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A28)</f>
         <v/>
       </c>
       <c r="C28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A28,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A28,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A28,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A28,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A28,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A28,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14625,15 +14743,15 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A29)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A29)</f>
         <v/>
       </c>
       <c r="C29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A29,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A29,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A29,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A29,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A29,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A29,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14644,15 +14762,15 @@
         </is>
       </c>
       <c r="B30" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A30)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A30)</f>
         <v/>
       </c>
       <c r="C30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A30,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A30,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A30,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A30,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A30,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A30,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14663,15 +14781,15 @@
         </is>
       </c>
       <c r="B31" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A31)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A31)</f>
         <v/>
       </c>
       <c r="C31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A31,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A31,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A31,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A31,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A31,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A31,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14682,376 +14800,395 @@
         </is>
       </c>
       <c r="B32" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A32)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A32)</f>
         <v/>
       </c>
       <c r="C32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A32,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A32,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A32,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A32,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A32,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A32,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Ops: Migrations</t>
+          <t>Ops: Live deploy</t>
         </is>
       </c>
       <c r="B33" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A33)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A33)</f>
         <v/>
       </c>
       <c r="C33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A33,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A33,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A33,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A33,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A33,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A33,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Ops: Onboarding</t>
+          <t>Ops: Migrations</t>
         </is>
       </c>
       <c r="B34" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A34)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A34)</f>
         <v/>
       </c>
       <c r="C34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A34,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A34,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A34,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A34,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A34,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A34,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Alerts</t>
+          <t>Ops: Onboarding</t>
         </is>
       </c>
       <c r="B35" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A35)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A35)</f>
         <v/>
       </c>
       <c r="C35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A35,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A35,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A35,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A35,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A35,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A35,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Buffer</t>
+          <t>Pipeline: Alerts</t>
         </is>
       </c>
       <c r="B36" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A36)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A36)</f>
         <v/>
       </c>
       <c r="C36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A36,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A36,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A36,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A36,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A36,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A36,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: LLM</t>
+          <t>Pipeline: Buffer</t>
         </is>
       </c>
       <c r="B37" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A37)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A37)</f>
         <v/>
       </c>
       <c r="C37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A37,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A37,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A37,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A37,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A37,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A37,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Prefilter</t>
+          <t>Pipeline: LLM</t>
         </is>
       </c>
       <c r="B38" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A38)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A38)</f>
         <v/>
       </c>
       <c r="C38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A38,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A38,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A38,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A38,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A38,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A38,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Scheduler</t>
+          <t>Pipeline: Prefilter</t>
         </is>
       </c>
       <c r="B39" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A39)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A39)</f>
         <v/>
       </c>
       <c r="C39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A39,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A39,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A39,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A39,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A39,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A39,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Triage</t>
+          <t>Pipeline: Scheduler</t>
         </is>
       </c>
       <c r="B40" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A40)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A40)</f>
         <v/>
       </c>
       <c r="C40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A40,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A40,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A40,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A40,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A40,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A40,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Watcher</t>
+          <t>Pipeline: Triage</t>
         </is>
       </c>
       <c r="B41" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A41)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A41)</f>
         <v/>
       </c>
       <c r="C41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A41,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A41,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A41,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A41,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A41,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A41,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>UI: Cross-cutting</t>
+          <t>Pipeline: Watcher</t>
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A42)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A42)</f>
         <v/>
       </c>
       <c r="C42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A42,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A42,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A42,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A42,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A42,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A42,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>UI: Dashboard</t>
+          <t>UI: Cross-cutting</t>
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A43)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A43)</f>
         <v/>
       </c>
       <c r="C43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A43,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A43,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A43,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A43,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A43,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A43,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>UI: Events</t>
+          <t>UI: Dashboard</t>
         </is>
       </c>
       <c r="B44" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A44)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A44)</f>
         <v/>
       </c>
       <c r="C44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A44,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A44,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A44,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A44,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A44,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A44,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>UI: Exclusions</t>
+          <t>UI: Events</t>
         </is>
       </c>
       <c r="B45" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A45)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A45)</f>
         <v/>
       </c>
       <c r="C45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A45,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A45,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A45,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A45,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A45,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A45,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>UI: Global</t>
+          <t>UI: Exclusions</t>
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A46)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A46)</f>
         <v/>
       </c>
       <c r="C46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A46,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A46,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A46,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A46,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A46,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A46,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>UI: Issues</t>
+          <t>UI: Global</t>
         </is>
       </c>
       <c r="B47" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A47)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A47)</f>
         <v/>
       </c>
       <c r="C47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A47,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A47,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A47,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A47,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A47,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A47,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>UI: Prompts</t>
+          <t>UI: Issues</t>
         </is>
       </c>
       <c r="B48" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A48)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A48)</f>
         <v/>
       </c>
       <c r="C48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A48,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A48,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A48,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A48,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A48,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A48,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>UI: Reports</t>
+          <t>UI: Prompts</t>
         </is>
       </c>
       <c r="B49" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A49)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A49)</f>
         <v/>
       </c>
       <c r="C49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A49,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A49,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A49,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A49,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A49,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A49,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>UI: Settings</t>
+          <t>UI: Reports</t>
         </is>
       </c>
       <c r="B50" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A50)</f>
+        <f>COUNTIF(Stories!$B$2:$B$248,A50)</f>
         <v/>
       </c>
       <c r="C50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A50,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A50,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A50,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A50,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A50,Stories!$H$2:$H$246,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$248,A50,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
+          <t>UI: Settings</t>
+        </is>
+      </c>
+      <c r="B51" s="4">
+        <f>COUNTIF(Stories!$B$2:$B$248,A51)</f>
+        <v/>
+      </c>
+      <c r="C51" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$248,A51,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A51,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <v/>
+      </c>
+      <c r="D51" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$248,A51,Stories!$H$2:$H$248,"Fail")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
           <t>UI: Shell</t>
         </is>
       </c>
-      <c r="B51" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$246,A51)</f>
+      <c r="B52" s="4">
+        <f>COUNTIF(Stories!$B$2:$B$248,A52)</f>
         <v/>
       </c>
-      <c r="C51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A51,Stories!$H$2:$H$246,"Pass")+COUNTIFS(Stories!$B$2:$B$246,A51,Stories!$H$2:$H$246,"Pass (after fix)")</f>
+      <c r="C52" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$248,A52,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A52,Stories!$H$2:$H$248,"Pass (after fix)")</f>
         <v/>
       </c>
-      <c r="D51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$246,A51,Stories!$H$2:$H$246,"Fail")</f>
+      <c r="D52" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$248,A52,Stories!$H$2:$H$248,"Fail")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$248</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$253</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M248"/>
+  <dimension ref="A1:M253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -4875,12 +4875,12 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>No reachable LLM. POST /api/settings/test-llm -&gt; 400 {"ok":false,"error":"[Errno 8] nodename nor servname provided, or not known"} (fallback passes). Success path unverified.</t>
+          <t>Live: POST /api/settings/test-llm vs Ornith @10.0.0.79 → 200 {ok:true} in 0.26s</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
@@ -5700,17 +5700,29 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>No docker. {container:'  '} -&gt; 400 'String should have at least 1 character'; {} -&gt; 400 'Field required'; nonexistent and excluded ('portainer') containers -&gt; 500 {error:docker connection error}. Exclusion 400 path needs docker (name resolved via docker first).</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr"/>
-      <c r="K95" s="2" t="inlineStr"/>
-      <c r="L95" s="2" t="inlineStr"/>
+          <t>Live: analyze-now Dozzle first returned skipped (prefilter) → fixed to force LLM; now analyzed/noise via Ornith. Excluded container → 400.</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr">
+        <is>
+          <t>process_chunk keyword-gated manual analysis despite UI promising bypass</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>force=True path</t>
+        </is>
+      </c>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>analyzed noise Ornith-1.0-35B-4bit</t>
+        </is>
+      </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -6085,12 +6097,12 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>No LLM. POST /api/reports/generate -&gt; 201 report object with status 'llm_error', error '[Errno 8] nodename nor servname...', markdown_content fallback template, model llama3, prompt_version 1. Failure path OK; LLM content path unverified.</t>
+          <t>Live: POST /api/reports/generate → 201 status generated, model Ornith, 2250 chars</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
@@ -6140,12 +6152,12 @@
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>No Telegram creds. POST /api/telegram/test -&gt; 400 {"ok":false,"error":"telegram credentials are not configured"} (fallback passes).</t>
+          <t>Send path verified live: restart-storm alert delivered (alert_sent=true) via stored token/chat</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
@@ -6195,17 +6207,29 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>No Ollama. ?base_url=http://127.0.0.1:9 -&gt; 502 {"ok":false,"error":"could not reach an Ollama server at that base_url"}; no param (stored URL) -&gt; 502 same generic error. Success shape unverified.</t>
-        </is>
-      </c>
-      <c r="J104" s="2" t="inlineStr"/>
-      <c r="K104" s="2" t="inlineStr"/>
-      <c r="L104" s="2" t="inlineStr"/>
+          <t>Non-Ollama host returned ok:true/[] → now 502 generic</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr">
+        <is>
+          <t>404 body swallowed; no raise_for_status</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>raise_for_status + shape check</t>
+        </is>
+      </c>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>502 could not reach an Ollama server</t>
+        </is>
+      </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>
@@ -6525,12 +6549,12 @@
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
         <is>
-          <t>No LLM. try-llm on 999999 -&gt; 404 {"error":"not found"}; on seeded issue with base_url http://127.0.0.1:9/v1 -&gt; 400 {"ok":false,"error":"[Errno 61] Connection refused"}. Success 200 shape unverified.</t>
+          <t>Live: try-llm on issue #7 → ok, Ornith, 1026ms, sensible answer</t>
         </is>
       </c>
       <c r="J110" s="2" t="inlineStr"/>
@@ -12741,12 +12765,12 @@
       </c>
       <c r="H222" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I222" s="2" t="inlineStr">
         <is>
-          <t>Heredoc run: settings w/o keyword_flush_delay_lines -&gt; 5ca5251db402; with -&gt; 8b3f1a2c9d45; fresh/has alembic_version/relative URL -&gt; ''. Full script under /bin/sh with stubbed alembic: legacy -&gt; stamp &lt;rev&gt;, upgrade head, flask; fresh -&gt; upgrade head only. Docker path not run.</t>
+          <t>Live volume already had alembic_version (c9a0d7f2e411) so no stamp; 0006→0009 applied. Stamp branch verified locally with simulated legacy DB.</t>
         </is>
       </c>
       <c r="J222" s="2" t="inlineStr"/>
@@ -12796,12 +12820,12 @@
       </c>
       <c r="H223" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I223" s="2" t="inlineStr">
         <is>
-          <t>Stub run: entrypoint does 'alembic upgrade head' then exec 'python -m flask --app app run --host 0.0.0.0 --port ${APP_PORT:-5000}' (5000 default/8123 set); alembic failure aborts (exit 1). Real alembic upgrade head on temp sqlite -&gt; c3d4e5f6a7b8 (0008, head moved past b2c3d4e5f6a7). Docker not run.</t>
+          <t>docker logs: alembic upgrades then Flask on :80; healthy</t>
         </is>
       </c>
       <c r="J223" s="2" t="inlineStr"/>
@@ -12851,12 +12875,12 @@
       </c>
       <c r="H224" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I224" s="2" t="inlineStr">
         <is>
-          <t>Static Dockerfile check OK: python:3.12-slim; apt curl nodejs npm; npm -g @openai/codex @google/gemini-cli; groupadd/useradd uid/gid 1000 appuser; requirements copied+pip installed before app COPY; chmod +x entrypoint; /data chown appuser; USER appuser; EXPOSE 5000. Not built.</t>
+          <t>docker exec id -u → 1000; codex+gemini on PATH</t>
         </is>
       </c>
       <c r="J224" s="2" t="inlineStr"/>
@@ -12906,12 +12930,12 @@
       </c>
       <c r="H225" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>Static: Dockerfile &amp; docker-compose.yml HEALTHCHECK curl -fsS http://localhost:5000/api/health interval 30s timeout 5s start-period 15s retries 3; unraid uses localhost:80. /api/health returns 200 (app/api/health.py; tests/test_api.py, test_security.py pass). docker inspect not run.</t>
+          <t>HEALTHCHECK curl :80/api/health 30s; inspect → healthy</t>
         </is>
       </c>
       <c r="J225" s="2" t="inlineStr"/>
@@ -12961,12 +12985,12 @@
       </c>
       <c r="H226" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Static compose matches: 5050:5000; FLASK_ENV=production; DATABASE_URL=sqlite:////data/docksentinel.db; RUNTIME_LOCK_PATH; START_COORDINATOR=true; DOCKER_HOST unix socket; CLI_BACKENDS_DIR=/app/llm-backends; SECRET_KEY=${SECRET_KEY:?...}; PYTHONUNBUFFERED=1; restart unless-stopped. Not run.</t>
+          <t>env FLASK_ENV=production APP_PORT=80 START_COORDINATOR=true DOCKER_HOST=unix socket; SECRET_KEY from .env</t>
         </is>
       </c>
       <c r="J226" s="2" t="inlineStr"/>
@@ -13016,12 +13040,12 @@
       </c>
       <c r="H227" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Static: both compose files mount /var/run/docker.sock:/var/run/docker.sock:ro and docksentinel_data:/data with named volume declared. docker inspect not run.</t>
+          <t>docker.sock rw=false; volume docksentinel_docksentinel_data rw=true</t>
         </is>
       </c>
       <c r="J227" s="2" t="inlineStr"/>
@@ -13071,12 +13095,12 @@
       </c>
       <c r="H228" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I228" s="2" t="inlineStr">
         <is>
-          <t>Static: both compose files declare extra_hosts 'host.docker.internal:host-gateway'. getent inside container not run.</t>
+          <t>getent host.docker.internal → 172.17.0.1</t>
         </is>
       </c>
       <c r="J228" s="2" t="inlineStr"/>
@@ -13126,12 +13150,12 @@
       </c>
       <c r="H229" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I229" s="2" t="inlineStr">
         <is>
-          <t>Static unraid example: hostname docksentinel; group_add '281'; sysctl net.ipv4.ip_unprivileged_port_start=80; APP_PORT=80, MDNS_ENABLED=true, MDNS_HOSTNAME=docksentinel, MDNS_PORT=80; networks br0 external with ipv4_address placeholder 10.0.0.X; healthcheck port 80. Not deployed.</t>
+          <t>br0 ipvlan 10.0.0.220, port 80, mDNS docksentinel.local resolves from LAN Mac</t>
         </is>
       </c>
       <c r="J229" s="2" t="inlineStr"/>
@@ -13566,12 +13590,12 @@
       </c>
       <c r="H237" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Static: README quick start (export SECRET_KEY=$(openssl rand -hex 32); docker compose up -d --build; http://localhost:5050) matches compose 5050:5000 and SECRET_KEY ${SECRET_KEY:?} requirement. Not run against docker.</t>
+          <t>docker compose -f docker-compose.unraid.yml up -d --build on Tower → healthy</t>
         </is>
       </c>
       <c r="J237" s="2" t="inlineStr"/>
@@ -13621,12 +13645,12 @@
       </c>
       <c r="H238" s="2" t="inlineStr">
         <is>
-          <t>Blocked (needs docker/LLM/Telegram)</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Static: README documents BotFather token/chat id, Test Telegram, enable Sentinel, Reject/Approve/Discuss, long-polling no webhook, group privacy-mode note; matches app/api/telegram.py and bot. Test endpoint failure path verified (400); live delivery needs Telegram.</t>
+          <t>Telegram configured; alerts delivered. NOTE: getUpdates 409 — another poller uses this bot token, so button callbacks may be swallowed until that other instance is stopped.</t>
         </is>
       </c>
       <c r="J238" s="2" t="inlineStr"/>
@@ -14256,10 +14280,333 @@
         </is>
       </c>
     </row>
+    <row r="249">
+      <c r="A249" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-01</t>
+        </is>
+      </c>
+      <c r="B249" s="2" t="inlineStr">
+        <is>
+          <t>Ops: Live deploy</t>
+        </is>
+      </c>
+      <c r="C249" s="2" t="inlineStr">
+        <is>
+          <t>Docker Engine 29 event compatibility</t>
+        </is>
+      </c>
+      <c r="D249" s="2" t="inlineStr">
+        <is>
+          <t>As an operator on a current Docker engine I want lifecycle events and instant attach/detach to work.</t>
+        </is>
+      </c>
+      <c r="E249" s="2" t="inlineStr">
+        <is>
+          <t>_watch_events reads Action/Actor.ID when legacy status/id are absent (API 1.52+); die/start/oom events recorded; restart-storm fires.</t>
+        </is>
+      </c>
+      <c r="F249" s="2" t="inlineStr">
+        <is>
+          <t>app/services/docker_watcher.py _event_fields</t>
+        </is>
+      </c>
+      <c r="G249" s="2" t="inlineStr">
+        <is>
+          <t>On Tower: docker run --rm alpine sh -c 'exit 137' x3 → /api/insights?container=... shows container_event rows; 3rd die alert_sent=true.</t>
+        </is>
+      </c>
+      <c r="H249" s="2" t="inlineStr">
+        <is>
+          <t>Pass (after fix)</t>
+        </is>
+      </c>
+      <c r="I249" s="2" t="inlineStr">
+        <is>
+          <t>Docker 29: events had no status/id → nothing recorded</t>
+        </is>
+      </c>
+      <c r="J249" s="2" t="inlineStr">
+        <is>
+          <t>docker_watcher._watch_events read legacy fields only</t>
+        </is>
+      </c>
+      <c r="K249" s="2" t="inlineStr">
+        <is>
+          <t>_event_fields Action/Actor.ID</t>
+        </is>
+      </c>
+      <c r="L249" s="2" t="inlineStr">
+        <is>
+          <t>die/start rows recorded, storm alert fired</t>
+        </is>
+      </c>
+      <c r="M249" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-02</t>
+        </is>
+      </c>
+      <c r="B250" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Triage</t>
+        </is>
+      </c>
+      <c r="C250" s="2" t="inlineStr">
+        <is>
+          <t>Coalescer max-age flush</t>
+        </is>
+      </c>
+      <c r="D250" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want chatty containers analysed even if they log a matching line more often than the coalesce window.</t>
+        </is>
+      </c>
+      <c r="E250" s="2" t="inlineStr">
+        <is>
+          <t>Batch flushes window_seconds after its FIRST chunk regardless of new arrivals (no starvation).</t>
+        </is>
+      </c>
+      <c r="F250" s="2" t="inlineStr">
+        <is>
+          <t>app/services/chunk_coalescer.py</t>
+        </is>
+      </c>
+      <c r="G250" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_sentinel_pipeline.py::test_coalescer_flushes_by_max_age_even_under_constant_arrivals; live: queued rows for Namecheap-DDNS turn into analyzed within window.</t>
+        </is>
+      </c>
+      <c r="H250" s="2" t="inlineStr">
+        <is>
+          <t>Pass (after fix)</t>
+        </is>
+      </c>
+      <c r="I250" s="2" t="inlineStr">
+        <is>
+          <t>161 rows stuck 'queued' with 300s window</t>
+        </is>
+      </c>
+      <c r="J250" s="2" t="inlineStr">
+        <is>
+          <t>pure debounce</t>
+        </is>
+      </c>
+      <c r="K250" s="2" t="inlineStr">
+        <is>
+          <t>max-age timer</t>
+        </is>
+      </c>
+      <c r="L250" s="2" t="inlineStr">
+        <is>
+          <t>unit test + live analyzed rows appearing</t>
+        </is>
+      </c>
+      <c r="M250" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-03</t>
+        </is>
+      </c>
+      <c r="B251" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Triage</t>
+        </is>
+      </c>
+      <c r="C251" s="2" t="inlineStr">
+        <is>
+          <t>Manual analyze bypasses prefilter</t>
+        </is>
+      </c>
+      <c r="D251" s="2" t="inlineStr">
+        <is>
+          <t>As an operator pressing 'Analyze now' I want an LLM verdict even for quiet logs (as the UI promises).</t>
+        </is>
+      </c>
+      <c r="E251" s="2" t="inlineStr">
+        <is>
+          <t>analyze_container_now → process_chunk(force=True) → status analyzed (never 'skipped').</t>
+        </is>
+      </c>
+      <c r="F251" s="2" t="inlineStr">
+        <is>
+          <t>app/services/sentinel.py process_chunk force</t>
+        </is>
+      </c>
+      <c r="G251" s="2" t="inlineStr">
+        <is>
+          <t>POST /api/sentinel/analyze-now {container:'Dozzle'} → status analyzed.</t>
+        </is>
+      </c>
+      <c r="H251" s="2" t="inlineStr">
+        <is>
+          <t>Pass (after fix)</t>
+        </is>
+      </c>
+      <c r="I251" s="2" t="inlineStr">
+        <is>
+          <t>see API-38</t>
+        </is>
+      </c>
+      <c r="J251" s="2" t="inlineStr"/>
+      <c r="K251" s="2" t="inlineStr">
+        <is>
+          <t>force=True</t>
+        </is>
+      </c>
+      <c r="L251" s="2" t="inlineStr">
+        <is>
+          <t>analyzed</t>
+        </is>
+      </c>
+      <c r="M251" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-04</t>
+        </is>
+      </c>
+      <c r="B252" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C252" s="2" t="inlineStr">
+        <is>
+          <t>Restart-storm keyed by container name</t>
+        </is>
+      </c>
+      <c r="D252" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want recreated containers (new id, same name) counted as one crash loop.</t>
+        </is>
+      </c>
+      <c r="E252" s="2" t="inlineStr">
+        <is>
+          <t>count_container_events/find_recent_storm_alert filter by container_name.</t>
+        </is>
+      </c>
+      <c r="F252" s="2" t="inlineStr">
+        <is>
+          <t>app/repositories/analysis_events.py</t>
+        </is>
+      </c>
+      <c r="G252" s="2" t="inlineStr">
+        <is>
+          <t>docker run --rm --name X ... exit 137 three times → 3rd die alert_sent=true.</t>
+        </is>
+      </c>
+      <c r="H252" s="2" t="inlineStr">
+        <is>
+          <t>Pass (after fix)</t>
+        </is>
+      </c>
+      <c r="I252" s="2" t="inlineStr">
+        <is>
+          <t>--rm recreations never reached threshold by id</t>
+        </is>
+      </c>
+      <c r="J252" s="2" t="inlineStr"/>
+      <c r="K252" s="2" t="inlineStr">
+        <is>
+          <t>count by name</t>
+        </is>
+      </c>
+      <c r="L252" s="2" t="inlineStr">
+        <is>
+          <t>3rd die alert_sent=true, then cooldown</t>
+        </is>
+      </c>
+      <c r="M252" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="2" t="inlineStr">
+        <is>
+          <t>LIVE-05</t>
+        </is>
+      </c>
+      <c r="B253" s="2" t="inlineStr">
+        <is>
+          <t>UI: Dashboard</t>
+        </is>
+      </c>
+      <c r="C253" s="2" t="inlineStr">
+        <is>
+          <t>LLM failure counter resets on restart</t>
+        </is>
+      </c>
+      <c r="D253" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want 'LLM failures since last restart' to mean that.</t>
+        </is>
+      </c>
+      <c r="E253" s="2" t="inlineStr">
+        <is>
+          <t>coordinator.start() sets llm_failure_count=0.</t>
+        </is>
+      </c>
+      <c r="F253" s="2" t="inlineStr">
+        <is>
+          <t>app/services/coordinator.py</t>
+        </is>
+      </c>
+      <c r="G253" s="2" t="inlineStr">
+        <is>
+          <t>After redeploy /api/sentinel/status llm_failure_count == 0 (was 10000 carried from April).</t>
+        </is>
+      </c>
+      <c r="H253" s="2" t="inlineStr">
+        <is>
+          <t>Pass (after fix)</t>
+        </is>
+      </c>
+      <c r="I253" s="2" t="inlineStr">
+        <is>
+          <t>llm_failure_count=10000 carried over</t>
+        </is>
+      </c>
+      <c r="J253" s="2" t="inlineStr"/>
+      <c r="K253" s="2" t="inlineStr">
+        <is>
+          <t>reset on start</t>
+        </is>
+      </c>
+      <c r="L253" s="2" t="inlineStr">
+        <is>
+          <t>0 after redeploy</t>
+        </is>
+      </c>
+      <c r="M253" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M248"/>
+  <autoFilter ref="A1:M253"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H248" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not tested,Pass,Fail,Fixed - retest,Pass (after fix),Blocked (needs docker/LLM/Telegram),Won't fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14303,7 +14650,7 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$248,A2)</f>
+        <f>COUNTIF(Stories!$H$2:$H$253,A2)</f>
         <v/>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -14316,7 +14663,7 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$248,A3)</f>
+        <f>COUNTIF(Stories!$H$2:$H$253,A3)</f>
         <v/>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -14329,7 +14676,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$248,A4)</f>
+        <f>COUNTIF(Stories!$H$2:$H$253,A4)</f>
         <v/>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -14342,7 +14689,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$248,A5)</f>
+        <f>COUNTIF(Stories!$H$2:$H$253,A5)</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -14355,7 +14702,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$248,A6)</f>
+        <f>COUNTIF(Stories!$H$2:$H$253,A6)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -14368,7 +14715,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$248,A7)</f>
+        <f>COUNTIF(Stories!$H$2:$H$253,A7)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -14381,7 +14728,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$248,A8)</f>
+        <f>COUNTIF(Stories!$H$2:$H$253,A8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -14394,7 +14741,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTA(Stories!$A$2:$A$248)</f>
+        <f>COUNTA(Stories!$A$2:$A$253)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -14458,15 +14805,15 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A14)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A14)</f>
         <v/>
       </c>
       <c r="C14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A14,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A14,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A14,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A14,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A14,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A14,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14477,15 +14824,15 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A15)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A15)</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A15,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A15,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A15,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A15,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A15,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A15,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14496,15 +14843,15 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A16)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A16)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A16,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A16,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A16,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A16,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A16,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A16,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14515,15 +14862,15 @@
         </is>
       </c>
       <c r="B17" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A17)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A17)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A17,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A17,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A17,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A17,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A17,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A17,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14534,15 +14881,15 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A18)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A18)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A18,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A18,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A18,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A18,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A18,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A18,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14553,15 +14900,15 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A19)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A19)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A19,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A19,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A19,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A19,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A19,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A19,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14572,15 +14919,15 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A20)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A20)</f>
         <v/>
       </c>
       <c r="C20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A20,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A20,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A20,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A20,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A20,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A20,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14591,15 +14938,15 @@
         </is>
       </c>
       <c r="B21" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A21)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A21)</f>
         <v/>
       </c>
       <c r="C21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A21,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A21,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A21,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A21,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A21,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A21,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14610,15 +14957,15 @@
         </is>
       </c>
       <c r="B22" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A22)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A22)</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A22,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A22,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A22,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A22,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A22,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A22,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14629,15 +14976,15 @@
         </is>
       </c>
       <c r="B23" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A23)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A23)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A23,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A23,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A23,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A23,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A23,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A23,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14648,15 +14995,15 @@
         </is>
       </c>
       <c r="B24" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A24)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A24)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A24,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A24,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A24,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A24,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A24,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A24,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14667,15 +15014,15 @@
         </is>
       </c>
       <c r="B25" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A25)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A25)</f>
         <v/>
       </c>
       <c r="C25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A25,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A25,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A25,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A25,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A25,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A25,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14686,15 +15033,15 @@
         </is>
       </c>
       <c r="B26" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A26)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A26)</f>
         <v/>
       </c>
       <c r="C26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A26,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A26,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A26,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A26,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A26,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A26,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14705,15 +15052,15 @@
         </is>
       </c>
       <c r="B27" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A27)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A27)</f>
         <v/>
       </c>
       <c r="C27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A27,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A27,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A27,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A27,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A27,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A27,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14724,15 +15071,15 @@
         </is>
       </c>
       <c r="B28" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A28)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A28)</f>
         <v/>
       </c>
       <c r="C28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A28,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A28,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A28,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A28,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A28,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A28,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14743,15 +15090,15 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A29)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A29)</f>
         <v/>
       </c>
       <c r="C29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A29,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A29,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A29,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A29,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A29,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A29,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14762,15 +15109,15 @@
         </is>
       </c>
       <c r="B30" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A30)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A30)</f>
         <v/>
       </c>
       <c r="C30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A30,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A30,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A30,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A30,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A30,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A30,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14781,15 +15128,15 @@
         </is>
       </c>
       <c r="B31" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A31)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A31)</f>
         <v/>
       </c>
       <c r="C31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A31,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A31,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A31,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A31,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A31,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A31,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14800,15 +15147,15 @@
         </is>
       </c>
       <c r="B32" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A32)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A32)</f>
         <v/>
       </c>
       <c r="C32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A32,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A32,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A32,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A32,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A32,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A32,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14819,15 +15166,15 @@
         </is>
       </c>
       <c r="B33" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A33)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A33)</f>
         <v/>
       </c>
       <c r="C33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A33,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A33,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A33,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A33,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A33,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A33,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14838,15 +15185,15 @@
         </is>
       </c>
       <c r="B34" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A34)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A34)</f>
         <v/>
       </c>
       <c r="C34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A34,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A34,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A34,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A34,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A34,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A34,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14857,15 +15204,15 @@
         </is>
       </c>
       <c r="B35" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A35)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A35)</f>
         <v/>
       </c>
       <c r="C35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A35,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A35,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A35,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A35,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A35,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A35,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14876,15 +15223,15 @@
         </is>
       </c>
       <c r="B36" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A36)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A36)</f>
         <v/>
       </c>
       <c r="C36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A36,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A36,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A36,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A36,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A36,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A36,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14895,15 +15242,15 @@
         </is>
       </c>
       <c r="B37" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A37)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A37)</f>
         <v/>
       </c>
       <c r="C37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A37,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A37,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A37,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A37,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A37,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A37,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14914,15 +15261,15 @@
         </is>
       </c>
       <c r="B38" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A38)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A38)</f>
         <v/>
       </c>
       <c r="C38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A38,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A38,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A38,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A38,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A38,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A38,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14933,15 +15280,15 @@
         </is>
       </c>
       <c r="B39" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A39)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A39)</f>
         <v/>
       </c>
       <c r="C39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A39,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A39,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A39,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A39,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A39,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A39,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14952,15 +15299,15 @@
         </is>
       </c>
       <c r="B40" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A40)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A40)</f>
         <v/>
       </c>
       <c r="C40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A40,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A40,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A40,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A40,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A40,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A40,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14971,15 +15318,15 @@
         </is>
       </c>
       <c r="B41" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A41)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A41)</f>
         <v/>
       </c>
       <c r="C41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A41,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A41,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A41,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A41,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A41,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A41,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14990,15 +15337,15 @@
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A42)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A42)</f>
         <v/>
       </c>
       <c r="C42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A42,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A42,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A42,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A42,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A42,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A42,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15009,15 +15356,15 @@
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A43)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A43)</f>
         <v/>
       </c>
       <c r="C43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A43,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A43,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A43,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A43,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A43,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A43,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15028,15 +15375,15 @@
         </is>
       </c>
       <c r="B44" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A44)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A44)</f>
         <v/>
       </c>
       <c r="C44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A44,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A44,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A44,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A44,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A44,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A44,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15047,15 +15394,15 @@
         </is>
       </c>
       <c r="B45" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A45)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A45)</f>
         <v/>
       </c>
       <c r="C45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A45,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A45,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A45,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A45,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A45,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A45,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15066,15 +15413,15 @@
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A46)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A46)</f>
         <v/>
       </c>
       <c r="C46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A46,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A46,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A46,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A46,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A46,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A46,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15085,15 +15432,15 @@
         </is>
       </c>
       <c r="B47" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A47)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A47)</f>
         <v/>
       </c>
       <c r="C47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A47,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A47,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A47,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A47,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A47,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A47,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15104,15 +15451,15 @@
         </is>
       </c>
       <c r="B48" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A48)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A48)</f>
         <v/>
       </c>
       <c r="C48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A48,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A48,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A48,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A48,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A48,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A48,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15123,15 +15470,15 @@
         </is>
       </c>
       <c r="B49" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A49)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A49)</f>
         <v/>
       </c>
       <c r="C49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A49,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A49,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A49,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A49,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A49,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A49,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15142,15 +15489,15 @@
         </is>
       </c>
       <c r="B50" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A50)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A50)</f>
         <v/>
       </c>
       <c r="C50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A50,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A50,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A50,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A50,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A50,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A50,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15161,15 +15508,15 @@
         </is>
       </c>
       <c r="B51" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A51)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A51)</f>
         <v/>
       </c>
       <c r="C51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A51,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A51,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A51,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A51,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A51,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A51,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15180,15 +15527,15 @@
         </is>
       </c>
       <c r="B52" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$248,A52)</f>
+        <f>COUNTIF(Stories!$B$2:$B$253,A52)</f>
         <v/>
       </c>
       <c r="C52" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A52,Stories!$H$2:$H$248,"Pass")+COUNTIFS(Stories!$B$2:$B$248,A52,Stories!$H$2:$H$248,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A52,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A52,Stories!$H$2:$H$253,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D52" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$248,A52,Stories!$H$2:$H$248,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$253,A52,Stories!$H$2:$H$253,"Fail")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -14200,7 +14200,7 @@
       </c>
       <c r="H247" s="2" t="inlineStr">
         <is>
-          <t>Fixed - retest</t>
+          <t>Pass (after fix)</t>
         </is>
       </c>
       <c r="I247" s="2" t="inlineStr">
@@ -14218,7 +14218,11 @@
           <t>redact + one-line warning</t>
         </is>
       </c>
-      <c r="L247" s="2" t="inlineStr"/>
+      <c r="L247" s="2" t="inlineStr">
+        <is>
+          <t>live logs: 0 token matches over 10 min while 409 persists; one-line warning</t>
+        </is>
+      </c>
       <c r="M247" s="2" t="inlineStr">
         <is>
           <t>2026-08-15</t>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$253</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$259</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M253"/>
+  <dimension ref="A1:M259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14607,10 +14607,340 @@
         </is>
       </c>
     </row>
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
+        <is>
+          <t>TRI-01</t>
+        </is>
+      </c>
+      <c r="B254" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Triage</t>
+        </is>
+      </c>
+      <c r="C254" s="2" t="inlineStr">
+        <is>
+          <t>Operator stops are not incidents</t>
+        </is>
+      </c>
+      <c r="D254" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I don't want `docker stop`/compose restarts classified critical or counted as restart storms.</t>
+        </is>
+      </c>
+      <c r="E254" s="2" t="inlineStr">
+        <is>
+          <t>die within 20s of a kill/stop for the same container name → noise 'stopped by operator (exit N)' with matched_keywords 'die:stopped' (excluded from storm count); stop → noise; kill → noise.</t>
+        </is>
+      </c>
+      <c r="F254" s="2" t="inlineStr">
+        <is>
+          <t>app/services/sentinel.py classify/handle_container_event</t>
+        </is>
+      </c>
+      <c r="G254" s="2" t="inlineStr">
+        <is>
+          <t>docker run -d --name t alpine sleep 300; docker stop t → /api/insights?container=t shows die:stopped noise.</t>
+        </is>
+      </c>
+      <c r="H254" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I254" s="2" t="inlineStr">
+        <is>
+          <t>Live on Tower: docker stop → kill(noise) stop(noise) die:stopped noise "stopped by operator (exit 137)"</t>
+        </is>
+      </c>
+      <c r="J254" s="2" t="inlineStr"/>
+      <c r="K254" s="2" t="inlineStr"/>
+      <c r="L254" s="2" t="inlineStr"/>
+      <c r="M254" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>TRI-02</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Triage</t>
+        </is>
+      </c>
+      <c r="C255" s="2" t="inlineStr">
+        <is>
+          <t>Analysis cooldown</t>
+        </is>
+      </c>
+      <c r="D255" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I don't want the same warning re-analysed by the LLM every few minutes.</t>
+        </is>
+      </c>
+      <c r="E255" s="2" t="inlineStr">
+        <is>
+          <t>analysis_cooldown_minutes (15): if last analyzed verdict for the container was warning/noise within the window and new chunk is ≥0.6 Jaccard-similar (timestamps stripped) → status analysis_cooldown, no LLM call. Never for critical or manual analyze.</t>
+        </is>
+      </c>
+      <c r="F255" s="2" t="inlineStr">
+        <is>
+          <t>sentinel._find_cooldown_match</t>
+        </is>
+      </c>
+      <c r="G255" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_triage_tuning.py; live: repeated Namecheap-DDNS chunks show analysis_cooldown.</t>
+        </is>
+      </c>
+      <c r="H255" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I255" s="2" t="inlineStr">
+        <is>
+          <t>12 unit tests; setting present live (15)</t>
+        </is>
+      </c>
+      <c r="J255" s="2" t="inlineStr"/>
+      <c r="K255" s="2" t="inlineStr"/>
+      <c r="L255" s="2" t="inlineStr"/>
+      <c r="M255" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
+        <is>
+          <t>TRI-03</t>
+        </is>
+      </c>
+      <c r="B256" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C256" s="2" t="inlineStr">
+        <is>
+          <t>Persistent-warning escalation</t>
+        </is>
+      </c>
+      <c r="D256" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want a warning that keeps recurring to become an alert.</t>
+        </is>
+      </c>
+      <c r="E256" s="2" t="inlineStr">
+        <is>
+          <t>persistent_warning_count (3) warnings for one container within persistent_warning_window_minutes (60) → one '⚠️ PERSISTENT WARNING · name · N in W min' alert (respects mute, rejected, global rate limit, per-name cooldown).</t>
+        </is>
+      </c>
+      <c r="F256" s="2" t="inlineStr">
+        <is>
+          <t>sentinel._maybe_escalate_warning, alerts.maybe_send_escalation</t>
+        </is>
+      </c>
+      <c r="G256" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_triage_tuning.py</t>
+        </is>
+      </c>
+      <c r="H256" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I256" s="2" t="inlineStr">
+        <is>
+          <t>unit tests; settings 3/60 live</t>
+        </is>
+      </c>
+      <c r="J256" s="2" t="inlineStr"/>
+      <c r="K256" s="2" t="inlineStr"/>
+      <c r="L256" s="2" t="inlineStr"/>
+      <c r="M256" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="2" t="inlineStr">
+        <is>
+          <t>TRI-04</t>
+        </is>
+      </c>
+      <c r="B257" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C257" s="2" t="inlineStr">
+        <is>
+          <t>Confidence gate</t>
+        </is>
+      </c>
+      <c r="D257" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want low-confidence criticals recorded but not pushed.</t>
+        </is>
+      </c>
+      <c r="E257" s="2" t="inlineStr">
+        <is>
+          <t>alert_min_confidence (0=off): verdict.confidence below → no alert, alert_error 'suppressed: confidence X &lt; Y'.</t>
+        </is>
+      </c>
+      <c r="F257" s="2" t="inlineStr">
+        <is>
+          <t>sentinel._confidence_suppression</t>
+        </is>
+      </c>
+      <c r="G257" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_triage_tuning.py</t>
+        </is>
+      </c>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
+        <is>
+          <t>unit tests; setting 0.0 live (off by default)</t>
+        </is>
+      </c>
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr"/>
+      <c r="M257" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
+        <is>
+          <t>TRI-05</t>
+        </is>
+      </c>
+      <c r="B258" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C258" s="2" t="inlineStr">
+        <is>
+          <t>Per-container mute</t>
+        </is>
+      </c>
+      <c r="D258" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want to silence one container for a while from Telegram, the UI, or the API.</t>
+        </is>
+      </c>
+      <c r="E258" s="2" t="inlineStr">
+        <is>
+          <t>container_mutes table; PUT/GET/DELETE /api/mutes; UI buttons on Events/Issues + Dashboard card; Telegram '🔕 Mute 24h' button + /mutes + /unmute; AlertService checks mute first → 'muted until …'.</t>
+        </is>
+      </c>
+      <c r="F258" s="2" t="inlineStr">
+        <is>
+          <t>app/api/mutes.py, repositories/container_mutes.py, telegram_bot.py, alerts.py</t>
+        </is>
+      </c>
+      <c r="G258" s="2" t="inlineStr">
+        <is>
+          <t>PUT /api/mutes/X {hours:24} → GET /api/mutes lists it; alerts for X get alert_error muted.</t>
+        </is>
+      </c>
+      <c r="H258" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I258" s="2" t="inlineStr">
+        <is>
+          <t>Live: PUT/GET /api/mutes ok (Namecheap-DDNS muted 24h); 8 tests</t>
+        </is>
+      </c>
+      <c r="J258" s="2" t="inlineStr"/>
+      <c r="K258" s="2" t="inlineStr"/>
+      <c r="L258" s="2" t="inlineStr"/>
+      <c r="M258" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="2" t="inlineStr">
+        <is>
+          <t>TRI-06</t>
+        </is>
+      </c>
+      <c r="B259" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Telegram notify</t>
+        </is>
+      </c>
+      <c r="C259" s="2" t="inlineStr">
+        <is>
+          <t>Slim alert card</t>
+        </is>
+      </c>
+      <c r="D259" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want alerts readable on a phone in one screen.</t>
+        </is>
+      </c>
+      <c r="E259" s="2" t="inlineStr">
+        <is>
+          <t>≤12 lines: header, summary, ROOT CAUSE (240), FIX ≤3 lines/300, LOG EXCERPT last 3 lines ≤120, one-line footer with confidence/event/dashboard.</t>
+        </is>
+      </c>
+      <c r="F259" s="2" t="inlineStr">
+        <is>
+          <t>alerts._format_message</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>tests assert substrings; visual check on next real alert.</t>
+        </is>
+      </c>
+      <c r="H259" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I259" s="2" t="inlineStr">
+        <is>
+          <t>tests updated (3-line excerpt); live visual pending next alert</t>
+        </is>
+      </c>
+      <c r="J259" s="2" t="inlineStr"/>
+      <c r="K259" s="2" t="inlineStr"/>
+      <c r="L259" s="2" t="inlineStr"/>
+      <c r="M259" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M253"/>
+  <autoFilter ref="A1:M259"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H253" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H259" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not tested,Pass,Fail,Fixed - retest,Pass (after fix),Blocked (needs docker/LLM/Telegram),Won't fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14654,7 +14984,7 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$253,A2)</f>
+        <f>COUNTIF(Stories!$H$2:$H$259,A2)</f>
         <v/>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -14667,7 +14997,7 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$253,A3)</f>
+        <f>COUNTIF(Stories!$H$2:$H$259,A3)</f>
         <v/>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -14680,7 +15010,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$253,A4)</f>
+        <f>COUNTIF(Stories!$H$2:$H$259,A4)</f>
         <v/>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -14693,7 +15023,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$253,A5)</f>
+        <f>COUNTIF(Stories!$H$2:$H$259,A5)</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -14706,7 +15036,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$253,A6)</f>
+        <f>COUNTIF(Stories!$H$2:$H$259,A6)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -14719,7 +15049,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$253,A7)</f>
+        <f>COUNTIF(Stories!$H$2:$H$259,A7)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -14732,7 +15062,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$253,A8)</f>
+        <f>COUNTIF(Stories!$H$2:$H$259,A8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -14745,7 +15075,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTA(Stories!$A$2:$A$253)</f>
+        <f>COUNTA(Stories!$A$2:$A$259)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -14809,15 +15139,15 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A14)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A14)</f>
         <v/>
       </c>
       <c r="C14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A14,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A14,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A14,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A14,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A14,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A14,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14828,15 +15158,15 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A15)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A15)</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A15,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A15,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A15,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A15,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A15,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A15,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14847,15 +15177,15 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A16)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A16)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A16,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A16,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A16,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A16,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A16,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A16,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14866,15 +15196,15 @@
         </is>
       </c>
       <c r="B17" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A17)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A17)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A17,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A17,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A17,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A17,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A17,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A17,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14885,15 +15215,15 @@
         </is>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A18)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A18)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A18,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A18,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A18,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A18,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A18,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A18,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14904,15 +15234,15 @@
         </is>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A19)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A19)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A19,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A19,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A19,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A19,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A19,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A19,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14923,15 +15253,15 @@
         </is>
       </c>
       <c r="B20" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A20)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A20)</f>
         <v/>
       </c>
       <c r="C20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A20,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A20,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A20,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A20,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A20,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A20,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14942,15 +15272,15 @@
         </is>
       </c>
       <c r="B21" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A21)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A21)</f>
         <v/>
       </c>
       <c r="C21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A21,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A21,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A21,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A21,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A21,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A21,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14961,15 +15291,15 @@
         </is>
       </c>
       <c r="B22" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A22)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A22)</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A22,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A22,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A22,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A22,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A22,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A22,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14980,15 +15310,15 @@
         </is>
       </c>
       <c r="B23" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A23)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A23)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A23,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A23,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A23,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A23,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A23,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A23,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -14999,15 +15329,15 @@
         </is>
       </c>
       <c r="B24" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A24)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A24)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A24,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A24,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A24,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A24,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A24,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A24,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15018,15 +15348,15 @@
         </is>
       </c>
       <c r="B25" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A25)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A25)</f>
         <v/>
       </c>
       <c r="C25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A25,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A25,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A25,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A25,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A25,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A25,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15037,15 +15367,15 @@
         </is>
       </c>
       <c r="B26" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A26)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A26)</f>
         <v/>
       </c>
       <c r="C26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A26,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A26,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A26,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A26,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A26,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A26,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15056,15 +15386,15 @@
         </is>
       </c>
       <c r="B27" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A27)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A27)</f>
         <v/>
       </c>
       <c r="C27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A27,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A27,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A27,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A27,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A27,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A27,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15075,15 +15405,15 @@
         </is>
       </c>
       <c r="B28" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A28)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A28)</f>
         <v/>
       </c>
       <c r="C28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A28,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A28,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A28,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A28,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A28,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A28,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15094,15 +15424,15 @@
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A29)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A29)</f>
         <v/>
       </c>
       <c r="C29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A29,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A29,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A29,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A29,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A29,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A29,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15113,15 +15443,15 @@
         </is>
       </c>
       <c r="B30" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A30)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A30)</f>
         <v/>
       </c>
       <c r="C30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A30,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A30,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A30,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A30,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A30,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A30,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15132,15 +15462,15 @@
         </is>
       </c>
       <c r="B31" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A31)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A31)</f>
         <v/>
       </c>
       <c r="C31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A31,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A31,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A31,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A31,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A31,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A31,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15151,15 +15481,15 @@
         </is>
       </c>
       <c r="B32" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A32)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A32)</f>
         <v/>
       </c>
       <c r="C32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A32,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A32,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A32,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A32,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A32,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A32,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15170,15 +15500,15 @@
         </is>
       </c>
       <c r="B33" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A33)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A33)</f>
         <v/>
       </c>
       <c r="C33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A33,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A33,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A33,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A33,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A33,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A33,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15189,15 +15519,15 @@
         </is>
       </c>
       <c r="B34" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A34)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A34)</f>
         <v/>
       </c>
       <c r="C34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A34,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A34,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A34,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A34,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A34,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A34,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15208,15 +15538,15 @@
         </is>
       </c>
       <c r="B35" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A35)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A35)</f>
         <v/>
       </c>
       <c r="C35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A35,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A35,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A35,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A35,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A35,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A35,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15227,15 +15557,15 @@
         </is>
       </c>
       <c r="B36" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A36)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A36)</f>
         <v/>
       </c>
       <c r="C36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A36,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A36,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A36,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A36,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A36,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A36,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15246,15 +15576,15 @@
         </is>
       </c>
       <c r="B37" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A37)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A37)</f>
         <v/>
       </c>
       <c r="C37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A37,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A37,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A37,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A37,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A37,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A37,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15265,15 +15595,15 @@
         </is>
       </c>
       <c r="B38" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A38)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A38)</f>
         <v/>
       </c>
       <c r="C38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A38,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A38,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A38,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A38,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A38,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A38,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15284,15 +15614,15 @@
         </is>
       </c>
       <c r="B39" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A39)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A39)</f>
         <v/>
       </c>
       <c r="C39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A39,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A39,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A39,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A39,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A39,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A39,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15303,15 +15633,15 @@
         </is>
       </c>
       <c r="B40" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A40)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A40)</f>
         <v/>
       </c>
       <c r="C40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A40,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A40,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A40,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A40,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A40,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A40,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15322,15 +15652,15 @@
         </is>
       </c>
       <c r="B41" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A41)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A41)</f>
         <v/>
       </c>
       <c r="C41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A41,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A41,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A41,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A41,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A41,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A41,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15341,15 +15671,15 @@
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A42)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A42)</f>
         <v/>
       </c>
       <c r="C42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A42,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A42,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A42,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A42,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A42,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A42,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15360,15 +15690,15 @@
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A43)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A43)</f>
         <v/>
       </c>
       <c r="C43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A43,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A43,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A43,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A43,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A43,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A43,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15379,15 +15709,15 @@
         </is>
       </c>
       <c r="B44" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A44)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A44)</f>
         <v/>
       </c>
       <c r="C44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A44,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A44,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A44,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A44,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A44,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A44,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15398,15 +15728,15 @@
         </is>
       </c>
       <c r="B45" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A45)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A45)</f>
         <v/>
       </c>
       <c r="C45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A45,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A45,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A45,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A45,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A45,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A45,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15417,15 +15747,15 @@
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A46)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A46)</f>
         <v/>
       </c>
       <c r="C46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A46,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A46,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A46,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A46,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A46,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A46,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15436,15 +15766,15 @@
         </is>
       </c>
       <c r="B47" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A47)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A47)</f>
         <v/>
       </c>
       <c r="C47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A47,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A47,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A47,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A47,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A47,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A47,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15455,15 +15785,15 @@
         </is>
       </c>
       <c r="B48" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A48)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A48)</f>
         <v/>
       </c>
       <c r="C48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A48,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A48,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A48,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A48,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A48,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A48,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15474,15 +15804,15 @@
         </is>
       </c>
       <c r="B49" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A49)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A49)</f>
         <v/>
       </c>
       <c r="C49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A49,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A49,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A49,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A49,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A49,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A49,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15493,15 +15823,15 @@
         </is>
       </c>
       <c r="B50" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A50)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A50)</f>
         <v/>
       </c>
       <c r="C50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A50,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A50,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A50,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A50,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A50,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A50,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15512,15 +15842,15 @@
         </is>
       </c>
       <c r="B51" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A51)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A51)</f>
         <v/>
       </c>
       <c r="C51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A51,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A51,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A51,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A51,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A51,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A51,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15531,15 +15861,15 @@
         </is>
       </c>
       <c r="B52" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$253,A52)</f>
+        <f>COUNTIF(Stories!$B$2:$B$259,A52)</f>
         <v/>
       </c>
       <c r="C52" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A52,Stories!$H$2:$H$253,"Pass")+COUNTIFS(Stories!$B$2:$B$253,A52,Stories!$H$2:$H$253,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A52,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A52,Stories!$H$2:$H$259,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D52" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$253,A52,Stories!$H$2:$H$253,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$259,A52,Stories!$H$2:$H$259,"Fail")</f>
         <v/>
       </c>
     </row>

--- a/docs/qa/feature-tracker.xlsx
+++ b/docs/qa/feature-tracker.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Legend" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$259</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Stories'!$A$1:$M$267</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -450,7 +450,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M259"/>
+  <dimension ref="A1:M267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -14937,10 +14937,462 @@
         </is>
       </c>
     </row>
+    <row r="260">
+      <c r="A260" s="2" t="inlineStr">
+        <is>
+          <t>INC-01</t>
+        </is>
+      </c>
+      <c r="B260" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C260" s="2" t="inlineStr">
+        <is>
+          <t>One message per incident</t>
+        </is>
+      </c>
+      <c r="D260" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want a repeating problem to be ONE Telegram message that updates, not a new alert every cooldown.</t>
+        </is>
+      </c>
+      <c r="E260" s="2" t="inlineStr">
+        <is>
+          <t>First alert-worthy occurrence opens an incident and sends one message; later occurrences of the same signature edit that message in place ('×N', 'last seen HH:MM:SS') and send nothing new; the event records alert_error 'incident #N updated (×N)'.</t>
+        </is>
+      </c>
+      <c r="F260" s="2" t="inlineStr">
+        <is>
+          <t>app/services/incidents.py, app/services/alerts.py</t>
+        </is>
+      </c>
+      <c r="G260" s="2" t="inlineStr">
+        <is>
+          <t>Live: 4 crashes on one container -&gt; GET /api/incidents shows occurrence_count 4, notify_count 1.</t>
+        </is>
+      </c>
+      <c r="H260" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I260" s="2" t="inlineStr">
+        <is>
+          <t>Live: ds-inctest 4 crashes -&gt; incident #1 occurrence_count=4, notify_count=1, msg 9801 edited in place</t>
+        </is>
+      </c>
+      <c r="J260" s="2" t="inlineStr"/>
+      <c r="K260" s="2" t="inlineStr"/>
+      <c r="L260" s="2" t="inlineStr"/>
+      <c r="M260" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="2" t="inlineStr">
+        <is>
+          <t>INC-02</t>
+        </is>
+      </c>
+      <c r="B261" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C261" s="2" t="inlineStr">
+        <is>
+          <t>Signature groups the same problem</t>
+        </is>
+      </c>
+      <c r="D261" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want the same failure with different timestamps/ids/numbers treated as one problem.</t>
+        </is>
+      </c>
+      <c r="E261" s="2" t="inlineStr">
+        <is>
+          <t>incident_signature normalises the summary (lowercase, strip ISO timestamps/clock times, replace uuid/hex/digit runs with #, collapse whitespace, first 120 chars) then sha256[:32] over container|severity|normalised.</t>
+        </is>
+      </c>
+      <c r="F261" s="2" t="inlineStr">
+        <is>
+          <t>app/services/incidents.py incident_signature/normalize_summary</t>
+        </is>
+      </c>
+      <c r="G261" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_incidents.py signature cases.</t>
+        </is>
+      </c>
+      <c r="H261" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I261" s="2" t="inlineStr">
+        <is>
+          <t>unit tests: same error w/ different numbers/timestamps -&gt; same signature</t>
+        </is>
+      </c>
+      <c r="J261" s="2" t="inlineStr"/>
+      <c r="K261" s="2" t="inlineStr"/>
+      <c r="L261" s="2" t="inlineStr"/>
+      <c r="M261" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="2" t="inlineStr">
+        <is>
+          <t>INC-03</t>
+        </is>
+      </c>
+      <c r="B262" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C262" s="2" t="inlineStr">
+        <is>
+          <t>Severity escalation pings</t>
+        </is>
+      </c>
+      <c r="D262" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want to be pinged again if an open incident gets worse.</t>
+        </is>
+      </c>
+      <c r="E262" s="2" t="inlineStr">
+        <is>
+          <t>An occurrence ranking above the incident's classification re-keys the signature, updates severity and sends a NEW message (notify_count+1).</t>
+        </is>
+      </c>
+      <c r="F262" s="2" t="inlineStr">
+        <is>
+          <t>app/services/incidents.py notify_for</t>
+        </is>
+      </c>
+      <c r="G262" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_incidents.py escalation case.</t>
+        </is>
+      </c>
+      <c r="H262" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I262" s="2" t="inlineStr">
+        <is>
+          <t>unit tests: warning-&gt;critical sends a new message and re-keys</t>
+        </is>
+      </c>
+      <c r="J262" s="2" t="inlineStr"/>
+      <c r="K262" s="2" t="inlineStr"/>
+      <c r="L262" s="2" t="inlineStr"/>
+      <c r="M262" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
+        <is>
+          <t>INC-04</t>
+        </is>
+      </c>
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>Auto-resolve with notice</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want to know when a problem stops without having to check.</t>
+        </is>
+      </c>
+      <c r="E263" s="2" t="inlineStr">
+        <is>
+          <t>Scheduled every 5 min: open incidents with last_seen_at older than incident_resolve_after_minutes (30) become resolved, the original message is edited to '✅ RESOLVED …', and (when incident_notify_on_resolve) a short resolve message is sent.</t>
+        </is>
+      </c>
+      <c r="F263" s="2" t="inlineStr">
+        <is>
+          <t>app/services/incidents.py resolve_stale, coordinator job 'resolve-incidents'</t>
+        </is>
+      </c>
+      <c r="G263" s="2" t="inlineStr">
+        <is>
+          <t>Live: set resolve window to 2 min, stop the crashes, wait -&gt; GET /api/incidents?status=resolved.</t>
+        </is>
+      </c>
+      <c r="H263" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I263" s="2" t="inlineStr">
+        <is>
+          <t>Live: resolve window 2 min -&gt; incident auto-resolved at 03:22:19 with notice</t>
+        </is>
+      </c>
+      <c r="J263" s="2" t="inlineStr"/>
+      <c r="K263" s="2" t="inlineStr"/>
+      <c r="L263" s="2" t="inlineStr"/>
+      <c r="M263" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
+        <is>
+          <t>INC-05</t>
+        </is>
+      </c>
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>Pipeline: Alerts</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>Reminder for long-running incidents</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want an optional nudge if something has been broken for hours.</t>
+        </is>
+      </c>
+      <c r="E264" s="2" t="inlineStr">
+        <is>
+          <t>incident_reminder_hours (0=off): when an occurrence arrives and last_notified_at is older than N hours, send a fresh message instead of a silent edit.</t>
+        </is>
+      </c>
+      <c r="F264" s="2" t="inlineStr">
+        <is>
+          <t>app/services/incidents.py</t>
+        </is>
+      </c>
+      <c r="G264" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_incidents.py reminder case.</t>
+        </is>
+      </c>
+      <c r="H264" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I264" s="2" t="inlineStr">
+        <is>
+          <t>unit tests; default off (0)</t>
+        </is>
+      </c>
+      <c r="J264" s="2" t="inlineStr"/>
+      <c r="K264" s="2" t="inlineStr"/>
+      <c r="L264" s="2" t="inlineStr"/>
+      <c r="M264" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
+        <is>
+          <t>INC-06</t>
+        </is>
+      </c>
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>API: Incidents</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>Incidents API</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want to list and resolve incidents programmatically.</t>
+        </is>
+      </c>
+      <c r="E265" s="2" t="inlineStr">
+        <is>
+          <t>GET /api/incidents?status=open|resolved&amp;limit=1..500 -&gt; {items:[...]}; GET /api/incidents/&lt;id&gt; incl. occurrence_count/duration_seconds; POST /api/incidents/&lt;id&gt;/resolve -&gt; 200, 404 unknown, 409 already resolved; invalid status/limit -&gt; 400.</t>
+        </is>
+      </c>
+      <c r="F265" s="2" t="inlineStr">
+        <is>
+          <t>app/api/incidents.py</t>
+        </is>
+      </c>
+      <c r="G265" s="2" t="inlineStr">
+        <is>
+          <t>curl against http://10.0.0.220/api/incidents</t>
+        </is>
+      </c>
+      <c r="H265" s="2" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="I265" s="2" t="inlineStr">
+        <is>
+          <t>Live: GET /api/incidents + ?status=resolved return expected shapes</t>
+        </is>
+      </c>
+      <c r="J265" s="2" t="inlineStr"/>
+      <c r="K265" s="2" t="inlineStr"/>
+      <c r="L265" s="2" t="inlineStr"/>
+      <c r="M265" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>INC-07</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>UI: Incidents</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>Incidents page</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want open incidents front and centre with a way to resolve or mute.</t>
+        </is>
+      </c>
+      <c r="E266" s="2" t="inlineStr">
+        <is>
+          <t>/incidents master-detail: open first with ×N/duration/severity, detail shows timeline + Resolve/Mute/links; sidebar badge shows open count; dashboard shows an open-incidents block.</t>
+        </is>
+      </c>
+      <c r="F266" s="2" t="inlineStr">
+        <is>
+          <t>app/templates/incidents.html, app/web/routes.py</t>
+        </is>
+      </c>
+      <c r="G266" s="2" t="inlineStr">
+        <is>
+          <t>Open http://10.0.0.220/incidents</t>
+        </is>
+      </c>
+      <c r="H266" s="2" t="inlineStr">
+        <is>
+          <t>Pass (after fix)</t>
+        </is>
+      </c>
+      <c r="I266" s="2" t="inlineStr">
+        <is>
+          <t>Live page renders; found row-layout defect (meta overflow + id misalignment)</t>
+        </is>
+      </c>
+      <c r="J266" s="2" t="inlineStr">
+        <is>
+          <t>row-link__meta had nowrap without ellipsis in a narrower box; id centred against a 2-line block</t>
+        </is>
+      </c>
+      <c r="K266" s="2" t="inlineStr">
+        <is>
+          <t>app.css: ellipsize meta, align stacked rows to first line</t>
+        </is>
+      </c>
+      <c r="L266" s="2" t="inlineStr">
+        <is>
+          <t>verified in browser</t>
+        </is>
+      </c>
+      <c r="M266" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
+        <is>
+          <t>INC-08</t>
+        </is>
+      </c>
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>Integration: Telegram bot</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>Incident commands and Resolve button</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
+        <is>
+          <t>As an operator I want to close an incident from my phone.</t>
+        </is>
+      </c>
+      <c r="E267" s="2" t="inlineStr">
+        <is>
+          <t>'/incidents' lists open ones, '/resolve &lt;id&gt;' closes one; every incident notification carries a '✅ Resolve' inline button (callback resolve:&lt;incident_id&gt;) appended after the existing Approve/Reject/Discuss/Mute row.</t>
+        </is>
+      </c>
+      <c r="F267" s="2" t="inlineStr">
+        <is>
+          <t>app/services/telegram_bot.py, app/services/incidents.py _with_resolve_button</t>
+        </is>
+      </c>
+      <c r="G267" s="2" t="inlineStr">
+        <is>
+          <t>tests/test_incidents.py resolve-button test; Telegram /incidents (blocked while a second poller holds the token).</t>
+        </is>
+      </c>
+      <c r="H267" s="2" t="inlineStr">
+        <is>
+          <t>Blocked (needs docker/LLM/Telegram)</t>
+        </is>
+      </c>
+      <c r="I267" s="2" t="inlineStr">
+        <is>
+          <t>Resolve button verified by unit test; live button/commands unverifiable while a second poller holds the bot token (getUpdates 409)</t>
+        </is>
+      </c>
+      <c r="J267" s="2" t="inlineStr"/>
+      <c r="K267" s="2" t="inlineStr"/>
+      <c r="L267" s="2" t="inlineStr"/>
+      <c r="M267" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M259"/>
+  <autoFilter ref="A1:M267"/>
   <dataValidations count="1">
-    <dataValidation sqref="H2:H259" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="H2:H267" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not tested,Pass,Fail,Fixed - retest,Pass (after fix),Blocked (needs docker/LLM/Telegram),Won't fix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14954,7 +15406,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D52"/>
+  <dimension ref="A1:D54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
@@ -14984,7 +15436,7 @@
         </is>
       </c>
       <c r="B2" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$259,A2)</f>
+        <f>COUNTIF(Stories!$H$2:$H$267,A2)</f>
         <v/>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -14997,7 +15449,7 @@
         </is>
       </c>
       <c r="B3" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$259,A3)</f>
+        <f>COUNTIF(Stories!$H$2:$H$267,A3)</f>
         <v/>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -15010,7 +15462,7 @@
         </is>
       </c>
       <c r="B4" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$259,A4)</f>
+        <f>COUNTIF(Stories!$H$2:$H$267,A4)</f>
         <v/>
       </c>
       <c r="C4" s="4" t="n"/>
@@ -15023,7 +15475,7 @@
         </is>
       </c>
       <c r="B5" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$259,A5)</f>
+        <f>COUNTIF(Stories!$H$2:$H$267,A5)</f>
         <v/>
       </c>
       <c r="C5" s="4" t="n"/>
@@ -15036,7 +15488,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$259,A6)</f>
+        <f>COUNTIF(Stories!$H$2:$H$267,A6)</f>
         <v/>
       </c>
       <c r="C6" s="4" t="n"/>
@@ -15049,7 +15501,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$259,A7)</f>
+        <f>COUNTIF(Stories!$H$2:$H$267,A7)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="n"/>
@@ -15062,7 +15514,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>COUNTIF(Stories!$H$2:$H$259,A8)</f>
+        <f>COUNTIF(Stories!$H$2:$H$267,A8)</f>
         <v/>
       </c>
       <c r="C8" s="4" t="n"/>
@@ -15075,7 +15527,7 @@
         </is>
       </c>
       <c r="B9" s="4">
-        <f>COUNTA(Stories!$A$2:$A$259)</f>
+        <f>COUNTA(Stories!$A$2:$A$267)</f>
         <v/>
       </c>
       <c r="C9" s="4" t="n"/>
@@ -15139,15 +15591,15 @@
         </is>
       </c>
       <c r="B14" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A14)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A14)</f>
         <v/>
       </c>
       <c r="C14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A14,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A14,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A14,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A14,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D14" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A14,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A14,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15158,15 +15610,15 @@
         </is>
       </c>
       <c r="B15" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A15)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A15)</f>
         <v/>
       </c>
       <c r="C15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A15,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A15,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A15,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A15,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D15" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A15,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A15,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15177,15 +15629,15 @@
         </is>
       </c>
       <c r="B16" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A16)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A16)</f>
         <v/>
       </c>
       <c r="C16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A16,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A16,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A16,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A16,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D16" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A16,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A16,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -15196,680 +15648,718 @@
         </is>
       </c>
       <c r="B17" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A17)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A17)</f>
         <v/>
       </c>
       <c r="C17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A17,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A17,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A17,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A17,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D17" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A17,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A17,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>API: Insights</t>
+          <t>API: Incidents</t>
         </is>
       </c>
       <c r="B18" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A18)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A18)</f>
         <v/>
       </c>
       <c r="C18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A18,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A18,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A18,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A18,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D18" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A18,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A18,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>API: Issues</t>
+          <t>API: Insights</t>
         </is>
       </c>
       <c r="B19" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A19)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A19)</f>
         <v/>
       </c>
       <c r="C19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A19,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A19,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A19,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A19,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D19" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A19,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A19,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>API: Ollama</t>
+          <t>API: Issues</t>
         </is>
       </c>
       <c r="B20" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A20)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A20)</f>
         <v/>
       </c>
       <c r="C20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A20,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A20,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A20,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A20,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D20" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A20,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A20,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>API: Prompts</t>
+          <t>API: Ollama</t>
         </is>
       </c>
       <c r="B21" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A21)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A21)</f>
         <v/>
       </c>
       <c r="C21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A21,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A21,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A21,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A21,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D21" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A21,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A21,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>API: Reports</t>
+          <t>API: Prompts</t>
         </is>
       </c>
       <c r="B22" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A22)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A22)</f>
         <v/>
       </c>
       <c r="C22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A22,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A22,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A22,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A22,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D22" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A22,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A22,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
         <is>
-          <t>API: Security</t>
+          <t>API: Reports</t>
         </is>
       </c>
       <c r="B23" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A23)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A23)</f>
         <v/>
       </c>
       <c r="C23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A23,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A23,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A23,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A23,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D23" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A23,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A23,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
         <is>
-          <t>API: Sentinel</t>
+          <t>API: Security</t>
         </is>
       </c>
       <c r="B24" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A24)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A24)</f>
         <v/>
       </c>
       <c r="C24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A24,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A24,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A24,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A24,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D24" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A24,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A24,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
-          <t>API: Settings</t>
+          <t>API: Sentinel</t>
         </is>
       </c>
       <c r="B25" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A25)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A25)</f>
         <v/>
       </c>
       <c r="C25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A25,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A25,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A25,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A25,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D25" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A25,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A25,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>API: Telegram</t>
+          <t>API: Settings</t>
         </is>
       </c>
       <c r="B26" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A26)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A26)</f>
         <v/>
       </c>
       <c r="C26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A26,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A26,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A26,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A26,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D26" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A26,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A26,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>Config: Bootstrap</t>
+          <t>API: Telegram</t>
         </is>
       </c>
       <c r="B27" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A27)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A27)</f>
         <v/>
       </c>
       <c r="C27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A27,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A27,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A27,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A27,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D27" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A27,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A27,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>Config: Env</t>
+          <t>Config: Bootstrap</t>
         </is>
       </c>
       <c r="B28" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A28)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A28)</f>
         <v/>
       </c>
       <c r="C28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A28,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A28,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A28,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A28,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D28" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A28,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A28,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>Integration: CLI backends</t>
+          <t>Config: Env</t>
         </is>
       </c>
       <c r="B29" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A29)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A29)</f>
         <v/>
       </c>
       <c r="C29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A29,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A29,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A29,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A29,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D29" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A29,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A29,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>Integration: Telegram bot</t>
+          <t>Integration: CLI backends</t>
         </is>
       </c>
       <c r="B30" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A30)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A30)</f>
         <v/>
       </c>
       <c r="C30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A30,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A30,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A30,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A30,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D30" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A30,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A30,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>Integration: Telegram notify</t>
+          <t>Integration: Telegram bot</t>
         </is>
       </c>
       <c r="B31" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A31)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A31)</f>
         <v/>
       </c>
       <c r="C31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A31,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A31,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A31,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A31,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D31" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A31,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A31,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>Ops: Docker</t>
+          <t>Integration: Telegram notify</t>
         </is>
       </c>
       <c r="B32" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A32)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A32)</f>
         <v/>
       </c>
       <c r="C32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A32,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A32,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A32,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A32,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D32" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A32,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A32,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>Ops: Live deploy</t>
+          <t>Ops: Docker</t>
         </is>
       </c>
       <c r="B33" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A33)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A33)</f>
         <v/>
       </c>
       <c r="C33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A33,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A33,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A33,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A33,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D33" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A33,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A33,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
         <is>
-          <t>Ops: Migrations</t>
+          <t>Ops: Live deploy</t>
         </is>
       </c>
       <c r="B34" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A34)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A34)</f>
         <v/>
       </c>
       <c r="C34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A34,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A34,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A34,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A34,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D34" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A34,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A34,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Ops: Onboarding</t>
+          <t>Ops: Migrations</t>
         </is>
       </c>
       <c r="B35" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A35)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A35)</f>
         <v/>
       </c>
       <c r="C35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A35,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A35,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A35,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A35,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D35" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A35,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A35,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Alerts</t>
+          <t>Ops: Onboarding</t>
         </is>
       </c>
       <c r="B36" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A36)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A36)</f>
         <v/>
       </c>
       <c r="C36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A36,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A36,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A36,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A36,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D36" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A36,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A36,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Buffer</t>
+          <t>Pipeline: Alerts</t>
         </is>
       </c>
       <c r="B37" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A37)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A37)</f>
         <v/>
       </c>
       <c r="C37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A37,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A37,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A37,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A37,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D37" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A37,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A37,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: LLM</t>
+          <t>Pipeline: Buffer</t>
         </is>
       </c>
       <c r="B38" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A38)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A38)</f>
         <v/>
       </c>
       <c r="C38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A38,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A38,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A38,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A38,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D38" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A38,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A38,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Prefilter</t>
+          <t>Pipeline: LLM</t>
         </is>
       </c>
       <c r="B39" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A39)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A39)</f>
         <v/>
       </c>
       <c r="C39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A39,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A39,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A39,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A39,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D39" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A39,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A39,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Scheduler</t>
+          <t>Pipeline: Prefilter</t>
         </is>
       </c>
       <c r="B40" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A40)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A40)</f>
         <v/>
       </c>
       <c r="C40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A40,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A40,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A40,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A40,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D40" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A40,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A40,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Triage</t>
+          <t>Pipeline: Scheduler</t>
         </is>
       </c>
       <c r="B41" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A41)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A41)</f>
         <v/>
       </c>
       <c r="C41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A41,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A41,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A41,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A41,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D41" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A41,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A41,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
         <is>
-          <t>Pipeline: Watcher</t>
+          <t>Pipeline: Triage</t>
         </is>
       </c>
       <c r="B42" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A42)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A42)</f>
         <v/>
       </c>
       <c r="C42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A42,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A42,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A42,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A42,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D42" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A42,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A42,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
         <is>
-          <t>UI: Cross-cutting</t>
+          <t>Pipeline: Watcher</t>
         </is>
       </c>
       <c r="B43" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A43)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A43)</f>
         <v/>
       </c>
       <c r="C43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A43,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A43,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A43,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A43,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D43" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A43,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A43,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
         <is>
-          <t>UI: Dashboard</t>
+          <t>UI: Cross-cutting</t>
         </is>
       </c>
       <c r="B44" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A44)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A44)</f>
         <v/>
       </c>
       <c r="C44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A44,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A44,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A44,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A44,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D44" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A44,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A44,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>UI: Events</t>
+          <t>UI: Dashboard</t>
         </is>
       </c>
       <c r="B45" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A45)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A45)</f>
         <v/>
       </c>
       <c r="C45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A45,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A45,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A45,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A45,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D45" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A45,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A45,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
         <is>
-          <t>UI: Exclusions</t>
+          <t>UI: Events</t>
         </is>
       </c>
       <c r="B46" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A46)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A46)</f>
         <v/>
       </c>
       <c r="C46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A46,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A46,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A46,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A46,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D46" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A46,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A46,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
         <is>
-          <t>UI: Global</t>
+          <t>UI: Exclusions</t>
         </is>
       </c>
       <c r="B47" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A47)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A47)</f>
         <v/>
       </c>
       <c r="C47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A47,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A47,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A47,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A47,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D47" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A47,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A47,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
         <is>
-          <t>UI: Issues</t>
+          <t>UI: Global</t>
         </is>
       </c>
       <c r="B48" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A48)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A48)</f>
         <v/>
       </c>
       <c r="C48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A48,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A48,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A48,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A48,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D48" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A48,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A48,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>UI: Prompts</t>
+          <t>UI: Incidents</t>
         </is>
       </c>
       <c r="B49" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A49)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A49)</f>
         <v/>
       </c>
       <c r="C49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A49,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A49,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A49,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A49,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D49" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A49,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A49,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
         <is>
-          <t>UI: Reports</t>
+          <t>UI: Issues</t>
         </is>
       </c>
       <c r="B50" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A50)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A50)</f>
         <v/>
       </c>
       <c r="C50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A50,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A50,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A50,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A50,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D50" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A50,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A50,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
         <is>
-          <t>UI: Settings</t>
+          <t>UI: Prompts</t>
         </is>
       </c>
       <c r="B51" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A51)</f>
+        <f>COUNTIF(Stories!$B$2:$B$267,A51)</f>
         <v/>
       </c>
       <c r="C51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A51,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A51,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A51,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A51,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
       <c r="D51" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A51,Stories!$H$2:$H$259,"Fail")</f>
+        <f>COUNTIFS(Stories!$B$2:$B$267,A51,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
         <is>
+          <t>UI: Reports</t>
+        </is>
+      </c>
+      <c r="B52" s="4">
+        <f>COUNTIF(Stories!$B$2:$B$267,A52)</f>
+        <v/>
+      </c>
+      <c r="C52" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$267,A52,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A52,Stories!$H$2:$H$267,"Pass (after fix)")</f>
+        <v/>
+      </c>
+      <c r="D52" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$267,A52,Stories!$H$2:$H$267,"Fail")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>UI: Settings</t>
+        </is>
+      </c>
+      <c r="B53" s="4">
+        <f>COUNTIF(Stories!$B$2:$B$267,A53)</f>
+        <v/>
+      </c>
+      <c r="C53" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$267,A53,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A53,Stories!$H$2:$H$267,"Pass (after fix)")</f>
+        <v/>
+      </c>
+      <c r="D53" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$267,A53,Stories!$H$2:$H$267,"Fail")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
           <t>UI: Shell</t>
         </is>
       </c>
-      <c r="B52" s="4">
-        <f>COUNTIF(Stories!$B$2:$B$259,A52)</f>
+      <c r="B54" s="4">
+        <f>COUNTIF(Stories!$B$2:$B$267,A54)</f>
         <v/>
       </c>
-      <c r="C52" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A52,Stories!$H$2:$H$259,"Pass")+COUNTIFS(Stories!$B$2:$B$259,A52,Stories!$H$2:$H$259,"Pass (after fix)")</f>
+      <c r="C54" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$267,A54,Stories!$H$2:$H$267,"Pass")+COUNTIFS(Stories!$B$2:$B$267,A54,Stories!$H$2:$H$267,"Pass (after fix)")</f>
         <v/>
       </c>
-      <c r="D52" s="4">
-        <f>COUNTIFS(Stories!$B$2:$B$259,A52,Stories!$H$2:$H$259,"Fail")</f>
+      <c r="D54" s="4">
+        <f>COUNTIFS(Stories!$B$2:$B$267,A54,Stories!$H$2:$H$267,"Fail")</f>
         <v/>
       </c>
     </row>
